--- a/Figures.out/gbr_out_sheep_lon.xlsx
+++ b/Figures.out/gbr_out_sheep_lon.xlsx
@@ -1,320 +1,334 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\DMI.prediction\R\Figures.out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCDE331-CD59-4C0A-8637-6B899B9B6099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
-  <si>
-    <t xml:space="preserve">matrix.NA..nrow...n.rows..ncol...1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">species</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ndf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mod.form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mod.vers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m.stop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best.w.R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best.w.nRMSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best.w.CCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is.best.model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best.global.w.R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best.global.w.nRMSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best.global.w.CCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is.best.global.model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w.R2.mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w.nRMSE.mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w.CCC.mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w.R2.sd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w.nRMSE.sd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w.CCC.sd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean.coef.int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean.coef.BW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean.coef.ADG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean.coef.NDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean.coef.CP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean.coef.NDF_digest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test.r2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test.w.r2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test.nrmse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test.w.nrmse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coef.int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coef.BW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coef.ADG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coef.NDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coef.CP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coef.NDF_digest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">observed.Y</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="126">
+  <si>
+    <t>matrix.NA..nrow...n.rows..ncol...1.</t>
+  </si>
+  <si>
+    <t>loop.iter</t>
+  </si>
+  <si>
+    <t>species</t>
+  </si>
+  <si>
+    <t>ndf</t>
+  </si>
+  <si>
+    <t>mod.form</t>
+  </si>
+  <si>
+    <t>mod.vers</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>m.stop</t>
+  </si>
+  <si>
+    <t>nu</t>
+  </si>
+  <si>
+    <t>best.w.R2</t>
+  </si>
+  <si>
+    <t>best.w.nRMSE</t>
+  </si>
+  <si>
+    <t>best.w.CCC</t>
+  </si>
+  <si>
+    <t>is.best.model</t>
+  </si>
+  <si>
+    <t>best.global.w.R2</t>
+  </si>
+  <si>
+    <t>best.global.w.nRMSE</t>
+  </si>
+  <si>
+    <t>best.global.w.CCC</t>
+  </si>
+  <si>
+    <t>is.best.global.model</t>
+  </si>
+  <si>
+    <t>w.R2.mean</t>
+  </si>
+  <si>
+    <t>w.nRMSE.mean</t>
+  </si>
+  <si>
+    <t>w.CCC.mean</t>
+  </si>
+  <si>
+    <t>w.R2.sd</t>
+  </si>
+  <si>
+    <t>w.nRMSE.sd</t>
+  </si>
+  <si>
+    <t>w.CCC.sd</t>
+  </si>
+  <si>
+    <t>mean.coef.int</t>
+  </si>
+  <si>
+    <t>mean.coef.BW</t>
+  </si>
+  <si>
+    <t>mean.coef.ADG</t>
+  </si>
+  <si>
+    <t>mean.coef.NDF</t>
+  </si>
+  <si>
+    <t>mean.coef.CP</t>
+  </si>
+  <si>
+    <t>mean.coef.NDF_digest</t>
+  </si>
+  <si>
+    <t>test.r2</t>
+  </si>
+  <si>
+    <t>test.w.r2</t>
+  </si>
+  <si>
+    <t>test.nrmse</t>
+  </si>
+  <si>
+    <t>test.w.nrmse</t>
+  </si>
+  <si>
+    <t>coef.int</t>
+  </si>
+  <si>
+    <t>coef.BW</t>
+  </si>
+  <si>
+    <t>coef.ADG</t>
+  </si>
+  <si>
+    <t>coef.NDF</t>
+  </si>
+  <si>
+    <t>coef.CP</t>
+  </si>
+  <si>
+    <t>coef.NDF_digest</t>
+  </si>
+  <si>
+    <t>observed.Y</t>
   </si>
   <si>
     <t xml:space="preserve"> mod.Y </t>
   </si>
   <si>
-    <t xml:space="preserve">gbr.form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total.sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k.IDs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sample.size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">treatment.IDs.CCs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all.treatment.IDs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">treatment.IDs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">experiment.IDs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train.IDs</t>
+    <t>gbr.form</t>
+  </si>
+  <si>
+    <t>total.sample</t>
+  </si>
+  <si>
+    <t>k.IDs</t>
+  </si>
+  <si>
+    <t>sample.size</t>
+  </si>
+  <si>
+    <t>treatment.IDs.CCs</t>
+  </si>
+  <si>
+    <t>all.treatment.IDs</t>
+  </si>
+  <si>
+    <t>treatment.IDs</t>
+  </si>
+  <si>
+    <t>experiment.IDs</t>
+  </si>
+  <si>
+    <t>train.IDs</t>
   </si>
   <si>
     <t xml:space="preserve">k.IDs.length </t>
   </si>
   <si>
-    <t xml:space="preserve">train.IDs.length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">species.ndf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total.sample.size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight.list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDs.remaining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k.IDs.length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gbr.model.train.coef.int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gbr.model.train.coef.BW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gbr.model.train.coef.ADG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gbr.model.train.coef.NDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gbr.model.train.coef.NDF*Digest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gbr.model.train.coef.offset.plus.intercept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gbr.whole.sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.ut.ids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.coef.intercept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.coef.bw_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.coef.adg_g_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.coef.NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.coef.CP_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.coef.NDF_digest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.coef.offset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.coef.offset.plus.intercept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.predicted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.predicted.base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.residuals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ws.rms.residuals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">var.corr.bw.adg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">var.corr.bw.ndf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coef.NDF_Digest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coef.offset.plus.intercept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test.ccc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w.AIC.mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test.w.coef.bw.sd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd.coef.int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd.coef.BW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd.coef.ADG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd.coef.NDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd.coef.CP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd.coef.NDF_digest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-1-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(699.7, 696.5, 1390, 1540, 1521, 1263, 1426, 1345, 1317, 1170, 1150, 1210, 1190, 1150, 595.5, 596.38, 598.88, 589.88, 592.97, 1050, 1183, 1344, 877, 622.5, 604.2, 613, 615.5, 653.5, 629.5, 620.5, 702, 714, 536, 489, 518, 493, 452, 502)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(4, 140, 92, 93, 76, 215, 201, 73, 3, 155)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 208, 209, 210, 211, 212, 213)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(27, 27, 29, 29, 33, 33, 33, 34, 34, 40, 40, 40, 40, 40, 44, 44, 44, 44, 44, 47, 47, 47, 47, 48, 48, 48, 48, 48, 48, 48, 49, 50, 51, 51, 51, 51, 51, 51)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheep - Low NDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">numeric(0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 214, 215, 216)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+    <t>train.IDs.length</t>
+  </si>
+  <si>
+    <t>species.ndf</t>
+  </si>
+  <si>
+    <t>total.sample.size</t>
+  </si>
+  <si>
+    <t>weight.list</t>
+  </si>
+  <si>
+    <t>IDs.remaining</t>
+  </si>
+  <si>
+    <t>k.IDs.length</t>
+  </si>
+  <si>
+    <t>gbr.model.train.coef.int</t>
+  </si>
+  <si>
+    <t>gbr.model.train.coef.BW</t>
+  </si>
+  <si>
+    <t>gbr.model.train.coef.ADG</t>
+  </si>
+  <si>
+    <t>gbr.model.train.coef.NDF</t>
+  </si>
+  <si>
+    <t>gbr.model.train.coef.NDF*Digest</t>
+  </si>
+  <si>
+    <t>gbr.model.train.coef.offset.plus.intercept</t>
+  </si>
+  <si>
+    <t>gbr.whole.sample</t>
+  </si>
+  <si>
+    <t>ws.ut.ids</t>
+  </si>
+  <si>
+    <t>ws.coef.intercept</t>
+  </si>
+  <si>
+    <t>ws.coef.bw_kg</t>
+  </si>
+  <si>
+    <t>ws.coef.adg_g_day</t>
+  </si>
+  <si>
+    <t>ws.coef.NDF_nutrition</t>
+  </si>
+  <si>
+    <t>ws.coef.CP_nutrition</t>
+  </si>
+  <si>
+    <t>ws.coef.NDF_digest</t>
+  </si>
+  <si>
+    <t>ws.coef.offset</t>
+  </si>
+  <si>
+    <t>ws.coef.offset.plus.intercept</t>
+  </si>
+  <si>
+    <t>ws.predicted</t>
+  </si>
+  <si>
+    <t>ws.predicted.base</t>
+  </si>
+  <si>
+    <t>ws.residuals</t>
+  </si>
+  <si>
+    <t>ws.rms.residuals</t>
+  </si>
+  <si>
+    <t>var.corr.bw.adg</t>
+  </si>
+  <si>
+    <t>var.corr.bw.ndf</t>
+  </si>
+  <si>
+    <t>coef.NDF_Digest</t>
+  </si>
+  <si>
+    <t>coef.offset.plus.intercept</t>
+  </si>
+  <si>
+    <t>test.ccc</t>
+  </si>
+  <si>
+    <t>w.AIC.mean</t>
+  </si>
+  <si>
+    <t>test.w.coef.bw.sd</t>
+  </si>
+  <si>
+    <t>sd.coef.int</t>
+  </si>
+  <si>
+    <t>sd.coef.BW</t>
+  </si>
+  <si>
+    <t>sd.coef.ADG</t>
+  </si>
+  <si>
+    <t>sd.coef.NDF</t>
+  </si>
+  <si>
+    <t>sd.coef.CP</t>
+  </si>
+  <si>
+    <t>sd.coef.NDF_digest</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>1-1-1</t>
+  </si>
+  <si>
+    <t>c(699.7, 696.5, 1390, 1540, 1521, 1263, 1426, 1345, 1317, 1170, 1150, 1210, 1190, 1150, 595.5, 596.38, 598.88, 589.88, 592.97, 1050, 1183, 1344, 877, 622.5, 604.2, 613, 615.5, 653.5, 629.5, 620.5, 702, 714, 536, 489, 518, 493, 452, 502)</t>
+  </si>
+  <si>
+    <t>feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition</t>
+  </si>
+  <si>
+    <t>c(211, 190, 208, 164, 196, 195, 118, 203, 180, 209, 210, 198, 108, 163, 182, 165, 213, 194, 205)</t>
+  </si>
+  <si>
+    <t>c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 208, 209, 210, 211, 212, 213)</t>
+  </si>
+  <si>
+    <t>c(27, 27, 29, 29, 33, 33, 33, 34, 34, 40, 40, 40, 40, 40, 44, 44, 44, 44, 44, 47, 47, 47, 47, 48, 48, 48, 48, 48, 48, 48, 49, 50, 51, 51, 51, 51, 51, 51)</t>
+  </si>
+  <si>
+    <t>c(107, 116, 134, 136, 138, 141, 142, 166, 167, 181, 183, 184, 191, 192, 193, 197, 199, 200, 212)</t>
+  </si>
+  <si>
+    <t>Sheep - Low NDF</t>
+  </si>
+  <si>
+    <t>numeric(0)</t>
+  </si>
+  <si>
+    <t>c(2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 206, 207, 214, 215, 216)</t>
+  </si>
+  <si>
+    <t>list(baselearner = list(list(model.frame = function () 
 return(NULL), get_data = function () 
 X, get_index = function () 
 index, get_vary = function () 
@@ -447,7 +461,7 @@
     X %*% (MPinvS/sxtx)
 })), offset = 875.276578947368, ustart = c(`1376` = -175.576578947368, `1377` = -178.776578947368, `1487` = 514.723421052632, `1490` = 664.723421052632, `1585` = 645.723421052632, `1587` = 387.723421052632, `1589` = 550.723421052632, `1639` = 469.723421052632, `1640` = 441.723421052632, `1770` = 294.723421052632, `1771` = 274.723421052632, `1772` = 334.723421052632, `1773` = 314.723421052632, `1774` = 274.723421052632, `1815` = -279.776578947368, `1816` = -278.896578947368, `1817` = -276.396578947368, 
 `1818` = -285.396578947368, `1819` = -282.306578947368, `1921` = 174.723421052632, `1922` = 307.723421052632, `1923` = 468.723421052632, `1924` = 1.72342105263158, `1945` = -252.776578947368, `1946` = -271.076578947368, `1947` = -262.276578947368, `1948` = -259.776578947368, `1949` = -221.776578947368, `1950` = -245.776578947368, `1951` = -254.776578947368, `1968` = -173.276578947368, `1981` = -161.276578947368, `1984` = -339.276578947368, `1985` = -386.276578947368, `1986` = -357.276578947368, `1987` = -382.276578947368, 
-`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 5000, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
+`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 1200, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
 return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
 y - f, risk = function (y, f, w = 1) 
 sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
@@ -691,28 +705,34 @@
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = Gaussian(), center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(691.234685910472, 730.729826129403, 1396.59500461923, 1419.33832619022, 1404.10874389614, 1295.36613906271, 1342.88417526389, 1213.25637869862, 1160.18784500046, 1217.83458452687, 1179.6744289599, 1276.91568386276, 1234.25744214834, 1200.41462070877, 606.283247411266, 597.680497870004, 550.066064180819, 548.564373510168, 596.567570232544, 1099.21592090905, 1341.14640563975, 1376.79146803818, 1029.49010276743, 558.13890917452, 586.06427559218, 593.959176559273, 581.574031380779, 605.750311701354, 
-595.58363200239, 582.028451703026, 707.293741786882, 759.501008359582, 549.598077102173, 485.803012227071, 528.825811799412, 588.026318695766, 483.756128908562, 546.573074420696)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(-8.46531408952796, 34.2298261294027, 6.59500461922607, -120.661673809784, -116.891256103856, 32.3661390627135, -83.1158247361063, -131.743621301383, -156.812154999544, 47.8345845268746, 29.6744289599019, 66.915683862763, 44.2574421483416, 50.4146207087672, 10.7832474112661, 1.3004978700036, -48.8139358191805, -41.3156264898321, 3.5975702325444, 49.2159209090455, 158.146405639754, 32.7914680381818, 152.490102767426, -64.3610908254797, -18.1357244078196, -19.0408234407273, -33.9259686192207, -47.7496882986463, 
--33.9163679976101, -38.4715482969739, 5.29374178688158, 45.5010083595821, 13.5980771021725, -3.19698777292905, 10.8258117994117, 95.0263186957659, 31.7561289085617, 44.5730744206958)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(8.46531408952796, 34.2298261294027, 6.59500461922607, 120.661673809784, 116.891256103856, 32.3661390627135, 83.1158247361063, 131.743621301383, 156.812154999544, 47.8345845268746, 29.6744289599019, 66.915683862763, 44.2574421483416, 50.4146207087672, 10.7832474112661, 1.3004978700036, 48.8139358191805, 41.3156264898321, 3.5975702325444, 49.2159209090455, 158.146405639754, 32.7914680381818, 152.490102767426, 64.3610908254797, 18.1357244078196, 19.0408234407273, 33.9259686192207, 47.7496882986463, 
-33.9163679976101, 38.4715482969739, 5.29374178688158, 45.5010083595821, 13.5980771021725, 3.19698777292905, 10.8258117994117, 95.0263186957659, 31.7561289085617, 44.5730744206958)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(153, 109, 214, 120, 121, 122, 154, 135, 72, 137)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2, 72, 74, 75, 77, 91, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 153, 154, 156, 171, 202, 214, 216)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+}, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t>c(707.387903197369, 747.269284368318, 1392.34364465428, 1410.15103076313, 1443.02412839264, 1333.73762586257, 1381.50854611726, 1157.05712222907, 1099.73730392678, 1204.80399597263, 1167.20833749162, 1266.37625686965, 1232.28824225727, 1190.91532121986, 616.691698335388, 611.475861394407, 568.840459284907, 568.501613183089, 607.226861030828, 1087.15364912471, 1329.52651012155, 1365.95050495955, 1004.54610534464, 569.222566311438, 594.498332157763, 602.411574724184, 591.596278371552, 615.925763531856, 
+606.064616955656, 592.568028767716, 710.717265651254, 758.989955179538, 556.740153027197, 490.873903139578, 535.239033898342, 594.989247491447, 488.81891177283, 553.145499971653)</t>
+  </si>
+  <si>
+    <t>c(7.68790319736911, 50.7692843683184, 2.34364465427598, -129.848969236873, -77.9758716073634, 70.7376258625673, -44.4914538827372, -187.942877770931, -217.26269607322, 34.8039959726289, 17.2083374916167, 56.3762568696516, 42.2882422572723, 40.9153212198648, 21.1916983353875, 15.0958613944066, -30.0395407150928, -21.3783868169107, 14.2568610308281, 37.1536491247061, 146.526510121551, 21.9505049595498, 127.546105344645, -53.2774336885616, -9.70166784223659, -10.5884252758161, -23.9037216284479, -37.5742364681441, 
+-23.435383044344, -27.9319712322839, 8.71726565125391, 44.9899551795377, 20.7401530271975, 1.87390313957786, 17.2390338983423, 101.989247491447, 36.8189117728297, 51.145499971653)</t>
+  </si>
+  <si>
+    <t>c(7.68790319736911, 50.7692843683184, 2.34364465427598, 129.848969236873, 77.9758716073634, 70.7376258625673, 44.4914538827372, 187.942877770931, 217.26269607322, 34.8039959726289, 17.2083374916167, 56.3762568696516, 42.2882422572723, 40.9153212198648, 21.1916983353875, 15.0958613944066, 30.0395407150928, 21.3783868169107, 14.2568610308281, 37.1536491247061, 146.526510121551, 21.9505049595498, 127.546105344645, 53.2774336885616, 9.70166784223659, 10.5884252758161, 23.9037216284479, 37.5742364681441, 
+23.435383044344, 27.9319712322839, 8.71726565125391, 44.9899551795377, 20.7401530271975, 1.87390313957786, 17.2390338983423, 101.989247491447, 36.8189117728297, 51.145499971653)</t>
+  </si>
+  <si>
+    <t>c(200, 134, 138, 199, 197, 166, 116, 167, 212, 193, 136, 191, 142, 181, 107, 192, 183, 141, 184)</t>
+  </si>
+  <si>
+    <t>c(108, 118, 163, 164, 165, 180, 182, 190, 194, 195, 196, 198, 203, 205, 208, 209, 210, 211, 213)</t>
+  </si>
+  <si>
+    <t>2-1-1</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>list(baselearner = list(list(model.frame = function () 
 return(NULL), get_data = function () 
 X, get_index = function () 
 index, get_vary = function () 
@@ -843,16 +863,14 @@
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-})), offset = 875.276578947368, ustart = c(`1376` = -175.576578947368, `1377` = -178.776578947368, `1487` = 514.723421052632, `1490` = 664.723421052632, `1585` = 645.723421052632, `1587` = 387.723421052632, `1589` = 550.723421052632, `1639` = 469.723421052632, `1640` = 441.723421052632, `1770` = 294.723421052632, `1771` = 274.723421052632, `1772` = 334.723421052632, `1773` = 314.723421052632, `1774` = 274.723421052632, `1815` = -279.776578947368, `1816` = -278.896578947368, `1817` = -276.396578947368, 
-`1818` = -285.396578947368, `1819` = -282.306578947368, `1921` = 174.723421052632, `1922` = 307.723421052632, `1923` = 468.723421052632, `1924` = 1.72342105263158, `1945` = -252.776578947368, `1946` = -271.076578947368, `1947` = -262.276578947368, `1948` = -259.776578947368, `1949` = -221.776578947368, `1950` = -245.776578947368, `1951` = -254.776578947368, `1968` = -173.276578947368, `1981` = -161.276578947368, `1984` = -339.276578947368, `1985` = -386.276578947368, `1986` = -357.276578947368, `1987` = -382.276578947368, 
-`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 2062, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
-return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
-y - f, risk = function (y, f, w = 1) 
-sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
-UseMethod("weighted.mean"), check_y = function (y) 
+})), offset = 697.910728140674, ustart = c(`1376` = 1, `1377` = -1, `1487` = 1, `1490` = 1, `1585` = 1, `1587` = 1, `1589` = 1, `1639` = 1, `1640` = 1, `1770` = 1, `1771` = 1, `1772` = 1, `1773` = 1, `1774` = 1, `1815` = -1, `1816` = -1, `1817` = -1, `1818` = -1, `1819` = -1, `1921` = 1, `1922` = 1, `1923` = 1, `1924` = 1, `1945` = -1, `1946` = -1, `1947` = -1, `1948` = -1, `1949` = -1, `1950` = -1, `1951` = -1, `1968` = 1, `1981` = 1, `1984` = -1, `1985` = -1, `1986` = -1, `1987` = -1, `1988` = -1, 
+`1989` = -1), control = list(mstop = 1200, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family", ngradient = function (y, f, w = 1) 
+sign(y - f), risk = function (y, f, w = 1) 
+sum(w * loss(y, f), na.rm = TRUE), offset = function (y, w) 
+optimize(risk, interval = range(y), y = y, w = w)$minimum, check_y = function (y) 
 {
     if (!is.numeric(y) || !is.null(dim(y))) 
-        stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
+        stop("response is not a numeric vector but ", sQuote("family = Laplace()"))
     y
 }, weights = function (w) 
 {
@@ -860,7 +878,7 @@
 }, nuisance = function () 
 return(NA), response = function (f) 
 f, rclass = function (f) 
-NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, `1949` = 653.5, 
+NA, name = "Absolute Error", charloss = "abs(y - f) \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, `1949` = 653.5, 
 `1950` = 629.5, `1951` = 620.5, `1968` = 702, `1981` = 714, `1984` = 536, `1985` = 489, `1986` = 518, `1987` = 493, `1988` = 452, `1989` = 502), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968", "1981", "1984", "1985", "1986", "1987", "1988", "1989"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 
 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
 nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
@@ -1089,28 +1107,22 @@
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = Gaussian(), center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(696.004400208782, 735.672952968239, 1395.87378190445, 1417.11269015581, 1417.06165313796, 1307.96439472255, 1355.64200419042, 1195.87328462709, 1141.42706340066, 1214.20604512029, 1176.16808302042, 1274.15258708777, 1234.14303949842, 1197.875640349, 609.230252357052, 601.678846842701, 555.566634938029, 554.42963038817, 599.595474136502, 1095.63512435983, 1338.06050227828, 1373.9964427028, 1021.76991137953, 561.186404812204, 588.380578169741, 596.294836731875, 584.355558921707, 608.61354112437, 
-598.535216898225, 584.980928912767, 708.073172119809, 759.092935740356, 551.342753760616, 486.810104927978, 530.313866278004, 589.784094387614, 484.757189580247, 548.140297461602)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(-3.69559979121811, 39.1729529682386, 5.87378190444588, -122.887309844188, -103.93834686204, 44.9643947225454, -70.3579958095779, -149.126715372909, -175.572936599343, 44.2060451202851, 26.1680830204191, 64.1525870877672, 44.1430394984186, 47.8756403489972, 13.730252357052, 5.29884684270121, -43.3133650619715, -35.4503696118303, 6.62547413650236, 45.6351243598262, 155.060502278284, 29.9964427027962, 144.769911379527, -61.3135951877961, -15.8194218302589, -16.7051632681255, -31.1444410782929, -44.8864588756298, 
--30.9647831017747, -35.5190710872328, 6.07317211980887, 45.0929357403561, 15.342753760616, -2.18989507202247, 12.3138662780041, 96.7840943876142, 32.7571895802471, 46.140297461602)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(3.69559979121811, 39.1729529682386, 5.87378190444588, 122.887309844188, 103.93834686204, 44.9643947225454, 70.3579958095779, 149.126715372909, 175.572936599343, 44.2060451202851, 26.1680830204191, 64.1525870877672, 44.1430394984186, 47.8756403489972, 13.730252357052, 5.29884684270121, 43.3133650619715, 35.4503696118303, 6.62547413650236, 45.6351243598262, 155.060502278284, 29.9964427027962, 144.769911379527, 61.3135951877961, 15.8194218302589, 16.7051632681255, 31.1444410782929, 44.8864588756298, 
-30.9647831017747, 35.5190710872328, 6.07317211980887, 45.0929357403561, 15.342753760616, 2.18989507202247, 12.3138662780041, 96.7840943876142, 32.7571895802471, 46.140297461602)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg.e75 + adg_g_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 139, 4, 216, 109, 73, 72, 156, 153, 93)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+}, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>feed_intake_g_d ~ bw_kg + bw_kg.sqd + adg_g_day + NDF_nutrition</t>
+  </si>
+  <si>
+    <t>c(118, 197, 142, 213, 182, 164, 199, 195, 203, 183, 141, 198, 116, 211, 209, 210, 191, 193, 194)</t>
+  </si>
+  <si>
+    <t>c(107, 108, 134, 136, 138, 163, 165, 166, 167, 180, 181, 184, 190, 192, 196, 200, 205, 208, 212)</t>
+  </si>
+  <si>
+    <t>list(baselearner = list(list(model.frame = function () 
 return(NULL), get_data = function () 
 X, get_index = function () 
 index, get_vary = function () 
@@ -1231,7 +1243,7 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, Xnames = c("(Intercept)", "bw_kg.e75", "adg_g_day", "NDF_nutrition"), MPinv = function () 
+}, Xnames = c("(Intercept)", "bw_kg", "bw_kg.sqd", "adg_g_day", "NDF_nutrition"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
@@ -1243,7 +1255,7 @@
     X %*% (MPinvS/sxtx)
 })), offset = 875.276578947368, ustart = c(`1376` = -175.576578947368, `1377` = -178.776578947368, `1487` = 514.723421052632, `1490` = 664.723421052632, `1585` = 645.723421052632, `1587` = 387.723421052632, `1589` = 550.723421052632, `1639` = 469.723421052632, `1640` = 441.723421052632, `1770` = 294.723421052632, `1771` = 274.723421052632, `1772` = 334.723421052632, `1773` = 314.723421052632, `1774` = 274.723421052632, `1815` = -279.776578947368, `1816` = -278.896578947368, `1817` = -276.396578947368, 
 `1818` = -285.396578947368, `1819` = -282.306578947368, `1921` = 174.723421052632, `1922` = 307.723421052632, `1923` = 468.723421052632, `1924` = 1.72342105263158, `1945` = -252.776578947368, `1946` = -271.076578947368, `1947` = -262.276578947368, `1948` = -259.776578947368, `1949` = -221.776578947368, `1950` = -245.776578947368, `1951` = -254.776578947368, `1968` = -173.276578947368, `1981` = -161.276578947368, `1984` = -339.276578947368, `1985` = -386.276578947368, `1986` = -357.276578947368, `1987` = -382.276578947368, 
-`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 5000, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
+`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 1200, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
 return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
 y - f, risk = function (y, f, w = 1) 
 sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
@@ -1487,40 +1499,28 @@
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = Gaussian(), center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(694.24387966202, 733.983037297086, 1397.47551913153, 1418.85587394392, 1408.25878845572, 1299.5491841656, 1347.05482177669, 1191.98521376248, 1138.40304873107, 1218.34606082634, 1180.46129373252, 1277.78467918857, 1237.07196906038, 1201.84017900178, 607.287741585154, 598.060607534112, 548.701120873963, 546.806533887958, 597.073925648443, 1099.59153962548, 1340.57972608526, 1376.19840139404, 1026.5245275721, 559.722272942937, 586.793242979015, 594.682937616884, 582.680452908119, 607.012082431985, 
-596.575427832741, 582.875466548556, 710.864903597913, 762.964401670314, 552.469551257775, 488.460984979319, 531.620530386804, 590.836776448236, 486.415005901661, 549.37176854652)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(-5.45612033797988, 37.4830372970856, 7.4755191315312, -121.144126056078, -112.741211544276, 36.549184165601, -78.9451782233098, -153.014786237515, -178.596951268935, 48.3460608263424, 30.4612937325244, 67.7846791885747, 47.0719690603792, 51.840179001782, 11.7877415851539, 1.68060753411237, -50.1788791260367, -43.073466112042, 4.10392564844278, 49.5915396254786, 157.579726085259, 32.1984013940382, 149.524527572099, -62.7777270570625, -17.4067570209849, -18.3170623831156, -32.8195470918811, -46.4879175680154, 
--32.9245721672594, -37.6245334514442, 8.86490359791287, 48.9644016703143, 16.469551257775, -0.53901502068129, 13.620530386804, 97.8367764482365, 34.4150059016614, 47.3717685465195)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(5.45612033797988, 37.4830372970856, 7.4755191315312, 121.144126056078, 112.741211544276, 36.549184165601, 78.9451782233098, 153.014786237515, 178.596951268935, 48.3460608263424, 30.4612937325244, 67.7846791885747, 47.0719690603792, 51.840179001782, 11.7877415851539, 1.68060753411237, 50.1788791260367, 43.073466112042, 4.10392564844278, 49.5915396254786, 157.579726085259, 32.1984013940382, 149.524527572099, 62.7777270570625, 17.4067570209849, 18.3170623831156, 32.8195470918811, 46.4879175680154, 
-32.9245721672594, 37.6245334514442, 8.86490359791287, 48.9644016703143, 16.469551257775, 0.53901502068129, 13.620530386804, 97.8367764482365, 34.4150059016614, 47.3717685465195)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(92, 3, 154, 215, 106, 140, 77, 91, 105, 75)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2, 3, 75, 76, 77, 91, 92, 105, 106, 119, 120, 121, 122, 135, 137, 140, 154, 155, 171, 201, 202, 214, 215)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(699.7, 696.5, 1390, 1540, 1521, 1263, 1426, 1345, 1317, 1170, 1150, 1210, 1190, 1150, 595.5, 596.38, 598.88, 589.88, 592.97, 1050, 1183, 1344, 877, 622.5, 604.2, 613, 615.5, 653.5, 629.5, 620.5, 702)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg.e75 + adg_g_day + NDF_nutrition.sqd + CP_nutrition.log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(156, 135, 4, 92, 140, 119, 153, 76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t>c(688.982031338571, 727.917117251008, 1388.12848446115, 1412.9474094908, 1415.47799505845, 1305.84037122978, 1353.75201209906, 1269.10256892563, 1214.94177764155, 1204.26464785288, 1165.33829584855, 1263.89578097819, 1220.07549329176, 1185.83626064049, 607.539970771731, 603.419731299575, 564.882524875035, 565.42024789562, 599.802899811298, 1086.32442615241, 1333.11616855286, 1369.53801957658, 1020.79396885958, 557.47872631712, 586.969007428779, 594.92541082397, 582.098411249916, 605.881064141295, 
+596.895500134169, 583.868144575807, 693.393813492161, 742.811545956923, 541.086302309205, 476.478032631793, 520.040294596191, 579.769763281921, 474.414652447199, 537.94521149965)</t>
+  </si>
+  <si>
+    <t>c(-10.7179686614295, 31.4171172510075, -1.87151553885292, -127.052590509199, -105.522004941552, 42.8403712297804, -72.2479879009363, -75.8974310743695, -102.058222358445, 34.2646478528845, 15.3382958485499, 53.8957809781941, 30.0754932917635, 35.836260640488, 12.0399707717309, 7.03973129957456, -33.997475124965, -24.4597521043801, 6.83289981129838, 36.3244261524087, 150.11616855286, 25.538019576582, 143.793968859579, -65.02127368288, -17.2309925712204, -18.07458917603, -33.4015887500838, -47.6189358587047, 
+-32.6044998658308, -36.6318554241934, -8.60618650783852, 28.8115459569231, 5.08630230920517, -12.5219673682074, 2.04029459619051, 86.7697632819209, 22.4146524471988, 35.9452114996498)</t>
+  </si>
+  <si>
+    <t>c(10.7179686614295, 31.4171172510075, 1.87151553885292, 127.052590509199, 105.522004941552, 42.8403712297804, 72.2479879009363, 75.8974310743695, 102.058222358445, 34.2646478528845, 15.3382958485499, 53.8957809781941, 30.0754932917635, 35.836260640488, 12.0399707717309, 7.03973129957456, 33.997475124965, 24.4597521043801, 6.83289981129838, 36.3244261524087, 150.11616855286, 25.538019576582, 143.793968859579, 65.02127368288, 17.2309925712204, 18.07458917603, 33.4015887500838, 47.6189358587047, 32.6044998658308, 
+36.6318554241934, 8.60618650783852, 28.8115459569231, 5.08630230920517, 12.5219673682074, 2.04029459619051, 86.7697632819209, 22.4146524471988, 35.9452114996498)</t>
+  </si>
+  <si>
+    <t>c(200, 165, 205, 184, 107, 180, 138, 190, 212, 208, 167, 134, 192, 166, 196, 181, 163, 136, 108)</t>
+  </si>
+  <si>
+    <t>c(116, 118, 141, 142, 164, 182, 183, 191, 193, 194, 195, 197, 198, 199, 203, 209, 210, 211, 213)</t>
+  </si>
+  <si>
+    <t>list(baselearner = list(list(model.frame = function () 
 return(NULL), get_data = function () 
 X, get_index = function () 
 index, get_vary = function () 
@@ -1641,7 +1641,7 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, Xnames = c("(Intercept)", "bw_kg.e75", "adg_g_day", "NDF_nutrition.sqd", "CP_nutrition.log"), MPinv = function () 
+}, Xnames = c("(Intercept)", "bw_kg", "bw_kg.sqd", "adg_g_day", "NDF_nutrition"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
@@ -1651,25 +1651,26 @@
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-})), offset = 953.435806451613, ustart = c(`1376` = -253.735806451613, `1377` = -256.935806451613, `1487` = 436.564193548387, `1490` = 586.564193548387, `1585` = 567.564193548387, `1587` = 309.564193548387, `1589` = 472.564193548387, `1639` = 391.564193548387, `1640` = 363.564193548387, `1770` = 216.564193548387, `1771` = 196.564193548387, `1772` = 256.564193548387, `1773` = 236.564193548387, `1774` = 196.564193548387, `1815` = -357.935806451613, `1816` = -357.055806451613, `1817` = -354.555806451613, 
-`1818` = -363.555806451613, `1819` = -360.465806451613, `1921` = 96.5641935483872, `1922` = 229.564193548387, `1923` = 390.564193548387, `1924` = -76.4358064516128, `1945` = -330.935806451613, `1946` = -349.235806451613, `1947` = -340.435806451613, `1948` = -337.935806451613, `1949` = -299.935806451613, `1950` = -323.935806451613, `1951` = -332.935806451613, `1968` = -251.435806451613), control = list(mstop = 3351, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", 
-    fW = function (f) 
-    return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
-    y - f, risk = function (y, f, w = 1) 
-    sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
-    UseMethod("weighted.mean"), check_y = function (y) 
-    {
-        if (!is.numeric(y) || !is.null(dim(y))) 
-            stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
-        y
-    }, weights = function (w) 
-    {
-        switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
-    }, nuisance = function () 
-    return(NA), response = function (f) 
-    f, rclass = function (f) 
-    NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, 
-`1949` = 653.5, `1950` = 629.5, `1951` = 620.5, `1968` = 702), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+})), offset = 875.276578947368, ustart = c(`1376` = -175.576578947368, `1377` = -178.776578947368, `1487` = 514.723421052632, `1490` = 664.723421052632, `1585` = 645.723421052632, `1587` = 387.723421052632, `1589` = 550.723421052632, `1639` = 469.723421052632, `1640` = 441.723421052632, `1770` = 294.723421052632, `1771` = 274.723421052632, `1772` = 334.723421052632, `1773` = 314.723421052632, `1774` = 274.723421052632, `1815` = -279.776578947368, `1816` = -278.896578947368, `1817` = -276.396578947368, 
+`1818` = -285.396578947368, `1819` = -282.306578947368, `1921` = 174.723421052632, `1922` = 307.723421052632, `1923` = 468.723421052632, `1924` = 1.72342105263158, `1945` = -252.776578947368, `1946` = -271.076578947368, `1947` = -262.276578947368, `1948` = -259.776578947368, `1949` = -221.776578947368, `1950` = -245.776578947368, `1951` = -254.776578947368, `1968` = -173.276578947368, `1981` = -161.276578947368, `1984` = -339.276578947368, `1985` = -386.276578947368, `1986` = -357.276578947368, `1987` = -382.276578947368, 
+`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 1168, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
+return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
+y - f, risk = function (y, f, w = 1) 
+sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
+UseMethod("weighted.mean"), check_y = function (y) 
+{
+    if (!is.numeric(y) || !is.null(dim(y))) 
+        stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
+    y
+}, weights = function (w) 
+{
+    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
+}, nuisance = function () 
+return(NA), response = function (f) 
+f, rclass = function (f) 
+NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, `1949` = 653.5, 
+`1950` = 629.5, `1951` = 620.5, `1968` = 702, `1981` = 714, `1984` = 536, `1985` = 489, `1986` = 518, `1987` = 493, `1988` = 452, `1989` = 502), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968", "1981", "1984", "1985", "1986", "1987", "1988", "1989"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 
+1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
 nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
 {
     res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
@@ -1896,28 +1897,22 @@
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = Gaussian(), center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(726.664713616053, 756.276257112251, 1426.49199116427, 1433.84390976671, 1390.80072847693, 1320.53294965235, 1347.46987139732, 1208.12420743823, 1141.11325920574, 1198.25439364873, 1165.55436879291, 1252.42654332159, 1217.17574328645, 1184.45883833017, 645.240759162444, 640.675960555899, 599.501676831111, 593.060767187753, 634.658108983854, 1121.43313226861, 1334.12241686899, 1366.77271874675, 1045.4981062457, 586.476957198727, 574.890736005953, 586.463062140276, 582.300907213488, 605.776825004966, 
-597.895633984322, 587.465930386195, 704.059562576193)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(26.9647136160531, 59.7762571122507, 36.4919911642653, -106.156090233294, -130.199271523071, 57.5329496523539, -78.5301286026779, -136.875792561766, -175.886740794263, 28.25439364873, 15.5543687929148, 42.4265433215883, 27.1757432864545, 34.458838330173, 49.7407591624444, 44.2959605558989, 0.621676831111017, 3.18076718775308, 41.6881089838537, 71.433132268613, 151.122416868992, 22.7727187467453, 168.498106245696, -36.0230428012727, -29.3092639940473, -26.5369378597238, -33.1990927865115, -47.723174995034, 
--31.6043660156784, -33.0340696138048, 2.05956257619266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(26.9647136160531, 59.7762571122507, 36.4919911642653, 106.156090233294, 130.199271523071, 57.5329496523539, 78.5301286026779, 136.875792561766, 175.886740794263, 28.25439364873, 15.5543687929148, 42.4265433215883, 27.1757432864545, 34.458838330173, 49.7407591624444, 44.2959605558989, 0.621676831111017, 3.18076718775308, 41.6881089838537, 71.433132268613, 151.122416868992, 22.7727187467453, 168.498106245696, 36.0230428012727, 29.3092639940473, 26.5369378597238, 33.1990927865115, 47.723174995034, 
-31.6043660156784, 33.0340696138048, 2.05956257619266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 201, 120, 171, 73, 72, 109, 74)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2, 3, 72, 73, 74, 75, 77, 91, 93, 105, 106, 109, 120, 121, 122, 137, 139, 154, 155, 171, 201, 202, 214, 215, 216)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t>c(688.978383452354, 727.915434368706, 1388.15197204725, 1412.96701576245, 1415.46461151288, 1305.82698768421, 1353.73862855349, 1269.0028502715, 1214.84205898742, 1204.29117075935, 1165.36548344705, 1263.92265314254, 1220.10362696803, 1185.86433019706, 607.525568568919, 603.397019570112, 564.842129973743, 565.376068961711, 599.784300602959, 1086.34917977886, 1333.13673890677, 1369.55802951575, 1020.80880711259, 557.467835874906, 586.954348649523, 594.910752044714, 582.085027704345, 605.868936708071, 
+596.880841354913, 583.852191441527, 693.411785587666, 742.836152994652, 541.090722000649, 476.482452323237, 520.044714287634, 579.774182973365, 474.419072138643, 537.949631191094)</t>
+  </si>
+  <si>
+    <t>c(-10.7216165476459, 31.4154343687064, -1.84802795275482, -127.032984237555, -105.535388487123, 42.8269876842091, -72.2613714465074, -75.9971497284996, -102.157941012576, 34.2911707593491, 15.3654834470451, 53.9226531425411, 30.103626968026, 35.8643301970556, 12.0255685689185, 7.01701957011221, -34.0378700262571, -24.5039310382892, 6.81430060295941, 36.3491797788565, 150.136738906773, 25.5580295157461, 143.808807112591, -65.0321641250943, -17.2456513504768, -18.0892479552864, -33.4149722956549, -47.6310632919286, 
+-32.6191586450871, -36.6478085584727, -8.58821441233397, 28.8361529946517, 5.09072200064907, -12.5175476767635, 2.04471428763441, 86.7741829733648, 22.4190721386427, 35.9496311910937)</t>
+  </si>
+  <si>
+    <t>c(10.7216165476459, 31.4154343687064, 1.84802795275482, 127.032984237555, 105.535388487123, 42.8269876842091, 72.2613714465074, 75.9971497284996, 102.157941012576, 34.2911707593491, 15.3654834470451, 53.9226531425411, 30.103626968026, 35.8643301970556, 12.0255685689185, 7.01701957011221, 34.0378700262571, 24.5039310382892, 6.81430060295941, 36.3491797788565, 150.136738906773, 25.5580295157461, 143.808807112591, 65.0321641250943, 17.2456513504768, 18.0892479552864, 33.4149722956549, 47.6310632919286, 
+32.6191586450871, 36.6478085584727, 8.58821441233397, 28.8361529946517, 5.09072200064907, 12.5175476767635, 2.04471428763441, 86.7741829733648, 22.4190721386427, 35.9496311910937)</t>
+  </si>
+  <si>
+    <t>list(baselearner = list(list(model.frame = function () 
 return(NULL), get_data = function () 
 X, get_index = function () 
 index, get_vary = function () 
@@ -2038,7 +2033,7 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, Xnames = c("(Intercept)", "bw_kg.e75", "adg_g_day", "NDF_nutrition.sqd", "CP_nutrition.log"), MPinv = function () 
+}, Xnames = c("(Intercept)", "bw_kg", "bw_kg.sqd", "adg_g_day", "NDF_nutrition"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
@@ -2048,25 +2043,24 @@
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-})), offset = 953.435806451613, ustart = c(`1376` = -253.735806451613, `1377` = -256.935806451613, `1487` = 436.564193548387, `1490` = 586.564193548387, `1585` = 567.564193548387, `1587` = 309.564193548387, `1589` = 472.564193548387, `1639` = 391.564193548387, `1640` = 363.564193548387, `1770` = 216.564193548387, `1771` = 196.564193548387, `1772` = 256.564193548387, `1773` = 236.564193548387, `1774` = 196.564193548387, `1815` = -357.935806451613, `1816` = -357.055806451613, `1817` = -354.555806451613, 
-`1818` = -363.555806451613, `1819` = -360.465806451613, `1921` = 96.5641935483872, `1922` = 229.564193548387, `1923` = 390.564193548387, `1924` = -76.4358064516128, `1945` = -330.935806451613, `1946` = -349.235806451613, `1947` = -340.435806451613, `1948` = -337.935806451613, `1949` = -299.935806451613, `1950` = -323.935806451613, `1951` = -332.935806451613, `1968` = -251.435806451613), control = list(mstop = 5000, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", 
-    fW = function (f) 
-    return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
-    y - f, risk = function (y, f, w = 1) 
-    sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
-    UseMethod("weighted.mean"), check_y = function (y) 
-    {
-        if (!is.numeric(y) || !is.null(dim(y))) 
-            stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
-        y
-    }, weights = function (w) 
-    {
-        switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
-    }, nuisance = function () 
-    return(NA), response = function (f) 
-    f, rclass = function (f) 
-    NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, 
-`1949` = 653.5, `1950` = 629.5, `1951` = 620.5, `1968` = 702), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+})), offset = 697.910728140674, ustart = c(`1376` = 1, `1377` = -1, `1487` = 1, `1490` = 1, `1585` = 1, `1587` = 1, `1589` = 1, `1639` = 1, `1640` = 1, `1770` = 1, `1771` = 1, `1772` = 1, `1773` = 1, `1774` = 1, `1815` = -1, `1816` = -1, `1817` = -1, `1818` = -1, `1819` = -1, `1921` = 1, `1922` = 1, `1923` = 1, `1924` = 1, `1945` = -1, `1946` = -1, `1947` = -1, `1948` = -1, `1949` = -1, `1950` = -1, `1951` = -1, `1968` = 1, `1981` = 1, `1984` = -1, `1985` = -1, `1986` = -1, `1987` = -1, `1988` = -1, 
+`1989` = -1), control = list(mstop = 1200, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family", ngradient = function (y, f, w = 1) 
+sign(y - f), risk = function (y, f, w = 1) 
+sum(w * loss(y, f), na.rm = TRUE), offset = function (y, w) 
+optimize(risk, interval = range(y), y = y, w = w)$minimum, check_y = function (y) 
+{
+    if (!is.numeric(y) || !is.null(dim(y))) 
+        stop("response is not a numeric vector but ", sQuote("family = Laplace()"))
+    y
+}, weights = function (w) 
+{
+    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
+}, nuisance = function () 
+return(NA), response = function (f) 
+f, rclass = function (f) 
+NA, name = "Absolute Error", charloss = "abs(y - f) \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, `1949` = 653.5, 
+`1950` = 629.5, `1951` = 620.5, `1968` = 702, `1981` = 714, `1984` = 536, `1985` = 489, `1986` = 518, `1987` = 493, `1988` = 452, `1989` = 502), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968", "1981", "1984", "1985", "1986", "1987", "1988", "1989"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 
+1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
 nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
 {
     res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
@@ -2293,27 +2287,14 @@
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = Gaussian(), center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(728.301234410878, 757.836529382397, 1429.10525967987, 1435.82973116948, 1382.39460076689, 1315.03395315272, 1340.69137541636, 1222.3844862093, 1154.1459702716, 1197.53189828898, 1165.0815633701, 1250.99656276731, 1214.14460564679, 1183.17468159184, 641.9218475661, 636.954330831244, 595.116017971238, 588.461281827217, 630.594219845623, 1126.48320390415, 1336.21677762916, 1368.75142757264, 1051.99115248116, 585.911385621541, 571.322250211811, 582.709915508142, 579.851660053858, 603.163853286224, 
-594.953249328838, 584.515489704279, 707.935238838811)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(28.6012344108779, 61.336529382397, 39.1052596798686, -104.170268830523, -138.605399233107, 52.0339531527216, -85.3086245836394, -122.615513790704, -162.854029728397, 27.5318982889803, 15.0815633701018, 40.9965627673064, 24.1446056467889, 33.17468159184, 46.4218475661003, 40.5743308312437, -3.7639820287618, -1.41871817278309, 37.6242198456229, 76.483203904153, 153.21677762916, 24.7514275726382, 174.991152481163, -36.5886143784594, -32.8777497881891, -30.2900844918579, -35.6483399461421, -50.3361467137764, 
--34.546750671162, -35.9845102957208, 5.93523883881096)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(28.6012344108779, 61.336529382397, 39.1052596798686, 104.170268830523, 138.605399233107, 52.0339531527216, 85.3086245836394, 122.615513790704, 162.854029728397, 27.5318982889803, 15.0815633701018, 40.9965627673064, 24.1446056467889, 33.17468159184, 46.4218475661003, 40.5743308312437, 3.7639820287618, 1.41871817278309, 37.6242198456229, 76.483203904153, 153.21677762916, 24.7514275726382, 174.991152481163, 36.5886143784594, 32.8777497881891, 30.2900844918579, 35.6483399461421, 50.3361467137764, 34.546750671162, 
-35.9845102957208, 5.93523883881096)</t>
+}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2349,6 +2330,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2630,11 +2620,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:CL9"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="42" max="42" width="58.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2902,84 +2895,85 @@
       <c r="CK1" t="s">
         <v>88</v>
       </c>
+      <c r="CL1" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2"/>
-      <c r="B2" t="s">
-        <v>89</v>
+    <row r="2" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>90</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="F2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="H2">
+        <v>1152</v>
+      </c>
+      <c r="I2">
         <v>0.1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.886847980340545</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13.032398577572</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.941983811633431</v>
-      </c>
-      <c r="L2" t="b">
+      <c r="J2">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="K2">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="L2">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="M2" t="b">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="N2" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="P2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.886847980340545</v>
-      </c>
-      <c r="R2" t="n">
-        <v>13.032398577572</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.941983811633431</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.0197140583302016</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.49802188736545</v>
-      </c>
-      <c r="V2"/>
-      <c r="W2" t="n">
-        <v>-578.984549673842</v>
-      </c>
-      <c r="X2" t="n">
-        <v>17.4024441183606</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3.20263363207431</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.340004807835203</v>
-      </c>
-      <c r="AA2" t="e">
-        <v>#NUM!</v>
+      <c r="N2">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="O2">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="P2">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="S2">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="T2">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="U2">
+        <v>0.16527049029912699</v>
+      </c>
+      <c r="V2">
+        <v>6.7146937504072799</v>
+      </c>
+      <c r="X2">
+        <v>-523.72658474291404</v>
+      </c>
+      <c r="Y2">
+        <v>19.6561286472419</v>
+      </c>
+      <c r="Z2">
+        <v>3.5094676140463998</v>
+      </c>
+      <c r="AA2">
+        <v>-0.16772005526266701</v>
       </c>
       <c r="AB2" t="e">
         <v>#NUM!</v>
@@ -2987,234 +2981,211 @@
       <c r="AC2" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD2" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AE2" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AF2"/>
-      <c r="AG2" t="n">
-        <v>-696.232085077385</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21.8199217333388</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3.10825399247241</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-0.181930923025759</v>
-      </c>
-      <c r="AK2"/>
-      <c r="AL2"/>
-      <c r="AM2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN2"/>
-      <c r="AO2" t="s">
+      <c r="AD2">
+        <v>0.94733201371943399</v>
+      </c>
+      <c r="AE2">
+        <v>0.94792373972235799</v>
+      </c>
+      <c r="AF2">
+        <v>8.1716749422302506</v>
+      </c>
+      <c r="AG2">
+        <v>7.2602179508498201</v>
+      </c>
+      <c r="AH2">
+        <v>-792.42114620335803</v>
+      </c>
+      <c r="AI2">
+        <v>19.6561286472419</v>
+      </c>
+      <c r="AJ2">
+        <v>2.9680058443498001</v>
+      </c>
+      <c r="AN2" t="s">
         <v>93</v>
       </c>
-      <c r="AP2"/>
-      <c r="AQ2" t="s">
+      <c r="AP2" t="s">
         <v>94</v>
       </c>
-      <c r="AR2"/>
-      <c r="AS2" t="s">
+      <c r="AR2" t="s">
         <v>95</v>
       </c>
-      <c r="AT2"/>
-      <c r="AU2" t="s">
-        <v>95</v>
+      <c r="AT2" t="s">
+        <v>96</v>
       </c>
       <c r="AV2" t="s">
         <v>96</v>
       </c>
       <c r="AW2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ2">
+        <v>19</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB2">
+        <v>38</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE2" t="s">
         <v>95</v>
       </c>
-      <c r="AX2"/>
-      <c r="AY2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-696.232085077385</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>21.8199217333388</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.10825399247241</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>-0.181930923025759</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>-0.181930923025759</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>179.044493869984</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>100</v>
+      <c r="BF2">
+        <v>-792.42114620335803</v>
+      </c>
+      <c r="BG2">
+        <v>19.6561286472419</v>
+      </c>
+      <c r="BH2">
+        <v>2.9680058443498001</v>
+      </c>
+      <c r="BK2">
+        <v>197.18043274401001</v>
       </c>
       <c r="BL2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>-696.232085077385</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>21.8199217333388</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.10825399247241</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-0.181930923025759</v>
-      </c>
-      <c r="BQ2"/>
-      <c r="BR2"/>
-      <c r="BS2" t="n">
-        <v>875.276578947368</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>179.044493869984</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN2">
+        <v>-632.55944419763898</v>
+      </c>
+      <c r="BO2">
+        <v>17.453646855525299</v>
+      </c>
+      <c r="BP2">
+        <v>3.2013877327939699</v>
+      </c>
+      <c r="BQ2">
+        <v>-0.134158727071815</v>
+      </c>
+      <c r="BT2">
+        <v>989.60157894736801</v>
+      </c>
+      <c r="BU2">
+        <v>357.04213474973</v>
       </c>
       <c r="BV2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BW2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BX2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.414712651360894</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.093447395609349</v>
-      </c>
-      <c r="CA2"/>
-      <c r="CB2" t="n">
-        <v>179.044493869984</v>
-      </c>
-      <c r="CC2"/>
-      <c r="CD2"/>
-      <c r="CE2" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BZ2">
+        <v>0.41471265136089402</v>
+      </c>
+      <c r="CA2">
+        <v>9.3447395609349004E-2</v>
+      </c>
+      <c r="CC2">
+        <v>197.18043274401001</v>
+      </c>
+      <c r="CD2">
+        <v>0.97646206530456303</v>
+      </c>
+      <c r="CF2">
         <v>1</v>
       </c>
-      <c r="CF2" t="n">
-        <v>314.316335004526</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>11.1259368388956</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0.158472096168607</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0.123937542903003</v>
-      </c>
-      <c r="CJ2"/>
-      <c r="CK2"/>
+      <c r="CG2">
+        <v>379.99149295325202</v>
+      </c>
+      <c r="CI2">
+        <v>0.76574257821147196</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3"/>
-      <c r="B3" t="s">
-        <v>89</v>
+    <row r="3" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>90</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="F3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="H3">
+        <v>1200</v>
+      </c>
+      <c r="I3">
         <v>0.1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.886847980340545</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13.032398577572</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.941983811633431</v>
-      </c>
-      <c r="L3" t="b">
+      <c r="J3">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="K3">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="L3">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="M3" t="b">
         <v>1</v>
       </c>
-      <c r="M3" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="N3" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="P3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.886847980340545</v>
-      </c>
-      <c r="R3" t="n">
-        <v>13.032398577572</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.941983811633431</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.0197140583302016</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.49802188736545</v>
-      </c>
-      <c r="V3"/>
-      <c r="W3" t="n">
-        <v>-578.984549673842</v>
-      </c>
-      <c r="X3" t="n">
-        <v>17.4024441183606</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.20263363207431</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-0.340004807835203</v>
-      </c>
-      <c r="AA3" t="e">
-        <v>#NUM!</v>
+      <c r="N3">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="O3">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="P3">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="S3">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="T3">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="U3">
+        <v>0.16527049029912699</v>
+      </c>
+      <c r="V3">
+        <v>6.7146937504072799</v>
+      </c>
+      <c r="X3">
+        <v>-523.72658474291404</v>
+      </c>
+      <c r="Y3">
+        <v>19.6561286472419</v>
+      </c>
+      <c r="Z3">
+        <v>3.5094676140463998</v>
+      </c>
+      <c r="AA3">
+        <v>-0.16772005526266701</v>
       </c>
       <c r="AB3" t="e">
         <v>#NUM!</v>
@@ -3222,231 +3193,202 @@
       <c r="AC3" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD3" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AE3" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AF3"/>
-      <c r="AG3" t="n">
-        <v>-696.232085077385</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>21.8199217333388</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>3.10825399247241</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.181930923025759</v>
-      </c>
-      <c r="AK3"/>
-      <c r="AL3"/>
-      <c r="AM3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN3"/>
-      <c r="AO3" t="s">
+      <c r="AD3">
+        <v>0.71360424487835705</v>
+      </c>
+      <c r="AE3">
+        <v>0.68906754069799803</v>
+      </c>
+      <c r="AF3">
+        <v>17.667685911238099</v>
+      </c>
+      <c r="AG3">
+        <v>18.8912907744356</v>
+      </c>
+      <c r="AH3">
+        <v>-255.03202328246999</v>
+      </c>
+      <c r="AJ3">
+        <v>4.050929383743</v>
+      </c>
+      <c r="AK3">
+        <v>-0.16772005526266701</v>
+      </c>
+      <c r="AN3" t="s">
         <v>93</v>
       </c>
-      <c r="AP3"/>
-      <c r="AQ3" t="s">
-        <v>104</v>
-      </c>
-      <c r="AR3"/>
-      <c r="AS3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AT3"/>
-      <c r="AU3" t="s">
-        <v>95</v>
+      <c r="AP3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>96</v>
       </c>
       <c r="AV3" t="s">
         <v>96</v>
       </c>
       <c r="AW3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AX3"/>
-      <c r="AY3" t="n">
+        <v>97</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AZ3">
+        <v>19</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB3">
         <v>38</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>98</v>
-      </c>
       <c r="BC3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BF3">
+        <v>-255.03202328246999</v>
+      </c>
+      <c r="BH3">
+        <v>4.050929383743</v>
+      </c>
+      <c r="BI3">
+        <v>-0.16772005526266701</v>
+      </c>
+      <c r="BJ3">
+        <v>-0.16772005526266701</v>
+      </c>
+      <c r="BK3">
+        <v>505.91955566489901</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>102</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN3">
+        <v>-632.55944419763898</v>
+      </c>
+      <c r="BO3">
+        <v>17.453646855525299</v>
+      </c>
+      <c r="BP3">
+        <v>3.2013877327939699</v>
+      </c>
+      <c r="BQ3">
+        <v>-0.134158727071815</v>
+      </c>
+      <c r="BT3">
+        <v>760.95157894736803</v>
+      </c>
+      <c r="BU3">
+        <v>128.39213474972999</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>103</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>103</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BY3" t="s">
         <v>105</v>
       </c>
-      <c r="BD3" t="s">
-        <v>104</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-696.232085077385</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>21.8199217333388</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3.10825399247241</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>-0.181930923025759</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>-0.181930923025759</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>179.044493869984</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>95</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>-676.856805042085</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>20.4694886716185</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.1418397722591</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>-0.167811484374966</v>
-      </c>
-      <c r="BQ3"/>
-      <c r="BR3"/>
-      <c r="BS3" t="n">
-        <v>875.276578947368</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>198.419773905283</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>107</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>107</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>108</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>109</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0.414712651360894</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.093447395609349</v>
-      </c>
-      <c r="CA3"/>
-      <c r="CB3" t="n">
-        <v>179.044493869984</v>
-      </c>
-      <c r="CC3"/>
-      <c r="CD3"/>
-      <c r="CE3" t="n">
+      <c r="BZ3">
+        <v>0.41471265136089402</v>
+      </c>
+      <c r="CA3">
+        <v>9.3447395609349004E-2</v>
+      </c>
+      <c r="CC3">
+        <v>505.91955566489901</v>
+      </c>
+      <c r="CD3">
+        <v>0.89213840114508702</v>
+      </c>
+      <c r="CF3">
         <v>1</v>
       </c>
-      <c r="CF3" t="n">
-        <v>314.316335004526</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>11.1259368388956</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>0.158472096168607</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>0.123937542903003</v>
-      </c>
-      <c r="CJ3"/>
-      <c r="CK3"/>
+      <c r="CG3">
+        <v>379.99149295325202</v>
+      </c>
+      <c r="CI3">
+        <v>0.76574257821147196</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4"/>
-      <c r="B4" t="s">
-        <v>89</v>
+    <row r="4" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>5</v>
       </c>
       <c r="C4" t="s">
         <v>90</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" t="s">
         <v>91</v>
       </c>
-      <c r="F4" t="n">
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>4997</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="F4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1200</v>
+      </c>
+      <c r="I4">
         <v>0.1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="N4" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="R4" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.0401735871330047</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.02061254220075</v>
-      </c>
-      <c r="V4"/>
-      <c r="W4" t="n">
-        <v>-833.899568899317</v>
-      </c>
-      <c r="X4" t="n">
-        <v>61.0018759126625</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.15673539413435</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-0.197734830277901</v>
+      <c r="J4">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="K4">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="L4">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>-0.32876631361057901</v>
+      </c>
+      <c r="S4">
+        <v>33.3423292157213</v>
+      </c>
+      <c r="T4">
+        <v>0.51638466339185196</v>
+      </c>
+      <c r="U4">
+        <v>1.4835698757575999</v>
+      </c>
+      <c r="V4">
+        <v>25.4042002747867</v>
+      </c>
+      <c r="X4">
+        <v>-5.3947368421052602</v>
+      </c>
+      <c r="Y4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z4">
+        <v>0.38700647742010602</v>
       </c>
       <c r="AA4" t="e">
         <v>#NUM!</v>
@@ -3457,231 +3399,166 @@
       <c r="AC4" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD4" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AE4" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AF4"/>
-      <c r="AG4" t="n">
-        <v>-832.162155361418</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>60.5626490457522</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>3.1176223782857</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-0.175405650685892</v>
-      </c>
-      <c r="AK4"/>
-      <c r="AL4"/>
-      <c r="AM4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN4"/>
-      <c r="AO4" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP4"/>
-      <c r="AQ4" t="s">
-        <v>111</v>
-      </c>
-      <c r="AR4"/>
-      <c r="AS4" t="s">
+      <c r="AD4">
+        <v>-2.26270276997167</v>
+      </c>
+      <c r="AE4">
+        <v>-3.4656198325313099</v>
+      </c>
+      <c r="AF4">
+        <v>64.317104056111205</v>
+      </c>
+      <c r="AG4">
+        <v>67.231165148396002</v>
+      </c>
+      <c r="AH4">
+        <v>-5.3947368421052602</v>
+      </c>
+      <c r="AJ4">
+        <v>0.226921743803353</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR4" t="s">
         <v>95</v>
       </c>
-      <c r="AT4"/>
-      <c r="AU4" t="s">
-        <v>95</v>
+      <c r="AT4" t="s">
+        <v>96</v>
       </c>
       <c r="AV4" t="s">
         <v>96</v>
       </c>
       <c r="AW4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AZ4">
+        <v>19</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB4">
+        <v>38</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE4" t="s">
         <v>95</v>
       </c>
-      <c r="AX4"/>
-      <c r="AY4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD4" t="s">
+      <c r="BF4">
+        <v>-5.3947368421052602</v>
+      </c>
+      <c r="BH4">
+        <v>0.226921743803353</v>
+      </c>
+      <c r="BK4">
+        <v>1144.6052617179</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>110</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BV4" t="s">
         <v>111</v>
       </c>
-      <c r="BE4" t="n">
-        <v>-832.162155361418</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>60.5626490457522</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.1176223782857</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>-0.175405650685892</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>-0.175405650685892</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>43.1144235859508</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>112</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>95</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>-832.185863737071</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>60.5675855232738</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.1176223782857</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>-0.175405650685892</v>
-      </c>
-      <c r="BQ4"/>
-      <c r="BR4"/>
-      <c r="BS4" t="n">
-        <v>875.276578947368</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>43.090715210297</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>113</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>113</v>
-      </c>
       <c r="BW4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="BX4" t="s">
-        <v>115</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.42337515535142</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.093447395609349</v>
-      </c>
-      <c r="CA4"/>
-      <c r="CB4" t="n">
-        <v>43.1144235859508</v>
-      </c>
-      <c r="CC4"/>
-      <c r="CD4"/>
-      <c r="CE4" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>111</v>
+      </c>
+      <c r="CC4">
+        <v>1144.6052617179</v>
+      </c>
+      <c r="CD4">
+        <v>3.8000458482671598E-2</v>
+      </c>
+      <c r="CF4">
         <v>1</v>
       </c>
-      <c r="CF4" t="n">
-        <v>157.688596920877</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>1.57384509643995</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>0.0862305896077315</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>0.240551227381187</v>
-      </c>
-      <c r="CJ4"/>
-      <c r="CK4"/>
+      <c r="CI4">
+        <v>0.22639400140969701</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5"/>
-      <c r="B5" t="s">
-        <v>89</v>
+    <row r="5" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>90</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4999</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="H5">
+        <v>1200</v>
+      </c>
+      <c r="I5">
         <v>0.1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="J5" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="R5" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.0401735871330047</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.02061254220075</v>
-      </c>
-      <c r="V5"/>
-      <c r="W5" t="n">
-        <v>-833.899568899317</v>
-      </c>
-      <c r="X5" t="n">
-        <v>61.0018759126625</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.15673539413435</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.197734830277901</v>
+      <c r="J5">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="K5">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="L5">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>-0.32876631361057901</v>
+      </c>
+      <c r="S5">
+        <v>33.3423292157213</v>
+      </c>
+      <c r="T5">
+        <v>0.51638466339185196</v>
+      </c>
+      <c r="U5">
+        <v>1.4835698757575999</v>
+      </c>
+      <c r="V5">
+        <v>25.4042002747867</v>
+      </c>
+      <c r="X5">
+        <v>-5.3947368421052602</v>
+      </c>
+      <c r="Y5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z5">
+        <v>0.38700647742010602</v>
       </c>
       <c r="AA5" t="e">
         <v>#NUM!</v>
@@ -3692,234 +3569,172 @@
       <c r="AC5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AF5"/>
-      <c r="AG5" t="n">
-        <v>-832.185863737071</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>60.5651166904523</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3.1176223782857</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.175405650685892</v>
-      </c>
-      <c r="AK5"/>
-      <c r="AL5"/>
-      <c r="AM5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN5"/>
-      <c r="AO5" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP5"/>
-      <c r="AQ5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AR5"/>
-      <c r="AS5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AT5"/>
-      <c r="AU5" t="s">
-        <v>95</v>
+      <c r="AD5">
+        <v>-0.71329874306843799</v>
+      </c>
+      <c r="AE5">
+        <v>-0.125157203050455</v>
+      </c>
+      <c r="AF5">
+        <v>43.212851953305602</v>
+      </c>
+      <c r="AG5">
+        <v>35.936452588578</v>
+      </c>
+      <c r="AJ5">
+        <v>0.54709121103685998</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>96</v>
       </c>
       <c r="AV5" t="s">
         <v>96</v>
       </c>
       <c r="AW5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AX5"/>
-      <c r="AY5" t="n">
+        <v>97</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>107</v>
+      </c>
+      <c r="AZ5">
+        <v>19</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB5">
         <v>38</v>
       </c>
-      <c r="AZ5" t="s">
-        <v>97</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>98</v>
-      </c>
       <c r="BC5" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="BD5" t="s">
-        <v>116</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-832.185863737071</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>60.5651166904523</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.1176223782857</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>-0.175405650685892</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>-0.175405650685892</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>43.090715210297</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>112</v>
+        <v>101</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH5">
+        <v>0.54709121103685998</v>
+      </c>
+      <c r="BK5">
+        <v>622.50001052983896</v>
       </c>
       <c r="BL5" t="s">
-        <v>95</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>-832.185863737071</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>60.5675855232738</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.1176223782857</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-0.175405650685892</v>
-      </c>
-      <c r="BQ5"/>
-      <c r="BR5"/>
-      <c r="BS5" t="n">
-        <v>875.276578947368</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>43.090715210297</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>113</v>
+        <v>110</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>96</v>
       </c>
       <c r="BV5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BW5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="BX5" t="s">
-        <v>115</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.42337515535142</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.093447395609349</v>
-      </c>
-      <c r="CA5"/>
-      <c r="CB5" t="n">
-        <v>43.090715210297</v>
-      </c>
-      <c r="CC5"/>
-      <c r="CD5"/>
-      <c r="CE5" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>111</v>
+      </c>
+      <c r="CC5">
+        <v>622.50001052983896</v>
+      </c>
+      <c r="CD5">
+        <v>0.15893772863508801</v>
+      </c>
+      <c r="CF5">
         <v>1</v>
       </c>
-      <c r="CF5" t="n">
-        <v>157.688596920877</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>1.57384509643995</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0.0862305896077315</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>0.240551227381187</v>
-      </c>
-      <c r="CJ5"/>
-      <c r="CK5"/>
+      <c r="CI5">
+        <v>0.22639400140969701</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6"/>
-      <c r="B6" t="s">
-        <v>89</v>
+    <row r="6" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>
       </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" t="s">
         <v>91</v>
       </c>
-      <c r="F6" t="n">
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="H6">
+        <v>1200</v>
+      </c>
+      <c r="I6">
         <v>0.1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.905510996893924</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11.1364153795657</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.95112780313445</v>
-      </c>
-      <c r="L6" t="b">
+      <c r="J6">
+        <v>8.8030112637406302E-2</v>
+      </c>
+      <c r="K6">
+        <v>25.4024968592257</v>
+      </c>
+      <c r="L6">
+        <v>0.66632748962552601</v>
+      </c>
+      <c r="M6" t="b">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="N6" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="P6" t="b">
+      <c r="N6">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="O6">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="P6">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="Q6" t="b">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.905510996893924</v>
-      </c>
-      <c r="R6" t="n">
-        <v>11.1364153795657</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.95112780313445</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.0595018696511139</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.50009551668511</v>
-      </c>
-      <c r="V6"/>
-      <c r="W6" t="n">
-        <v>-434.731793095423</v>
-      </c>
-      <c r="X6" t="n">
-        <v>39.2060239785636</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.05653609121004</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.000277409337397985</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-106.261594212221</v>
+      <c r="R6">
+        <v>8.8030112637406302E-2</v>
+      </c>
+      <c r="S6">
+        <v>25.4024968592257</v>
+      </c>
+      <c r="T6">
+        <v>0.66632748962552601</v>
+      </c>
+      <c r="U6">
+        <v>1.31843724885147</v>
+      </c>
+      <c r="V6">
+        <v>23.306390527962101</v>
+      </c>
+      <c r="X6">
+        <v>-414.09257240753101</v>
+      </c>
+      <c r="Y6">
+        <v>-0.53342845613260004</v>
+      </c>
+      <c r="Z6">
+        <v>3.1338786203963802</v>
+      </c>
+      <c r="AA6">
+        <v>-0.31477599844463899</v>
       </c>
       <c r="AB6" t="e">
         <v>#NUM!</v>
@@ -3927,236 +3742,220 @@
       <c r="AC6" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AF6"/>
-      <c r="AG6" t="n">
-        <v>-309.342543756606</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>57.3068462799672</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.83152518379771</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.000343432315436051</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-116.018938752221</v>
-      </c>
-      <c r="AL6"/>
-      <c r="AM6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AN6"/>
-      <c r="AO6" t="s">
-        <v>119</v>
-      </c>
-      <c r="AP6"/>
-      <c r="AQ6" t="s">
-        <v>120</v>
-      </c>
-      <c r="AR6"/>
-      <c r="AS6" t="s">
-        <v>121</v>
-      </c>
-      <c r="AT6"/>
-      <c r="AU6" t="s">
-        <v>95</v>
+      <c r="AD6">
+        <v>0.87795354887985599</v>
+      </c>
+      <c r="AE6">
+        <v>0.85935627531769898</v>
+      </c>
+      <c r="AF6">
+        <v>12.938075052234</v>
+      </c>
+      <c r="AG6">
+        <v>13.0422455412196</v>
+      </c>
+      <c r="AH6">
+        <v>-446.310415879365</v>
+      </c>
+      <c r="AJ6">
+        <v>3.3324585662639401</v>
+      </c>
+      <c r="AK6">
+        <v>-0.26185669279599599</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>96</v>
       </c>
       <c r="AV6" t="s">
         <v>96</v>
       </c>
       <c r="AW6" t="s">
-        <v>121</v>
-      </c>
-      <c r="AX6"/>
-      <c r="AY6" t="n">
-        <v>31</v>
-      </c>
-      <c r="AZ6" t="s">
         <v>97</v>
       </c>
-      <c r="BA6" t="n">
-        <v>31</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>98</v>
+      <c r="AX6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AZ6">
+        <v>19</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB6">
+        <v>38</v>
       </c>
       <c r="BC6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BD6" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-309.342543756606</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>57.3068462799672</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.83152518379771</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0.000343432315436051</v>
-      </c>
-      <c r="BI6"/>
-      <c r="BJ6" t="n">
-        <v>644.093262695007</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>122</v>
+        <v>101</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>113</v>
+      </c>
+      <c r="BF6">
+        <v>-446.310415879365</v>
+      </c>
+      <c r="BG6">
+        <v>0.27412985470394202</v>
+      </c>
+      <c r="BH6">
+        <v>3.3324585662639401</v>
+      </c>
+      <c r="BI6">
+        <v>-0.26185669279599599</v>
+      </c>
+      <c r="BJ6">
+        <v>-0.26185669279599599</v>
+      </c>
+      <c r="BK6">
+        <v>471.61326833116101</v>
       </c>
       <c r="BL6" t="s">
-        <v>121</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>-282.151839791794</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>54.7906389860756</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>2.86253947848178</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0.000288762090617214</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>-116.500812140052</v>
-      </c>
-      <c r="BR6"/>
-      <c r="BS6" t="n">
-        <v>953.435806451613</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>671.283966659819</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>123</v>
+        <v>115</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN6">
+        <v>-467.71300486298702</v>
+      </c>
+      <c r="BO6">
+        <v>-1.0053923475541</v>
+      </c>
+      <c r="BP6">
+        <v>3.1465960102752799</v>
+      </c>
+      <c r="BQ6">
+        <v>-0.17542257842859901</v>
+      </c>
+      <c r="BT6">
+        <v>917.92368421052595</v>
+      </c>
+      <c r="BU6">
+        <v>450.21067934753898</v>
       </c>
       <c r="BV6" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="BW6" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="BX6" t="s">
-        <v>125</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.394499545773217</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.375807717611359</v>
-      </c>
-      <c r="CA6"/>
-      <c r="CB6" t="n">
-        <v>644.093262695007</v>
-      </c>
-      <c r="CC6"/>
-      <c r="CD6"/>
-      <c r="CE6" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BZ6">
+        <v>0.41471265136089402</v>
+      </c>
+      <c r="CA6">
+        <v>9.3447395609349004E-2</v>
+      </c>
+      <c r="CC6">
+        <v>471.61326833116101</v>
+      </c>
+      <c r="CD6">
+        <v>0.94665820375000398</v>
+      </c>
+      <c r="CF6">
         <v>1</v>
       </c>
-      <c r="CF6"/>
-      <c r="CG6" t="n">
-        <v>40.1061693979523</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>0.473567406359439</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>0.000130449546441295</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>6.87529293487546</v>
-      </c>
-      <c r="CK6"/>
+      <c r="CG6">
+        <v>45.562911188282001</v>
+      </c>
+      <c r="CI6">
+        <v>0.28083445266121698</v>
+      </c>
+      <c r="CJ6">
+        <v>7.4839199759677594E-2</v>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7"/>
-      <c r="B7" t="s">
-        <v>89</v>
+    <row r="7" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>10</v>
       </c>
       <c r="C7" t="s">
         <v>90</v>
       </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" t="s">
         <v>91</v>
       </c>
-      <c r="F7" t="n">
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="F7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>1200</v>
+      </c>
+      <c r="I7">
         <v>0.1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.905510996893924</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11.1364153795657</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.95112780313445</v>
-      </c>
-      <c r="L7" t="b">
+      <c r="J7">
+        <v>8.8030112637406302E-2</v>
+      </c>
+      <c r="K7">
+        <v>25.4024968592257</v>
+      </c>
+      <c r="L7">
+        <v>0.66632748962552601</v>
+      </c>
+      <c r="M7" t="b">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0.92021239833307</v>
-      </c>
-      <c r="N7" t="n">
-        <v>10.7374768324468</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.959343725314109</v>
-      </c>
-      <c r="P7" t="b">
+      <c r="N7">
+        <v>0.83046812929889602</v>
+      </c>
+      <c r="O7">
+        <v>12.9196804267342</v>
+      </c>
+      <c r="P7">
+        <v>0.93430023322482503</v>
+      </c>
+      <c r="Q7" t="b">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0.905510996893924</v>
-      </c>
-      <c r="R7" t="n">
-        <v>11.1364153795657</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.95112780313445</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.0595018696511139</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.50009551668511</v>
-      </c>
-      <c r="V7"/>
-      <c r="W7" t="n">
-        <v>-434.731793095423</v>
-      </c>
-      <c r="X7" t="n">
-        <v>39.2060239785636</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3.05653609121004</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.000277409337397985</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-106.261594212221</v>
+      <c r="R7">
+        <v>8.8030112637406302E-2</v>
+      </c>
+      <c r="S7">
+        <v>25.4024968592257</v>
+      </c>
+      <c r="T7">
+        <v>0.66632748962552601</v>
+      </c>
+      <c r="U7">
+        <v>1.31843724885147</v>
+      </c>
+      <c r="V7">
+        <v>23.306390527962101</v>
+      </c>
+      <c r="X7">
+        <v>-414.09257240753101</v>
+      </c>
+      <c r="Y7">
+        <v>-0.53342845613260004</v>
+      </c>
+      <c r="Z7">
+        <v>3.1338786203963802</v>
+      </c>
+      <c r="AA7">
+        <v>-0.31477599844463899</v>
       </c>
       <c r="AB7" t="e">
         <v>#NUM!</v>
@@ -4164,161 +3963,478 @@
       <c r="AC7" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AF7"/>
-      <c r="AG7" t="n">
-        <v>-309.342543756606</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>57.3068462799672</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.83152518379771</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.000343432315436051</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-116.018938752221</v>
-      </c>
-      <c r="AL7"/>
-      <c r="AM7" t="s">
-        <v>118</v>
-      </c>
-      <c r="AN7"/>
-      <c r="AO7" t="s">
+      <c r="AD7">
+        <v>0.96529238138689599</v>
+      </c>
+      <c r="AE7">
+        <v>0.98371504468860904</v>
+      </c>
+      <c r="AF7">
+        <v>6.1075892402352903</v>
+      </c>
+      <c r="AG7">
+        <v>3.8593654361033298</v>
+      </c>
+      <c r="AH7">
+        <v>-381.874728935696</v>
+      </c>
+      <c r="AI7">
+        <v>-0.53342845613260004</v>
+      </c>
+      <c r="AJ7">
+        <v>2.9352986745288199</v>
+      </c>
+      <c r="AK7">
+        <v>-0.36769530409328099</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR7" t="s">
         <v>119</v>
       </c>
-      <c r="AP7"/>
-      <c r="AQ7" t="s">
-        <v>126</v>
-      </c>
-      <c r="AR7"/>
-      <c r="AS7" t="s">
-        <v>121</v>
-      </c>
-      <c r="AT7"/>
-      <c r="AU7" t="s">
-        <v>95</v>
+      <c r="AT7" t="s">
+        <v>96</v>
       </c>
       <c r="AV7" t="s">
         <v>96</v>
       </c>
       <c r="AW7" t="s">
-        <v>121</v>
-      </c>
-      <c r="AX7"/>
-      <c r="AY7" t="n">
-        <v>31</v>
-      </c>
-      <c r="AZ7" t="s">
         <v>97</v>
       </c>
-      <c r="BA7" t="n">
-        <v>31</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>98</v>
+      <c r="AX7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ7">
+        <v>19</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB7">
+        <v>38</v>
       </c>
       <c r="BC7" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="BD7" t="s">
-        <v>126</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-309.342543756606</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>57.3068462799672</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.83152518379771</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0.000343432315436051</v>
-      </c>
-      <c r="BI7"/>
-      <c r="BJ7" t="n">
-        <v>644.093262695007</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>128</v>
+        <v>101</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BF7">
+        <v>-381.874728935696</v>
+      </c>
+      <c r="BG7">
+        <v>-0.53342845613260004</v>
+      </c>
+      <c r="BH7">
+        <v>2.9352986745288199</v>
+      </c>
+      <c r="BI7">
+        <v>-0.36769530409328099</v>
+      </c>
+      <c r="BJ7">
+        <v>-0.36769530409328099</v>
+      </c>
+      <c r="BK7">
+        <v>450.75474474851399</v>
       </c>
       <c r="BL7" t="s">
         <v>121</v>
       </c>
-      <c r="BM7" t="n">
-        <v>-309.342543756606</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>57.3068462799672</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>2.83152518379771</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.000343432315436051</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-116.018938752221</v>
-      </c>
-      <c r="BR7"/>
-      <c r="BS7" t="n">
-        <v>953.435806451613</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>644.093262695007</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>129</v>
+      <c r="BM7" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN7">
+        <v>-468.16076000047798</v>
+      </c>
+      <c r="BO7">
+        <v>-0.962715116962511</v>
+      </c>
+      <c r="BP7">
+        <v>3.1465960102752799</v>
+      </c>
+      <c r="BQ7">
+        <v>-0.17542257842859901</v>
+      </c>
+      <c r="BT7">
+        <v>832.62947368420998</v>
+      </c>
+      <c r="BU7">
+        <v>364.46871368373201</v>
       </c>
       <c r="BV7" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="BW7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="BX7" t="s">
-        <v>131</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0.394499545773217</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0.375807717611359</v>
-      </c>
-      <c r="CA7"/>
-      <c r="CB7" t="n">
-        <v>644.093262695007</v>
-      </c>
-      <c r="CC7"/>
-      <c r="CD7"/>
-      <c r="CE7" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>124</v>
+      </c>
+      <c r="BZ7">
+        <v>0.41471265136089402</v>
+      </c>
+      <c r="CA7">
+        <v>9.3447395609349004E-2</v>
+      </c>
+      <c r="CC7">
+        <v>450.75474474851399</v>
+      </c>
+      <c r="CD7">
+        <v>0.98576808043574504</v>
+      </c>
+      <c r="CF7">
         <v>1</v>
       </c>
-      <c r="CF7"/>
-      <c r="CG7" t="n">
-        <v>40.1061693979523</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0.473567406359439</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>0.000130449546441295</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>6.87529293487546</v>
-      </c>
-      <c r="CK7"/>
+      <c r="CG7">
+        <v>45.562911188282001</v>
+      </c>
+      <c r="CI7">
+        <v>0.28083445266121698</v>
+      </c>
+      <c r="CJ7">
+        <v>7.4839199759677594E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1200</v>
+      </c>
+      <c r="I8">
+        <v>0.1</v>
+      </c>
+      <c r="J8">
+        <v>8.8030112637406302E-2</v>
+      </c>
+      <c r="K8">
+        <v>25.4024968592257</v>
+      </c>
+      <c r="L8">
+        <v>0.66632748962552601</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>-1.7815675368989599E-2</v>
+      </c>
+      <c r="S8">
+        <v>29.0832082521861</v>
+      </c>
+      <c r="T8">
+        <v>0.542480931051604</v>
+      </c>
+      <c r="U8">
+        <v>1.1344976742402499</v>
+      </c>
+      <c r="V8">
+        <v>20.843271848838899</v>
+      </c>
+      <c r="X8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z8">
+        <v>0.44800244214162699</v>
+      </c>
+      <c r="AA8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AB8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AC8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD8">
+        <v>-0.178300541681365</v>
+      </c>
+      <c r="AE8">
+        <v>-7.2032065209952603E-2</v>
+      </c>
+      <c r="AF8">
+        <v>40.200839928858002</v>
+      </c>
+      <c r="AG8">
+        <v>36.007757935167298</v>
+      </c>
+      <c r="AJ8">
+        <v>0.38367692581450202</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AZ8">
+        <v>19</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB8">
+        <v>38</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>113</v>
+      </c>
+      <c r="BH8">
+        <v>0.38367692581450202</v>
+      </c>
+      <c r="BK8">
+        <v>713.99998640545095</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>96</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>111</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>111</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>111</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>111</v>
+      </c>
+      <c r="CC8">
+        <v>713.99998640545095</v>
+      </c>
+      <c r="CD8">
+        <v>0.14307045164062401</v>
+      </c>
+      <c r="CF8">
+        <v>1</v>
+      </c>
+      <c r="CI8">
+        <v>9.0970017596472594E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>1200</v>
+      </c>
+      <c r="I9">
+        <v>0.1</v>
+      </c>
+      <c r="J9">
+        <v>8.8030112637406302E-2</v>
+      </c>
+      <c r="K9">
+        <v>25.4024968592257</v>
+      </c>
+      <c r="L9">
+        <v>0.66632748962552601</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>-1.7815675368989599E-2</v>
+      </c>
+      <c r="S9">
+        <v>29.0832082521861</v>
+      </c>
+      <c r="T9">
+        <v>0.542480931051604</v>
+      </c>
+      <c r="U9">
+        <v>1.1344976742402499</v>
+      </c>
+      <c r="V9">
+        <v>20.843271848838899</v>
+      </c>
+      <c r="X9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z9">
+        <v>0.44800244214162699</v>
+      </c>
+      <c r="AA9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AB9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AC9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD9">
+        <v>-0.49240553709499002</v>
+      </c>
+      <c r="AE9">
+        <v>3.5669308170445398E-2</v>
+      </c>
+      <c r="AF9">
+        <v>40.049844933276802</v>
+      </c>
+      <c r="AG9">
+        <v>29.698575046886901</v>
+      </c>
+      <c r="AJ9">
+        <v>0.51232795846875201</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ9">
+        <v>19</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB9">
+        <v>38</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>119</v>
+      </c>
+      <c r="BH9">
+        <v>0.51232795846875201</v>
+      </c>
+      <c r="BK9">
+        <v>629.50002458808797</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>96</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>111</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>111</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>111</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>111</v>
+      </c>
+      <c r="CC9">
+        <v>629.50002458808797</v>
+      </c>
+      <c r="CD9">
+        <v>0.198812059019052</v>
+      </c>
+      <c r="CF9">
+        <v>1</v>
+      </c>
+      <c r="CI9">
+        <v>9.0970017596472594E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Figures.out/gbr_out_sheep_lon.xlsx
+++ b/Figures.out/gbr_out_sheep_lon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\DMI.prediction\R\Figures.out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCDE331-CD59-4C0A-8637-6B899B9B6099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_B99231273C29E3BD4895A99233DD1C34C21F59DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="124">
   <si>
     <t>matrix.NA..nrow...n.rows..ncol...1.</t>
   </si>
@@ -193,6 +193,9 @@
     <t>k.IDs.length</t>
   </si>
   <si>
+    <t>test.IDs</t>
+  </si>
+  <si>
     <t>gbr.model.train.coef.int</t>
   </si>
   <si>
@@ -298,7 +301,7 @@
     <t>low</t>
   </si>
   <si>
-    <t>1-1-1</t>
+    <t>1-1-1-1</t>
   </si>
   <si>
     <t>c(699.7, 696.5, 1390, 1540, 1521, 1263, 1426, 1345, 1317, 1170, 1150, 1210, 1190, 1150, 595.5, 596.38, 598.88, 589.88, 592.97, 1050, 1183, 1344, 877, 622.5, 604.2, 613, 615.5, 653.5, 629.5, 620.5, 702, 714, 536, 489, 518, 493, 452, 502)</t>
@@ -307,7 +310,7 @@
     <t>feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition</t>
   </si>
   <si>
-    <t>c(211, 190, 208, 164, 196, 195, 118, 203, 180, 209, 210, 198, 108, 163, 182, 165, 213, 194, 205)</t>
+    <t>c(166, 211, 196, 205, 138, 208, 164, 108, 136, 190, 213, 167, 183, 181, 116, 191, 193, 200, 141)</t>
   </si>
   <si>
     <t>c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 208, 209, 210, 211, 212, 213)</t>
@@ -316,7 +319,7 @@
     <t>c(27, 27, 29, 29, 33, 33, 33, 34, 34, 40, 40, 40, 40, 40, 44, 44, 44, 44, 44, 47, 47, 47, 47, 48, 48, 48, 48, 48, 48, 48, 49, 50, 51, 51, 51, 51, 51, 51)</t>
   </si>
   <si>
-    <t>c(107, 116, 134, 136, 138, 141, 142, 166, 167, 181, 183, 184, 191, 192, 193, 197, 199, 200, 212)</t>
+    <t>c(107, 118, 134, 142, 163, 165, 180, 182, 184, 192, 194, 195, 197, 198, 199, 203, 209, 210, 212)</t>
   </si>
   <si>
     <t>Sheep - Low NDF</t>
@@ -325,7 +328,10 @@
     <t>numeric(0)</t>
   </si>
   <si>
-    <t>c(2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 206, 207, 214, 215, 216)</t>
+    <t>c(2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 214, 215, 216)</t>
+  </si>
+  <si>
+    <t>c(108, 116, 136, 138, 141, 164, 166, 167, 181, 183, 190, 191, 193, 196, 200, 205, 208, 211, 213)</t>
   </si>
   <si>
     <t>list(baselearner = list(list(model.frame = function () 
@@ -461,7 +467,7 @@
     X %*% (MPinvS/sxtx)
 })), offset = 875.276578947368, ustart = c(`1376` = -175.576578947368, `1377` = -178.776578947368, `1487` = 514.723421052632, `1490` = 664.723421052632, `1585` = 645.723421052632, `1587` = 387.723421052632, `1589` = 550.723421052632, `1639` = 469.723421052632, `1640` = 441.723421052632, `1770` = 294.723421052632, `1771` = 274.723421052632, `1772` = 334.723421052632, `1773` = 314.723421052632, `1774` = 274.723421052632, `1815` = -279.776578947368, `1816` = -278.896578947368, `1817` = -276.396578947368, 
 `1818` = -285.396578947368, `1819` = -282.306578947368, `1921` = 174.723421052632, `1922` = 307.723421052632, `1923` = 468.723421052632, `1924` = 1.72342105263158, `1945` = -252.776578947368, `1946` = -271.076578947368, `1947` = -262.276578947368, `1948` = -259.776578947368, `1949` = -221.776578947368, `1950` = -245.776578947368, `1951` = -254.776578947368, `1968` = -173.276578947368, `1981` = -161.276578947368, `1984` = -339.276578947368, `1985` = -386.276578947368, `1986` = -357.276578947368, `1987` = -382.276578947368, 
-`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 1200, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
+`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 1100, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
 return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
 y - f, risk = function (y, f, w = 1) 
 sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
@@ -708,28 +714,37 @@
 }, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
   </si>
   <si>
-    <t>c(707.387903197369, 747.269284368318, 1392.34364465428, 1410.15103076313, 1443.02412839264, 1333.73762586257, 1381.50854611726, 1157.05712222907, 1099.73730392678, 1204.80399597263, 1167.20833749162, 1266.37625686965, 1232.28824225727, 1190.91532121986, 616.691698335388, 611.475861394407, 568.840459284907, 568.501613183089, 607.226861030828, 1087.15364912471, 1329.52651012155, 1365.95050495955, 1004.54610534464, 569.222566311438, 594.498332157763, 602.411574724184, 591.596278371552, 615.925763531856, 
-606.064616955656, 592.568028767716, 710.717265651254, 758.989955179538, 556.740153027197, 490.873903139578, 535.239033898342, 594.989247491447, 488.81891177283, 553.145499971653)</t>
-  </si>
-  <si>
-    <t>c(7.68790319736911, 50.7692843683184, 2.34364465427598, -129.848969236873, -77.9758716073634, 70.7376258625673, -44.4914538827372, -187.942877770931, -217.26269607322, 34.8039959726289, 17.2083374916167, 56.3762568696516, 42.2882422572723, 40.9153212198648, 21.1916983353875, 15.0958613944066, -30.0395407150928, -21.3783868169107, 14.2568610308281, 37.1536491247061, 146.526510121551, 21.9505049595498, 127.546105344645, -53.2774336885616, -9.70166784223659, -10.5884252758161, -23.9037216284479, -37.5742364681441, 
--23.435383044344, -27.9319712322839, 8.71726565125391, 44.9899551795377, 20.7401530271975, 1.87390313957786, 17.2390338983423, 101.989247491447, 36.8189117728297, 51.145499971653)</t>
-  </si>
-  <si>
-    <t>c(7.68790319736911, 50.7692843683184, 2.34364465427598, 129.848969236873, 77.9758716073634, 70.7376258625673, 44.4914538827372, 187.942877770931, 217.26269607322, 34.8039959726289, 17.2083374916167, 56.3762568696516, 42.2882422572723, 40.9153212198648, 21.1916983353875, 15.0958613944066, 30.0395407150928, 21.3783868169107, 14.2568610308281, 37.1536491247061, 146.526510121551, 21.9505049595498, 127.546105344645, 53.2774336885616, 9.70166784223659, 10.5884252758161, 23.9037216284479, 37.5742364681441, 
-23.435383044344, 27.9319712322839, 8.71726565125391, 44.9899551795377, 20.7401530271975, 1.87390313957786, 17.2390338983423, 101.989247491447, 36.8189117728297, 51.145499971653)</t>
-  </si>
-  <si>
-    <t>c(200, 134, 138, 199, 197, 166, 116, 167, 212, 193, 136, 191, 142, 181, 107, 192, 183, 141, 184)</t>
-  </si>
-  <si>
-    <t>c(108, 118, 163, 164, 165, 180, 182, 190, 194, 195, 196, 198, 203, 205, 208, 209, 210, 211, 213)</t>
-  </si>
-  <si>
-    <t>2-1-1</t>
-  </si>
-  <si>
-    <t>NA</t>
+    <t>c(710.620997249566, 750.401075611211, 1389.96976803688, 1406.93392311784, 1446.30728649106, 1337.52169848894, 1385.07653796687, 1148.47465226024, 1090.66374128349, 1201.58188402975, 1164.23371059722, 1263.25333281729, 1230.49159918997, 1188.24651938514, 619.10535621307, 614.404331363065, 572.653300144295, 572.478818666772, 609.659097867675, 1084.90379778241, 1326.24958649781, 1362.64567624072, 1000.76266767438, 572.098291864774, 596.654345380954, 604.527318348069, 594.095652561544, 618.345176803266, 
+608.545733529338, 595.109462553002, 712.143532974217, 759.732281657244, 559.29199585301, 493.396280404922, 537.771233017176, 597.29554398003, 491.351110891663, 555.608946116062)</t>
+  </si>
+  <si>
+    <t>c(10.9209972495659, 53.9010756112107, -0.0302319631236969, -133.066076882165, -74.6927135089368, 74.5216984889405, -40.9234620331254, -196.525347739765, -226.336258716511, 31.5818840297479, 14.2337105972219, 53.2533328172908, 40.4915991899652, 38.2465193851417, 23.6053562130701, 18.0243313630654, -26.2266998557051, -17.4011813332282, 16.6890978676745, 34.9037977824119, 143.24958649781, 18.6456762407192, 123.762667674382, -50.4017081352256, -7.54565461904565, -8.47268165193066, -21.4043474384562, 
+-35.1548231967342, -20.9542664706619, -25.3905374469983, 10.1435329742167, 45.7322816572441, 23.2919958530096, 4.39628040492244, 19.771233017176, 104.29554398003, 39.3511108916634, 53.6089461160625)</t>
+  </si>
+  <si>
+    <t>c(10.9209972495659, 53.9010756112107, 0.0302319631236969, 133.066076882165, 74.6927135089368, 74.5216984889405, 40.9234620331254, 196.525347739765, 226.336258716511, 31.5818840297479, 14.2337105972219, 53.2533328172908, 40.4915991899652, 38.2465193851417, 23.6053562130701, 18.0243313630654, 26.2266998557051, 17.4011813332282, 16.6890978676745, 34.9037977824119, 143.24958649781, 18.6456762407192, 123.762667674382, 50.4017081352256, 7.54565461904565, 8.47268165193066, 21.4043474384562, 35.1548231967342, 
+20.9542664706619, 25.3905374469983, 10.1435329742167, 45.7322816572441, 23.2919958530096, 4.39628040492244, 19.771233017176, 104.29554398003, 39.3511108916634, 53.6089461160625)</t>
+  </si>
+  <si>
+    <t>c(199, 198, 192, 182, 212, 134, 203, 184, 165, 197, 163, 118, 195, 210, 180, 142, 194, 107, 209)</t>
+  </si>
+  <si>
+    <t>c(699.7, 696.5, 1390, 1540, 1521, 1263, 1426, 1345, 1317, 1170, 1150, 1210, 1190, 1150, 595.5, 596.38, 598.88, 589.88, 592.97, 1050, 1183, 1344, 877, 622.5, 604.2, 613, 615.5, 653.5, 629.5, 620.5, 702)</t>
+  </si>
+  <si>
+    <t>feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition + CP_nutrition</t>
+  </si>
+  <si>
+    <t>c(190, 136, 195, 134, 116, 108, 183, 118, 141, 203, 107, 182, 163, 180, 200, 184)</t>
+  </si>
+  <si>
+    <t>c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203)</t>
+  </si>
+  <si>
+    <t>c(138, 142, 164, 165, 166, 167, 181, 191, 192, 193, 194, 196, 197, 198, 199)</t>
+  </si>
+  <si>
+    <t>c(107, 108, 116, 118, 134, 136, 141, 163, 180, 182, 183, 184, 190, 195, 200, 203)</t>
   </si>
   <si>
     <t>list(baselearner = list(list(model.frame = function () 
@@ -853,7 +868,7 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, Xnames = c("(Intercept)", "bw_kg", "adg_g_day", "NDF_nutrition"), MPinv = function () 
+}, Xnames = c("(Intercept)", "bw_kg", "adg_g_day", "NDF_nutrition", "CP_nutrition"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
@@ -863,24 +878,25 @@
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-})), offset = 697.910728140674, ustart = c(`1376` = 1, `1377` = -1, `1487` = 1, `1490` = 1, `1585` = 1, `1587` = 1, `1589` = 1, `1639` = 1, `1640` = 1, `1770` = 1, `1771` = 1, `1772` = 1, `1773` = 1, `1774` = 1, `1815` = -1, `1816` = -1, `1817` = -1, `1818` = -1, `1819` = -1, `1921` = 1, `1922` = 1, `1923` = 1, `1924` = 1, `1945` = -1, `1946` = -1, `1947` = -1, `1948` = -1, `1949` = -1, `1950` = -1, `1951` = -1, `1968` = 1, `1981` = 1, `1984` = -1, `1985` = -1, `1986` = -1, `1987` = -1, `1988` = -1, 
-`1989` = -1), control = list(mstop = 1200, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family", ngradient = function (y, f, w = 1) 
-sign(y - f), risk = function (y, f, w = 1) 
-sum(w * loss(y, f), na.rm = TRUE), offset = function (y, w) 
-optimize(risk, interval = range(y), y = y, w = w)$minimum, check_y = function (y) 
-{
-    if (!is.numeric(y) || !is.null(dim(y))) 
-        stop("response is not a numeric vector but ", sQuote("family = Laplace()"))
-    y
-}, weights = function (w) 
-{
-    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
-}, nuisance = function () 
-return(NA), response = function (f) 
-f, rclass = function (f) 
-NA, name = "Absolute Error", charloss = "abs(y - f) \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, `1949` = 653.5, 
-`1950` = 629.5, `1951` = 620.5, `1968` = 702, `1981` = 714, `1984` = 536, `1985` = 489, `1986` = 518, `1987` = 493, `1988` = 452, `1989` = 502), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968", "1981", "1984", "1985", "1986", "1987", "1988", "1989"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 
-1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+})), offset = 953.435806451613, ustart = c(`1376` = -253.735806451613, `1377` = -256.935806451613, `1487` = 436.564193548387, `1490` = 586.564193548387, `1585` = 567.564193548387, `1587` = 309.564193548387, `1589` = 472.564193548387, `1639` = 391.564193548387, `1640` = 363.564193548387, `1770` = 216.564193548387, `1771` = 196.564193548387, `1772` = 256.564193548387, `1773` = 236.564193548387, `1774` = 196.564193548387, `1815` = -357.935806451613, `1816` = -357.055806451613, `1817` = -354.555806451613, 
+`1818` = -363.555806451613, `1819` = -360.465806451613, `1921` = 96.5641935483872, `1922` = 229.564193548387, `1923` = 390.564193548387, `1924` = -76.4358064516128, `1945` = -330.935806451613, `1946` = -349.235806451613, `1947` = -340.435806451613, `1948` = -337.935806451613, `1949` = -299.935806451613, `1950` = -323.935806451613, `1951` = -332.935806451613, `1968` = -251.435806451613), control = list(mstop = 1100, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", 
+    fW = function (f) 
+    return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
+    y - f, risk = function (y, f, w = 1) 
+    sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
+    UseMethod("weighted.mean"), check_y = function (y) 
+    {
+        if (!is.numeric(y) || !is.null(dim(y))) 
+            stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
+        y
+    }, weights = function (w) 
+    {
+        switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
+    }, nuisance = function () 
+    return(NA), response = function (f) 
+    f, rclass = function (f) 
+    NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, 
+`1949` = 653.5, `1950` = 629.5, `1951` = 620.5, `1968` = 702), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
 nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
 {
     res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
@@ -1107,19 +1123,22 @@
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t>feed_intake_g_d ~ bw_kg + bw_kg.sqd + adg_g_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t>c(118, 197, 142, 213, 182, 164, 199, 195, 203, 183, 141, 198, 116, 211, 209, 210, 191, 193, 194)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 134, 136, 138, 163, 165, 166, 167, 180, 181, 184, 190, 192, 196, 200, 205, 208, 212)</t>
+}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t>c(690.646246988091, 702.266791435633, 1415.7669277196, 1427.56651479569, 1379.38931691978, 1316.28621977746, 1336.03051748987, 1166.34278944223, 1111.88355329175, 1209.08343094914, 1177.77343438695, 1260.08884957976, 1231.89672417258, 1197.34850785696, 708.189715626926, 706.001514401897, 671.713902258108, 661.530682062377, 706.18068758043, 1100.76986368753, 1316.59630304364, 1345.25560324843, 1034.70000193737, 594.647492121294, 584.089723473352, 605.336995360276, 583.754695165285, 608.731652349524, 
+610.00309851547, 604.614127368904, 587.615863622735)</t>
+  </si>
+  <si>
+    <t>c(-9.05375301190918, 5.76679143563308, 25.7669277196026, -112.43348520431, -141.610683080222, 53.28621977746, -89.9694825101349, -178.65721055777, -205.116446708247, 39.0834309491447, 27.7734343869488, 50.088849579764, 41.8967241725813, 47.3485078569556, 112.689715626926, 109.621514401897, 72.833902258108, 71.6506820623766, 113.21068758043, 50.7698636875346, 133.596303043635, 1.25560324843491, 157.700001937375, -27.8525078787061, -20.1102765266475, -7.66300463972379, -31.7453048347147, -44.7683476504765, 
+-19.4969014845298, -15.8858726310957, -114.384136377265)</t>
+  </si>
+  <si>
+    <t>c(9.05375301190918, 5.76679143563308, 25.7669277196026, 112.43348520431, 141.610683080222, 53.28621977746, 89.9694825101349, 178.65721055777, 205.116446708247, 39.0834309491447, 27.7734343869488, 50.088849579764, 41.8967241725813, 47.3485078569556, 112.689715626926, 109.621514401897, 72.833902258108, 71.6506820623766, 113.21068758043, 50.7698636875346, 133.596303043635, 1.25560324843491, 157.700001937375, 27.8525078787061, 20.1102765266475, 7.66300463972379, 31.7453048347147, 44.7683476504765, 19.4969014845298, 
+15.8858726310957, 114.384136377265)</t>
+  </si>
+  <si>
+    <t>c(167, 199, 164, 196, 198, 138, 142, 181, 165, 197, 166, 192, 194, 193, 191)</t>
   </si>
   <si>
     <t>list(baselearner = list(list(model.frame = function () 
@@ -1243,7 +1262,7 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, Xnames = c("(Intercept)", "bw_kg", "bw_kg.sqd", "adg_g_day", "NDF_nutrition"), MPinv = function () 
+}, Xnames = c("(Intercept)", "bw_kg", "adg_g_day", "NDF_nutrition", "CP_nutrition"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
@@ -1253,26 +1272,25 @@
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-})), offset = 875.276578947368, ustart = c(`1376` = -175.576578947368, `1377` = -178.776578947368, `1487` = 514.723421052632, `1490` = 664.723421052632, `1585` = 645.723421052632, `1587` = 387.723421052632, `1589` = 550.723421052632, `1639` = 469.723421052632, `1640` = 441.723421052632, `1770` = 294.723421052632, `1771` = 274.723421052632, `1772` = 334.723421052632, `1773` = 314.723421052632, `1774` = 274.723421052632, `1815` = -279.776578947368, `1816` = -278.896578947368, `1817` = -276.396578947368, 
-`1818` = -285.396578947368, `1819` = -282.306578947368, `1921` = 174.723421052632, `1922` = 307.723421052632, `1923` = 468.723421052632, `1924` = 1.72342105263158, `1945` = -252.776578947368, `1946` = -271.076578947368, `1947` = -262.276578947368, `1948` = -259.776578947368, `1949` = -221.776578947368, `1950` = -245.776578947368, `1951` = -254.776578947368, `1968` = -173.276578947368, `1981` = -161.276578947368, `1984` = -339.276578947368, `1985` = -386.276578947368, `1986` = -357.276578947368, `1987` = -382.276578947368, 
-`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 1200, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
-return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
-y - f, risk = function (y, f, w = 1) 
-sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
-UseMethod("weighted.mean"), check_y = function (y) 
-{
-    if (!is.numeric(y) || !is.null(dim(y))) 
-        stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
-    y
-}, weights = function (w) 
-{
-    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
-}, nuisance = function () 
-return(NA), response = function (f) 
-f, rclass = function (f) 
-NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, `1949` = 653.5, 
-`1950` = 629.5, `1951` = 620.5, `1968` = 702, `1981` = 714, `1984` = 536, `1985` = 489, `1986` = 518, `1987` = 493, `1988` = 452, `1989` = 502), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968", "1981", "1984", "1985", "1986", "1987", "1988", "1989"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 
-1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+})), offset = 953.435806451613, ustart = c(`1376` = -253.735806451613, `1377` = -256.935806451613, `1487` = 436.564193548387, `1490` = 586.564193548387, `1585` = 567.564193548387, `1587` = 309.564193548387, `1589` = 472.564193548387, `1639` = 391.564193548387, `1640` = 363.564193548387, `1770` = 216.564193548387, `1771` = 196.564193548387, `1772` = 256.564193548387, `1773` = 236.564193548387, `1774` = 196.564193548387, `1815` = -357.935806451613, `1816` = -357.055806451613, `1817` = -354.555806451613, 
+`1818` = -363.555806451613, `1819` = -360.465806451613, `1921` = 96.5641935483872, `1922` = 229.564193548387, `1923` = 390.564193548387, `1924` = -76.4358064516128, `1945` = -330.935806451613, `1946` = -349.235806451613, `1947` = -340.435806451613, `1948` = -337.935806451613, `1949` = -299.935806451613, `1950` = -323.935806451613, `1951` = -332.935806451613, `1968` = -251.435806451613), control = list(mstop = 1099, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", 
+    fW = function (f) 
+    return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
+    y - f, risk = function (y, f, w = 1) 
+    sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
+    UseMethod("weighted.mean"), check_y = function (y) 
+    {
+        if (!is.numeric(y) || !is.null(dim(y))) 
+            stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
+        y
+    }, weights = function (w) 
+    {
+        switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
+    }, nuisance = function () 
+    return(NA), response = function (f) 
+    f, rclass = function (f) 
+    NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, 
+`1949` = 653.5, `1950` = 629.5, `1951` = 620.5, `1968` = 702), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
 nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
 {
     res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
@@ -1502,792 +1520,16 @@
 }, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
   </si>
   <si>
-    <t>c(688.982031338571, 727.917117251008, 1388.12848446115, 1412.9474094908, 1415.47799505845, 1305.84037122978, 1353.75201209906, 1269.10256892563, 1214.94177764155, 1204.26464785288, 1165.33829584855, 1263.89578097819, 1220.07549329176, 1185.83626064049, 607.539970771731, 603.419731299575, 564.882524875035, 565.42024789562, 599.802899811298, 1086.32442615241, 1333.11616855286, 1369.53801957658, 1020.79396885958, 557.47872631712, 586.969007428779, 594.92541082397, 582.098411249916, 605.881064141295, 
-596.895500134169, 583.868144575807, 693.393813492161, 742.811545956923, 541.086302309205, 476.478032631793, 520.040294596191, 579.769763281921, 474.414652447199, 537.94521149965)</t>
-  </si>
-  <si>
-    <t>c(-10.7179686614295, 31.4171172510075, -1.87151553885292, -127.052590509199, -105.522004941552, 42.8403712297804, -72.2479879009363, -75.8974310743695, -102.058222358445, 34.2646478528845, 15.3382958485499, 53.8957809781941, 30.0754932917635, 35.836260640488, 12.0399707717309, 7.03973129957456, -33.997475124965, -24.4597521043801, 6.83289981129838, 36.3244261524087, 150.11616855286, 25.538019576582, 143.793968859579, -65.02127368288, -17.2309925712204, -18.07458917603, -33.4015887500838, -47.6189358587047, 
--32.6044998658308, -36.6318554241934, -8.60618650783852, 28.8115459569231, 5.08630230920517, -12.5219673682074, 2.04029459619051, 86.7697632819209, 22.4146524471988, 35.9452114996498)</t>
-  </si>
-  <si>
-    <t>c(10.7179686614295, 31.4171172510075, 1.87151553885292, 127.052590509199, 105.522004941552, 42.8403712297804, 72.2479879009363, 75.8974310743695, 102.058222358445, 34.2646478528845, 15.3382958485499, 53.8957809781941, 30.0754932917635, 35.836260640488, 12.0399707717309, 7.03973129957456, 33.997475124965, 24.4597521043801, 6.83289981129838, 36.3244261524087, 150.11616855286, 25.538019576582, 143.793968859579, 65.02127368288, 17.2309925712204, 18.07458917603, 33.4015887500838, 47.6189358587047, 32.6044998658308, 
-36.6318554241934, 8.60618650783852, 28.8115459569231, 5.08630230920517, 12.5219673682074, 2.04029459619051, 86.7697632819209, 22.4146524471988, 35.9452114996498)</t>
-  </si>
-  <si>
-    <t>c(200, 165, 205, 184, 107, 180, 138, 190, 212, 208, 167, 134, 192, 166, 196, 181, 163, 136, 108)</t>
-  </si>
-  <si>
-    <t>c(116, 118, 141, 142, 164, 182, 183, 191, 193, 194, 195, 197, 198, 199, 203, 209, 210, 211, 213)</t>
-  </si>
-  <si>
-    <t>list(baselearner = list(list(model.frame = function () 
-return(NULL), get_data = function () 
-X, get_index = function () 
-index, get_vary = function () 
-NULL, get_names = function () 
-colnames(X), set_names = function (value) 
-attr(X, "colnames") &lt;&lt;- value, dpp = function (weights) 
-{
-    weights &lt;- weights[cc]
-    xtx &lt;- colSums(X^2 * weights, na.rm = TRUE)
-    xtx[xtx &lt; .Machine$double.eps] &lt;- 1
-    sxtx &lt;- sqrt(xtx)
-    p &lt;- ncol(X)
-    if (is(X, "Matrix")) {
-        MPinvS &lt;- t(X * weights)/sxtx
-        est &lt;- function(y) MPinvS %*% y
-    }
-    else {
-        MPinvS &lt;- NULL
-        storage.mode(X) &lt;- "double"
-        est &lt;- function(y) crossprod(X, y * weights)/sxtx
-    }
-    fit &lt;- function(y) {
-        if (!is.null(index)) 
-            y &lt;- y[cc]
-        mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
-        xselect &lt;- which(as.logical(mmu == amu))[1]
-        coef &lt;- mu[xselect]/sxtx[xselect]
-        ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
-            if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
-            return(coef * X[index, xselect, drop = FALSE])
-        })
-        class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
-        return(ret)
-    }
-    predict &lt;- function(bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) {
-        aggregate &lt;- match.arg(aggregate)
-        cf &lt;- switch(aggregate, sum = {
-            cf &lt;- rep(0, bm[[1]]$model["p"])
-            for (i in 1:length(bm)) {
-                m &lt;- bm[[i]]$model
-                cf[m[2]] &lt;- cf[m[2]] + m[1]
-            }
-            cf
-        }, cumsum = {
-            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
-            if (length(bm) &gt; 2) {
-                for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
-            }
-            cf
-        }, none = {
-            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
-            if (length(bm) &gt; 2) {
-                for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
-            }
-            cf
-        })
-        if (!is.null(newdata)) {
-            stopifnot(all(class(newdata) == class(X)))
-            stopifnot(all(colnames(newdata) == colnames(X)))
-            X &lt;- newdata
-            return(X %*% cf)
-        }
-        if (!is.null(index)) 
-            return(X[index, , drop = FALSE] %*% cf)
-        return(X %*% cf)
-    }
-    ret &lt;- list(fit = fit, predict = predict, Xnames = colnames(X), MPinv = function() {
-        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
-        return(MPinvS/sxtx)
-    }, hatvalues = function() {
-        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
-        X %*% (MPinvS/sxtx)
-    })
-    class(ret) &lt;- c("bl_cwlin", "bl")
-    return(ret)
-})), basemodel = list(list(fit = function (y) 
-{
-    if (!is.null(index)) 
-        y &lt;- y[cc]
-    mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
-    xselect &lt;- which(as.logical(mmu == amu))[1]
-    coef &lt;- mu[xselect]/sxtx[xselect]
-    ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
-        if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
-        return(coef * X[index, xselect, drop = FALSE])
-    })
-    class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
-    return(ret)
-}, predict = function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
-{
-    aggregate &lt;- match.arg(aggregate)
-    cf &lt;- switch(aggregate, sum = {
-        cf &lt;- rep(0, bm[[1]]$model["p"])
-        for (i in 1:length(bm)) {
-            m &lt;- bm[[i]]$model
-            cf[m[2]] &lt;- cf[m[2]] + m[1]
-        }
-        cf
-    }, cumsum = {
-        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
-        if (length(bm) &gt; 2) {
-            for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
-        }
-        cf
-    }, none = {
-        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
-        if (length(bm) &gt; 2) {
-            for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
-        }
-        cf
-    })
-    if (!is.null(newdata)) {
-        stopifnot(all(class(newdata) == class(X)))
-        stopifnot(all(colnames(newdata) == colnames(X)))
-        X &lt;- newdata
-        return(X %*% cf)
-    }
-    if (!is.null(index)) 
-        return(X[index, , drop = FALSE] %*% cf)
-    return(X %*% cf)
-}, Xnames = c("(Intercept)", "bw_kg", "bw_kg.sqd", "adg_g_day", "NDF_nutrition"), MPinv = function () 
-{
-    if (is.null(MPinvS)) 
-        MPinvS &lt;&lt;- t(X * weights)/sxtx
-    return(MPinvS/sxtx)
-}, hatvalues = function () 
-{
-    if (is.null(MPinvS)) 
-        MPinvS &lt;&lt;- t(X * weights)/sxtx
-    X %*% (MPinvS/sxtx)
-})), offset = 875.276578947368, ustart = c(`1376` = -175.576578947368, `1377` = -178.776578947368, `1487` = 514.723421052632, `1490` = 664.723421052632, `1585` = 645.723421052632, `1587` = 387.723421052632, `1589` = 550.723421052632, `1639` = 469.723421052632, `1640` = 441.723421052632, `1770` = 294.723421052632, `1771` = 274.723421052632, `1772` = 334.723421052632, `1773` = 314.723421052632, `1774` = 274.723421052632, `1815` = -279.776578947368, `1816` = -278.896578947368, `1817` = -276.396578947368, 
-`1818` = -285.396578947368, `1819` = -282.306578947368, `1921` = 174.723421052632, `1922` = 307.723421052632, `1923` = 468.723421052632, `1924` = 1.72342105263158, `1945` = -252.776578947368, `1946` = -271.076578947368, `1947` = -262.276578947368, `1948` = -259.776578947368, `1949` = -221.776578947368, `1950` = -245.776578947368, `1951` = -254.776578947368, `1968` = -173.276578947368, `1981` = -161.276578947368, `1984` = -339.276578947368, `1985` = -386.276578947368, `1986` = -357.276578947368, `1987` = -382.276578947368, 
-`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 1168, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
-return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
-y - f, risk = function (y, f, w = 1) 
-sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
-UseMethod("weighted.mean"), check_y = function (y) 
-{
-    if (!is.numeric(y) || !is.null(dim(y))) 
-        stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
-    y
-}, weights = function (w) 
-{
-    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
-}, nuisance = function () 
-return(NA), response = function (f) 
-f, rclass = function (f) 
-NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, `1949` = 653.5, 
-`1950` = 629.5, `1951` = 620.5, `1968` = 702, `1981` = 714, `1984` = 536, `1985` = 489, `1986` = 518, `1987` = 493, `1988` = 452, `1989` = 502), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968", "1981", "1984", "1985", "1986", "1987", "1988", "1989"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 
-1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
-nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
-{
-    res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
-    res$newX &lt;- newX
-    res$assign &lt;- assign
-    res$center &lt;- cm
-    res$call &lt;- cl
-    res$hatvalues &lt;- function() {
-        H &lt;- vector(mode = "list", length = ncol(X))
-        MPinv &lt;- res$basemodel[[1]]$MPinv()
-        for (j in unique(res$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
-        H
-    }
-    res$rownames &lt;- rownames(mf)
-    res$model.frame &lt;- function(which = NULL) {
-        if (!is.null(which)) 
-            warning("Argument ", sQuote("which"), " is ignored")
-        mf
-    }
-    class(res) &lt;- c("glmboost", "mboost")
-    res
-}, mstop = function () 
-mstop, xselect = function () 
-{
-    if (mstop == 0) 
-        return(NULL)
-    return(xselect[1:mstop])
-}, fitted = function () 
-as.vector(fit), resid = function () 
-u, risk = function () 
-{
-    mrisk[1:(mstop + 1)]
-}, logLik = function () 
--mrisk[mstop + 1], which = function (which = NULL, usedonly = FALSE) 
-{
-    if (is.null(which)) 
-        which &lt;- 1:length(bnames)
-    if (is.character(which)) {
-        i &lt;- sapply(which, function(w) {
-            wi &lt;- grep(w, bnames, fixed = TRUE)
-            if (length(wi) &gt; 0) 
-                return(wi)
-            return(NA)
-        })
-        if (any(is.na(i))) 
-            warning(paste(which[is.na(i)], collapse = ","), " not found")
-        which &lt;- i
-    }
-    if (usedonly) 
-        which &lt;- which[which %in% RET$xselect()]
-    return(which)
-}, predict = function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
-{
-    if (mstop == 0) {
-        if (length(offset) == 1) {
-            if (!is.null(newdata)) 
-                return(rep(offset, NROW(newdata)))
-            return(rep(offset, NROW(y)))
-        }
-        if (!is.null(newdata)) {
-            warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
-            return(rep(0, NCOL(newdata)))
-        }
-        return(offset)
-    }
-    if (!is.null(xselect)) 
-        indx &lt;- ((1:length(xselect)) &lt;= mstop)
-    which &lt;- thiswhich(which, usedonly = nw &lt;- is.null(which))
-    if (length(which) == 0) 
-        return(NULL)
-    aggregate &lt;- match.arg(aggregate)
-    pfun &lt;- function(w, agg) {
-        ix &lt;- xselect == w &amp; indx
-        if (!any(ix)) 
-            return(0)
-        if (cwlin) 
-            w &lt;- 1
-        ret &lt;- nu * bl[[w]]$predict(ens[ix], newdata = newdata, aggregate = agg)
-        if (agg == "sum") 
-            return(ret)
-        m &lt;- Matrix(0, nrow = nrow(ret), ncol = sum(indx))
-        m[, which(ix)] &lt;- ret
-        m
-    }
-    pr &lt;- switch(aggregate, sum = {
-        pr &lt;- lapply(which, pfun, agg = "sum")
-        if (!nw) {
-            if (NCOL(pr[[1]]) == 1) {
-                pr &lt;- do.call("cbind", pr)
-                colnames(pr) &lt;- bnames[which]
-                attr(pr, "offset") &lt;- offset
-            }
-            return(pr)
-        } else {
-            ret &lt;- Reduce("+", pr)
-            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
-                warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
-            } else {
-                ret &lt;- ret + offset
-            }
-            return(ret)
-        }
-    }, cumsum = {
-        if (!nw) {
-            pr &lt;- lapply(which, pfun, agg = "none")
-            pr &lt;- lapply(pr, function(x) {
-                .Call("R_mcumsum", as(x, "matrix"), PACKAGE = "mboost")
-            })
-            names(pr) &lt;- bnames[which]
-            attr(pr, "offset") &lt;- offset
-            return(pr)
-        } else {
-            pr &lt;- 0
-            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
-            pr &lt;- .Call("R_mcumsum", as(pr, "matrix"), PACKAGE = "mboost")
-            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
-                warning(sQuote("length(offset) &gt; 1"), ": User-specified offset is not a scalar, ", "thus offset not used for prediction when ", sQuote("newdata"), " is specified")
-            } else {
-                pr &lt;- pr + offset
-            }
-            return(pr)
-        }
-    }, none = {
-        if (!nw) {
-            pr &lt;- lapply(which, pfun, agg = "none")
-            for (i in 1:length(pr)) pr[[i]] &lt;- as(pr[[i]], "matrix")
-            names(pr) &lt;- bnames[which]
-            attr(pr, "offset") &lt;- offset
-            return(pr)
-        } else {
-            pr &lt;- 0
-            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
-            pr &lt;- as(pr, "matrix")
-            attr(pr, "offset") &lt;- offset
-            return(pr)
-        }
-    })
-    return(pr)
-}, model.frame = function (which = NULL) 
-{
-    if (!is.null(which)) 
-        warning("Argument ", sQuote("which"), " is ignored")
-    mf
-}, subset = function (i) 
-{
-    if (i &lt;= mstop || i &lt;= length(xselect)) {
-        if (i != mstop) {
-            mstop &lt;&lt;- i
-            fit &lt;&lt;- RET$predict()
-            u &lt;&lt;- ngradient(y, fit, weights)
-        }
-    }
-    else {
-        if (mstop != length(xselect)) {
-            mstop &lt;&lt;- length(xselect)
-            fit &lt;&lt;- RET$predict()
-            u &lt;&lt;- ngradient(y, fit, weights)
-        }
-        tmp &lt;- boost(i - mstop)
-    }
-}, coef = function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
-{
-    if (!is.null(xselect)) 
-        indx &lt;- ((1:length(xselect)) &lt;= mstop)
-    which &lt;- thiswhich(which, usedonly = is.null(which))
-    if (length(which) == 0) 
-        return(NULL)
-    aggregate &lt;- match.arg(aggregate)
-    cfun &lt;- function(w) {
-        ix &lt;- (xselect == w &amp; indx)
-        cf &lt;- numeric(mstop)
-        if (!any(ix)) {
-            if (!cwlin) {
-                nm &lt;- bl[[w]]$Xnames
-                cf &lt;- matrix(0, nrow = length(nm), ncol = mstop)
-            }
-        }
-        else {
-            if (inherits(ens[ix][[1]], "bm_cwlin") &amp;&amp; !cwlin) {
-                cftmp &lt;- sapply(ens[ix], coef, all = TRUE)
-            }
-            else {
-                cftmp &lt;- sapply(ens[ix], coef)
-            }
-            nr &lt;- NROW(cftmp)
-            if (!is.matrix(cftmp)) 
-                nr &lt;- 1
-            cf &lt;- matrix(0, nrow = nr, ncol = mstop)
-            cf[, which(ix)] &lt;- cftmp
-        }
-        if (!is.matrix(cf)) 
-            cf &lt;- matrix(cf, nrow = 1)
-        if (any(sapply(cf, is.null))) {
-            ret &lt;- NULL
-        }
-        else {
-            ret &lt;- switch(aggregate, sum = rowSums(cf) * nu, cumsum = {
-                .Call("R_mcumsum", as(cf, "matrix") * nu, PACKAGE = "mboost")
-            }, none = nu * cf)
-        }
-        if (!cwlin) {
-            nm &lt;- bl[[w]]$Xnames
-            if (is.matrix(ret)) {
-                rownames(ret) &lt;- nm
-            }
-            else {
-                names(ret) &lt;- nm
-            }
-        }
-        ret
-    }
-    ret &lt;- lapply(which, cfun)
-    names(ret) &lt;- bnames[which]
-    attr(ret, "offset") &lt;- offset
-    return(ret)
-}, hatvalues = function () 
-{
-    H &lt;- vector(mode = "list", length = ncol(X))
-    MPinv &lt;- ret$basemodel[[1]]$MPinv()
-    for (j in unique(ret$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
-    H
-}, newX = function (newdata) 
-{
-    mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
-    X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
-    scale(X, center = cm, scale = FALSE)
-}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
-  </si>
-  <si>
-    <t>c(688.978383452354, 727.915434368706, 1388.15197204725, 1412.96701576245, 1415.46461151288, 1305.82698768421, 1353.73862855349, 1269.0028502715, 1214.84205898742, 1204.29117075935, 1165.36548344705, 1263.92265314254, 1220.10362696803, 1185.86433019706, 607.525568568919, 603.397019570112, 564.842129973743, 565.376068961711, 599.784300602959, 1086.34917977886, 1333.13673890677, 1369.55802951575, 1020.80880711259, 557.467835874906, 586.954348649523, 594.910752044714, 582.085027704345, 605.868936708071, 
-596.880841354913, 583.852191441527, 693.411785587666, 742.836152994652, 541.090722000649, 476.482452323237, 520.044714287634, 579.774182973365, 474.419072138643, 537.949631191094)</t>
-  </si>
-  <si>
-    <t>c(-10.7216165476459, 31.4154343687064, -1.84802795275482, -127.032984237555, -105.535388487123, 42.8269876842091, -72.2613714465074, -75.9971497284996, -102.157941012576, 34.2911707593491, 15.3654834470451, 53.9226531425411, 30.103626968026, 35.8643301970556, 12.0255685689185, 7.01701957011221, -34.0378700262571, -24.5039310382892, 6.81430060295941, 36.3491797788565, 150.136738906773, 25.5580295157461, 143.808807112591, -65.0321641250943, -17.2456513504768, -18.0892479552864, -33.4149722956549, -47.6310632919286, 
--32.6191586450871, -36.6478085584727, -8.58821441233397, 28.8361529946517, 5.09072200064907, -12.5175476767635, 2.04471428763441, 86.7741829733648, 22.4190721386427, 35.9496311910937)</t>
-  </si>
-  <si>
-    <t>c(10.7216165476459, 31.4154343687064, 1.84802795275482, 127.032984237555, 105.535388487123, 42.8269876842091, 72.2613714465074, 75.9971497284996, 102.157941012576, 34.2911707593491, 15.3654834470451, 53.9226531425411, 30.103626968026, 35.8643301970556, 12.0255685689185, 7.01701957011221, 34.0378700262571, 24.5039310382892, 6.81430060295941, 36.3491797788565, 150.136738906773, 25.5580295157461, 143.808807112591, 65.0321641250943, 17.2456513504768, 18.0892479552864, 33.4149722956549, 47.6310632919286, 
-32.6191586450871, 36.6478085584727, 8.58821441233397, 28.8361529946517, 5.09072200064907, 12.5175476767635, 2.04471428763441, 86.7741829733648, 22.4190721386427, 35.9496311910937)</t>
-  </si>
-  <si>
-    <t>list(baselearner = list(list(model.frame = function () 
-return(NULL), get_data = function () 
-X, get_index = function () 
-index, get_vary = function () 
-NULL, get_names = function () 
-colnames(X), set_names = function (value) 
-attr(X, "colnames") &lt;&lt;- value, dpp = function (weights) 
-{
-    weights &lt;- weights[cc]
-    xtx &lt;- colSums(X^2 * weights, na.rm = TRUE)
-    xtx[xtx &lt; .Machine$double.eps] &lt;- 1
-    sxtx &lt;- sqrt(xtx)
-    p &lt;- ncol(X)
-    if (is(X, "Matrix")) {
-        MPinvS &lt;- t(X * weights)/sxtx
-        est &lt;- function(y) MPinvS %*% y
-    }
-    else {
-        MPinvS &lt;- NULL
-        storage.mode(X) &lt;- "double"
-        est &lt;- function(y) crossprod(X, y * weights)/sxtx
-    }
-    fit &lt;- function(y) {
-        if (!is.null(index)) 
-            y &lt;- y[cc]
-        mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
-        xselect &lt;- which(as.logical(mmu == amu))[1]
-        coef &lt;- mu[xselect]/sxtx[xselect]
-        ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
-            if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
-            return(coef * X[index, xselect, drop = FALSE])
-        })
-        class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
-        return(ret)
-    }
-    predict &lt;- function(bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) {
-        aggregate &lt;- match.arg(aggregate)
-        cf &lt;- switch(aggregate, sum = {
-            cf &lt;- rep(0, bm[[1]]$model["p"])
-            for (i in 1:length(bm)) {
-                m &lt;- bm[[i]]$model
-                cf[m[2]] &lt;- cf[m[2]] + m[1]
-            }
-            cf
-        }, cumsum = {
-            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
-            if (length(bm) &gt; 2) {
-                for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
-            }
-            cf
-        }, none = {
-            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
-            if (length(bm) &gt; 2) {
-                for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
-            }
-            cf
-        })
-        if (!is.null(newdata)) {
-            stopifnot(all(class(newdata) == class(X)))
-            stopifnot(all(colnames(newdata) == colnames(X)))
-            X &lt;- newdata
-            return(X %*% cf)
-        }
-        if (!is.null(index)) 
-            return(X[index, , drop = FALSE] %*% cf)
-        return(X %*% cf)
-    }
-    ret &lt;- list(fit = fit, predict = predict, Xnames = colnames(X), MPinv = function() {
-        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
-        return(MPinvS/sxtx)
-    }, hatvalues = function() {
-        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
-        X %*% (MPinvS/sxtx)
-    })
-    class(ret) &lt;- c("bl_cwlin", "bl")
-    return(ret)
-})), basemodel = list(list(fit = function (y) 
-{
-    if (!is.null(index)) 
-        y &lt;- y[cc]
-    mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
-    xselect &lt;- which(as.logical(mmu == amu))[1]
-    coef &lt;- mu[xselect]/sxtx[xselect]
-    ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
-        if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
-        return(coef * X[index, xselect, drop = FALSE])
-    })
-    class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
-    return(ret)
-}, predict = function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
-{
-    aggregate &lt;- match.arg(aggregate)
-    cf &lt;- switch(aggregate, sum = {
-        cf &lt;- rep(0, bm[[1]]$model["p"])
-        for (i in 1:length(bm)) {
-            m &lt;- bm[[i]]$model
-            cf[m[2]] &lt;- cf[m[2]] + m[1]
-        }
-        cf
-    }, cumsum = {
-        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
-        if (length(bm) &gt; 2) {
-            for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
-        }
-        cf
-    }, none = {
-        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
-        if (length(bm) &gt; 2) {
-            for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
-        }
-        cf
-    })
-    if (!is.null(newdata)) {
-        stopifnot(all(class(newdata) == class(X)))
-        stopifnot(all(colnames(newdata) == colnames(X)))
-        X &lt;- newdata
-        return(X %*% cf)
-    }
-    if (!is.null(index)) 
-        return(X[index, , drop = FALSE] %*% cf)
-    return(X %*% cf)
-}, Xnames = c("(Intercept)", "bw_kg", "bw_kg.sqd", "adg_g_day", "NDF_nutrition"), MPinv = function () 
-{
-    if (is.null(MPinvS)) 
-        MPinvS &lt;&lt;- t(X * weights)/sxtx
-    return(MPinvS/sxtx)
-}, hatvalues = function () 
-{
-    if (is.null(MPinvS)) 
-        MPinvS &lt;&lt;- t(X * weights)/sxtx
-    X %*% (MPinvS/sxtx)
-})), offset = 697.910728140674, ustart = c(`1376` = 1, `1377` = -1, `1487` = 1, `1490` = 1, `1585` = 1, `1587` = 1, `1589` = 1, `1639` = 1, `1640` = 1, `1770` = 1, `1771` = 1, `1772` = 1, `1773` = 1, `1774` = 1, `1815` = -1, `1816` = -1, `1817` = -1, `1818` = -1, `1819` = -1, `1921` = 1, `1922` = 1, `1923` = 1, `1924` = 1, `1945` = -1, `1946` = -1, `1947` = -1, `1948` = -1, `1949` = -1, `1950` = -1, `1951` = -1, `1968` = 1, `1981` = 1, `1984` = -1, `1985` = -1, `1986` = -1, `1987` = -1, `1988` = -1, 
-`1989` = -1), control = list(mstop = 1200, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family", ngradient = function (y, f, w = 1) 
-sign(y - f), risk = function (y, f, w = 1) 
-sum(w * loss(y, f), na.rm = TRUE), offset = function (y, w) 
-optimize(risk, interval = range(y), y = y, w = w)$minimum, check_y = function (y) 
-{
-    if (!is.numeric(y) || !is.null(dim(y))) 
-        stop("response is not a numeric vector but ", sQuote("family = Laplace()"))
-    y
-}, weights = function (w) 
-{
-    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
-}, nuisance = function () 
-return(NA), response = function (f) 
-f, rclass = function (f) 
-NA, name = "Absolute Error", charloss = "abs(y - f) \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, `1949` = 653.5, 
-`1950` = 629.5, `1951` = 620.5, `1968` = 702, `1981` = 714, `1984` = 536, `1985` = 489, `1986` = 518, `1987` = 493, `1988` = 452, `1989` = 502), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968", "1981", "1984", "1985", "1986", "1987", "1988", "1989"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 
-1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
-nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
-{
-    res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
-    res$newX &lt;- newX
-    res$assign &lt;- assign
-    res$center &lt;- cm
-    res$call &lt;- cl
-    res$hatvalues &lt;- function() {
-        H &lt;- vector(mode = "list", length = ncol(X))
-        MPinv &lt;- res$basemodel[[1]]$MPinv()
-        for (j in unique(res$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
-        H
-    }
-    res$rownames &lt;- rownames(mf)
-    res$model.frame &lt;- function(which = NULL) {
-        if (!is.null(which)) 
-            warning("Argument ", sQuote("which"), " is ignored")
-        mf
-    }
-    class(res) &lt;- c("glmboost", "mboost")
-    res
-}, mstop = function () 
-mstop, xselect = function () 
-{
-    if (mstop == 0) 
-        return(NULL)
-    return(xselect[1:mstop])
-}, fitted = function () 
-as.vector(fit), resid = function () 
-u, risk = function () 
-{
-    mrisk[1:(mstop + 1)]
-}, logLik = function () 
--mrisk[mstop + 1], which = function (which = NULL, usedonly = FALSE) 
-{
-    if (is.null(which)) 
-        which &lt;- 1:length(bnames)
-    if (is.character(which)) {
-        i &lt;- sapply(which, function(w) {
-            wi &lt;- grep(w, bnames, fixed = TRUE)
-            if (length(wi) &gt; 0) 
-                return(wi)
-            return(NA)
-        })
-        if (any(is.na(i))) 
-            warning(paste(which[is.na(i)], collapse = ","), " not found")
-        which &lt;- i
-    }
-    if (usedonly) 
-        which &lt;- which[which %in% RET$xselect()]
-    return(which)
-}, predict = function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
-{
-    if (mstop == 0) {
-        if (length(offset) == 1) {
-            if (!is.null(newdata)) 
-                return(rep(offset, NROW(newdata)))
-            return(rep(offset, NROW(y)))
-        }
-        if (!is.null(newdata)) {
-            warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
-            return(rep(0, NCOL(newdata)))
-        }
-        return(offset)
-    }
-    if (!is.null(xselect)) 
-        indx &lt;- ((1:length(xselect)) &lt;= mstop)
-    which &lt;- thiswhich(which, usedonly = nw &lt;- is.null(which))
-    if (length(which) == 0) 
-        return(NULL)
-    aggregate &lt;- match.arg(aggregate)
-    pfun &lt;- function(w, agg) {
-        ix &lt;- xselect == w &amp; indx
-        if (!any(ix)) 
-            return(0)
-        if (cwlin) 
-            w &lt;- 1
-        ret &lt;- nu * bl[[w]]$predict(ens[ix], newdata = newdata, aggregate = agg)
-        if (agg == "sum") 
-            return(ret)
-        m &lt;- Matrix(0, nrow = nrow(ret), ncol = sum(indx))
-        m[, which(ix)] &lt;- ret
-        m
-    }
-    pr &lt;- switch(aggregate, sum = {
-        pr &lt;- lapply(which, pfun, agg = "sum")
-        if (!nw) {
-            if (NCOL(pr[[1]]) == 1) {
-                pr &lt;- do.call("cbind", pr)
-                colnames(pr) &lt;- bnames[which]
-                attr(pr, "offset") &lt;- offset
-            }
-            return(pr)
-        } else {
-            ret &lt;- Reduce("+", pr)
-            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
-                warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
-            } else {
-                ret &lt;- ret + offset
-            }
-            return(ret)
-        }
-    }, cumsum = {
-        if (!nw) {
-            pr &lt;- lapply(which, pfun, agg = "none")
-            pr &lt;- lapply(pr, function(x) {
-                .Call("R_mcumsum", as(x, "matrix"), PACKAGE = "mboost")
-            })
-            names(pr) &lt;- bnames[which]
-            attr(pr, "offset") &lt;- offset
-            return(pr)
-        } else {
-            pr &lt;- 0
-            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
-            pr &lt;- .Call("R_mcumsum", as(pr, "matrix"), PACKAGE = "mboost")
-            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
-                warning(sQuote("length(offset) &gt; 1"), ": User-specified offset is not a scalar, ", "thus offset not used for prediction when ", sQuote("newdata"), " is specified")
-            } else {
-                pr &lt;- pr + offset
-            }
-            return(pr)
-        }
-    }, none = {
-        if (!nw) {
-            pr &lt;- lapply(which, pfun, agg = "none")
-            for (i in 1:length(pr)) pr[[i]] &lt;- as(pr[[i]], "matrix")
-            names(pr) &lt;- bnames[which]
-            attr(pr, "offset") &lt;- offset
-            return(pr)
-        } else {
-            pr &lt;- 0
-            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
-            pr &lt;- as(pr, "matrix")
-            attr(pr, "offset") &lt;- offset
-            return(pr)
-        }
-    })
-    return(pr)
-}, model.frame = function (which = NULL) 
-{
-    if (!is.null(which)) 
-        warning("Argument ", sQuote("which"), " is ignored")
-    mf
-}, subset = function (i) 
-{
-    if (i &lt;= mstop || i &lt;= length(xselect)) {
-        if (i != mstop) {
-            mstop &lt;&lt;- i
-            fit &lt;&lt;- RET$predict()
-            u &lt;&lt;- ngradient(y, fit, weights)
-        }
-    }
-    else {
-        if (mstop != length(xselect)) {
-            mstop &lt;&lt;- length(xselect)
-            fit &lt;&lt;- RET$predict()
-            u &lt;&lt;- ngradient(y, fit, weights)
-        }
-        tmp &lt;- boost(i - mstop)
-    }
-}, coef = function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
-{
-    if (!is.null(xselect)) 
-        indx &lt;- ((1:length(xselect)) &lt;= mstop)
-    which &lt;- thiswhich(which, usedonly = is.null(which))
-    if (length(which) == 0) 
-        return(NULL)
-    aggregate &lt;- match.arg(aggregate)
-    cfun &lt;- function(w) {
-        ix &lt;- (xselect == w &amp; indx)
-        cf &lt;- numeric(mstop)
-        if (!any(ix)) {
-            if (!cwlin) {
-                nm &lt;- bl[[w]]$Xnames
-                cf &lt;- matrix(0, nrow = length(nm), ncol = mstop)
-            }
-        }
-        else {
-            if (inherits(ens[ix][[1]], "bm_cwlin") &amp;&amp; !cwlin) {
-                cftmp &lt;- sapply(ens[ix], coef, all = TRUE)
-            }
-            else {
-                cftmp &lt;- sapply(ens[ix], coef)
-            }
-            nr &lt;- NROW(cftmp)
-            if (!is.matrix(cftmp)) 
-                nr &lt;- 1
-            cf &lt;- matrix(0, nrow = nr, ncol = mstop)
-            cf[, which(ix)] &lt;- cftmp
-        }
-        if (!is.matrix(cf)) 
-            cf &lt;- matrix(cf, nrow = 1)
-        if (any(sapply(cf, is.null))) {
-            ret &lt;- NULL
-        }
-        else {
-            ret &lt;- switch(aggregate, sum = rowSums(cf) * nu, cumsum = {
-                .Call("R_mcumsum", as(cf, "matrix") * nu, PACKAGE = "mboost")
-            }, none = nu * cf)
-        }
-        if (!cwlin) {
-            nm &lt;- bl[[w]]$Xnames
-            if (is.matrix(ret)) {
-                rownames(ret) &lt;- nm
-            }
-            else {
-                names(ret) &lt;- nm
-            }
-        }
-        ret
-    }
-    ret &lt;- lapply(which, cfun)
-    names(ret) &lt;- bnames[which]
-    attr(ret, "offset") &lt;- offset
-    return(ret)
-}, hatvalues = function () 
-{
-    H &lt;- vector(mode = "list", length = ncol(X))
-    MPinv &lt;- ret$basemodel[[1]]$MPinv()
-    for (j in unique(ret$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
-    H
-}, newX = function (newdata) 
-{
-    mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
-    X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
-    scale(X, center = cm, scale = FALSE)
-}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+    <t>c(690.988869735865, 702.609414183407, 1416.10955046738, 1427.90913754346, 1379.73193966755, 1316.62884252523, 1336.37314023764, 1166.68541219, 1112.22617603953, 1209.42605369692, 1178.11605713472, 1260.43147232754, 1232.23934692036, 1197.69113060473, 708.5323383747, 706.344137149671, 672.056525005882, 661.873304810151, 706.523310328204, 1101.11248643531, 1316.93892579141, 1345.59822599621, 1035.04262468515, 594.990114869068, 584.432346221127, 605.679618108051, 584.09731791306, 609.074275097298, 610.345721263245, 
+604.956750116679, 587.958486370509)</t>
+  </si>
+  <si>
+    <t>c(-8.71113026413479, 6.10941418340747, 26.1095504673769, -112.090862456536, -141.268060332448, 53.6288425252344, -89.6268597623605, -178.314587809996, -204.773823960473, 39.4260536969191, 28.1160571347232, 50.4314723275384, 42.2393469203557, 47.69113060473, 113.0323383747, 109.964137149671, 73.1765250058824, 71.993304810151, 113.553310328204, 51.1124864353089, 133.938925791409, 1.59822599620929, 158.042624685149, -27.5098851309317, -19.7676537788731, -7.32038189194941, -31.4026820869403, -44.4257249027021, 
+-19.1542787367554, -15.5432498833213, -114.041513629491)</t>
+  </si>
+  <si>
+    <t>c(8.71113026413479, 6.10941418340747, 26.1095504673769, 112.090862456536, 141.268060332448, 53.6288425252344, 89.6268597623605, 178.314587809996, 204.773823960473, 39.4260536969191, 28.1160571347232, 50.4314723275384, 42.2393469203557, 47.69113060473, 113.0323383747, 109.964137149671, 73.1765250058824, 71.993304810151, 113.553310328204, 51.1124864353089, 133.938925791409, 1.59822599620929, 158.042624685149, 27.5098851309317, 19.7676537788731, 7.32038189194941, 31.4026820869403, 44.4257249027021, 
+19.1542787367554, 15.5432498833213, 114.041513629491)</t>
   </si>
 </sst>
 </file>
@@ -2621,13 +1863,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CL9"/>
+  <dimension ref="A1:CM5"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="42" max="42" width="58.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:90" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2898,82 +2137,85 @@
       <c r="CL1" t="s">
         <v>89</v>
       </c>
+      <c r="CM1" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="2" spans="1:90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:91" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1152</v>
+        <v>1100</v>
       </c>
       <c r="I2">
         <v>0.1</v>
       </c>
       <c r="J2">
-        <v>0.83046812929889602</v>
+        <v>0.92285396534869102</v>
       </c>
       <c r="K2">
-        <v>12.9196804267342</v>
+        <v>9.8571957579962302</v>
       </c>
       <c r="L2">
-        <v>0.93430023322482503</v>
+        <v>0.96721088014367096</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2">
-        <v>0.83046812929889602</v>
+        <v>0.92285396534869102</v>
       </c>
       <c r="O2">
-        <v>12.9196804267342</v>
+        <v>9.8571957579962302</v>
       </c>
       <c r="P2">
-        <v>0.93430023322482503</v>
+        <v>0.96721088014367096</v>
       </c>
       <c r="Q2" t="b">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>0.83046812929889602</v>
+        <v>0.92285396534869102</v>
       </c>
       <c r="S2">
-        <v>12.9196804267342</v>
+        <v>9.8571957579962302</v>
       </c>
       <c r="T2">
-        <v>0.93430023322482503</v>
+        <v>0.96721088014367096</v>
       </c>
       <c r="U2">
-        <v>0.16527049029912699</v>
+        <v>2.6101743222462202E-2</v>
       </c>
       <c r="V2">
-        <v>6.7146937504072799</v>
+        <v>0.34003042523030902</v>
       </c>
       <c r="X2">
-        <v>-523.72658474291404</v>
+        <v>-632.77451196780601</v>
       </c>
       <c r="Y2">
-        <v>19.6561286472419</v>
+        <v>16.501360631762299</v>
       </c>
       <c r="Z2">
-        <v>3.5094676140463998</v>
+        <v>3.2221389594992398</v>
       </c>
       <c r="AA2">
-        <v>-0.16772005526266701</v>
+        <v>-0.12947072348824501</v>
       </c>
       <c r="AB2" t="e">
         <v>#NUM!</v>
@@ -2982,210 +2224,216 @@
         <v>#NUM!</v>
       </c>
       <c r="AD2">
-        <v>0.94733201371943399</v>
+        <v>0.904397245715298</v>
       </c>
       <c r="AE2">
-        <v>0.94792373972235799</v>
+        <v>0.94341633750407405</v>
       </c>
       <c r="AF2">
-        <v>8.1716749422302506</v>
+        <v>10.097633577486301</v>
       </c>
       <c r="AG2">
-        <v>7.2602179508498201</v>
+        <v>7.9095086704082798</v>
       </c>
       <c r="AH2">
-        <v>-792.42114620335803</v>
+        <v>-621.19410312843195</v>
       </c>
       <c r="AI2">
-        <v>19.6561286472419</v>
+        <v>17.3625403171568</v>
       </c>
       <c r="AJ2">
-        <v>2.9680058443498001</v>
+        <v>3.3670975167658801</v>
       </c>
       <c r="AN2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AP2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AR2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AT2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AV2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AW2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AX2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AZ2">
         <v>19</v>
       </c>
       <c r="BA2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BB2">
         <v>38</v>
       </c>
       <c r="BC2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BD2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BE2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF2">
-        <v>-792.42114620335803</v>
+        <v>96</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>103</v>
       </c>
       <c r="BG2">
-        <v>19.6561286472419</v>
+        <v>-621.19410312843195</v>
       </c>
       <c r="BH2">
-        <v>2.9680058443498001</v>
-      </c>
-      <c r="BK2">
-        <v>197.18043274401001</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>102</v>
+        <v>17.3625403171568</v>
+      </c>
+      <c r="BI2">
+        <v>3.3670975167658801</v>
+      </c>
+      <c r="BL2">
+        <v>214.345370555778</v>
       </c>
       <c r="BM2" t="s">
-        <v>96</v>
-      </c>
-      <c r="BN2">
-        <v>-632.55944419763898</v>
+        <v>104</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>97</v>
       </c>
       <c r="BO2">
-        <v>17.453646855525299</v>
+        <v>-621.92898641646696</v>
       </c>
       <c r="BP2">
+        <v>16.781721765066099</v>
+      </c>
+      <c r="BQ2">
         <v>3.2013877327939699</v>
       </c>
-      <c r="BQ2">
-        <v>-0.134158727071815</v>
-      </c>
-      <c r="BT2">
-        <v>989.60157894736801</v>
+      <c r="BR2">
+        <v>-0.12433687358266</v>
       </c>
       <c r="BU2">
-        <v>357.04213474973</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>103</v>
+        <v>835.53947368421098</v>
+      </c>
+      <c r="BV2">
+        <v>213.61048726774399</v>
       </c>
       <c r="BW2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BX2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BY2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BZ2">
+        <v>106</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CA2">
         <v>0.41471265136089402</v>
       </c>
-      <c r="CA2">
+      <c r="CB2">
         <v>9.3447395609349004E-2</v>
       </c>
-      <c r="CC2">
-        <v>197.18043274401001</v>
-      </c>
       <c r="CD2">
-        <v>0.97646206530456303</v>
-      </c>
-      <c r="CF2">
+        <v>214.345370555778</v>
+      </c>
+      <c r="CE2">
+        <v>0.96164322004108904</v>
+      </c>
+      <c r="CG2">
         <v>1</v>
       </c>
-      <c r="CG2">
-        <v>379.99149295325202</v>
+      <c r="CH2">
+        <v>16.377171238468001</v>
       </c>
       <c r="CI2">
-        <v>0.76574257821147196</v>
+        <v>1.2178919907250301</v>
+      </c>
+      <c r="CJ2">
+        <v>0.20500235766852901</v>
       </c>
     </row>
-    <row r="3" spans="1:90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:91" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3">
-        <v>1200</v>
+        <v>1099</v>
       </c>
       <c r="I3">
         <v>0.1</v>
       </c>
       <c r="J3">
-        <v>0.83046812929889602</v>
+        <v>0.92285396534869102</v>
       </c>
       <c r="K3">
-        <v>12.9196804267342</v>
+        <v>9.8571957579962302</v>
       </c>
       <c r="L3">
-        <v>0.93430023322482503</v>
+        <v>0.96721088014367096</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3">
-        <v>0.83046812929889602</v>
+        <v>0.92285396534869102</v>
       </c>
       <c r="O3">
-        <v>12.9196804267342</v>
+        <v>9.8571957579962302</v>
       </c>
       <c r="P3">
-        <v>0.93430023322482503</v>
+        <v>0.96721088014367096</v>
       </c>
       <c r="Q3" t="b">
         <v>1</v>
       </c>
       <c r="R3">
-        <v>0.83046812929889602</v>
+        <v>0.92285396534869102</v>
       </c>
       <c r="S3">
-        <v>12.9196804267342</v>
+        <v>9.8571957579962302</v>
       </c>
       <c r="T3">
-        <v>0.93430023322482503</v>
+        <v>0.96721088014367096</v>
       </c>
       <c r="U3">
-        <v>0.16527049029912699</v>
+        <v>2.6101743222462202E-2</v>
       </c>
       <c r="V3">
-        <v>6.7146937504072799</v>
+        <v>0.34003042523030902</v>
       </c>
       <c r="X3">
-        <v>-523.72658474291404</v>
+        <v>-632.77451196780601</v>
       </c>
       <c r="Y3">
-        <v>19.6561286472419</v>
+        <v>16.501360631762299</v>
       </c>
       <c r="Z3">
-        <v>3.5094676140463998</v>
+        <v>3.2221389594992398</v>
       </c>
       <c r="AA3">
-        <v>-0.16772005526266701</v>
+        <v>-0.12947072348824501</v>
       </c>
       <c r="AB3" t="e">
         <v>#NUM!</v>
@@ -3194,1243 +2442,590 @@
         <v>#NUM!</v>
       </c>
       <c r="AD3">
-        <v>0.71360424487835705</v>
+        <v>0.94131068498208403</v>
       </c>
       <c r="AE3">
-        <v>0.68906754069799803</v>
+        <v>0.92791452499900495</v>
       </c>
       <c r="AF3">
-        <v>17.667685911238099</v>
+        <v>9.6167579385061295</v>
       </c>
       <c r="AG3">
-        <v>18.8912907744356</v>
+        <v>8.9699253528807503</v>
       </c>
       <c r="AH3">
-        <v>-255.03202328246999</v>
+        <v>-644.35492080717995</v>
+      </c>
+      <c r="AI3">
+        <v>15.640180946367799</v>
       </c>
       <c r="AJ3">
-        <v>4.050929383743</v>
+        <v>3.0771804022325902</v>
       </c>
       <c r="AK3">
-        <v>-0.16772005526266701</v>
+        <v>-0.12947072348824501</v>
       </c>
       <c r="AN3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AR3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AT3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AV3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AW3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AX3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AZ3">
         <v>19</v>
       </c>
       <c r="BA3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BB3">
         <v>38</v>
       </c>
       <c r="BC3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BD3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BE3" t="s">
+        <v>108</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG3">
+        <v>-644.35492080717995</v>
+      </c>
+      <c r="BH3">
+        <v>15.640180946367799</v>
+      </c>
+      <c r="BI3">
+        <v>3.0771804022325902</v>
+      </c>
+      <c r="BJ3">
+        <v>-0.12947072348824501</v>
+      </c>
+      <c r="BK3">
+        <v>-0.12947072348824501</v>
+      </c>
+      <c r="BL3">
+        <v>270.65876340334597</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO3">
+        <v>-621.92898641646696</v>
+      </c>
+      <c r="BP3">
+        <v>16.781721765066099</v>
+      </c>
+      <c r="BQ3">
+        <v>3.2013877327939699</v>
+      </c>
+      <c r="BR3">
+        <v>-0.12433687358266</v>
+      </c>
+      <c r="BU3">
+        <v>915.01368421052598</v>
+      </c>
+      <c r="BV3">
+        <v>293.08469779405903</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BY3" t="s">
         <v>106</v>
       </c>
-      <c r="BF3">
-        <v>-255.03202328246999</v>
-      </c>
-      <c r="BH3">
-        <v>4.050929383743</v>
-      </c>
-      <c r="BI3">
-        <v>-0.16772005526266701</v>
-      </c>
-      <c r="BJ3">
-        <v>-0.16772005526266701</v>
-      </c>
-      <c r="BK3">
-        <v>505.91955566489901</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>102</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BN3">
-        <v>-632.55944419763898</v>
-      </c>
-      <c r="BO3">
-        <v>17.453646855525299</v>
-      </c>
-      <c r="BP3">
-        <v>3.2013877327939699</v>
-      </c>
-      <c r="BQ3">
-        <v>-0.134158727071815</v>
-      </c>
-      <c r="BT3">
-        <v>760.95157894736803</v>
-      </c>
-      <c r="BU3">
-        <v>128.39213474972999</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>103</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>103</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>104</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>105</v>
-      </c>
-      <c r="BZ3">
+      <c r="BZ3" t="s">
+        <v>107</v>
+      </c>
+      <c r="CA3">
         <v>0.41471265136089402</v>
       </c>
-      <c r="CA3">
+      <c r="CB3">
         <v>9.3447395609349004E-2</v>
       </c>
-      <c r="CC3">
-        <v>505.91955566489901</v>
-      </c>
       <c r="CD3">
-        <v>0.89213840114508702</v>
-      </c>
-      <c r="CF3">
+        <v>270.65876340334597</v>
+      </c>
+      <c r="CE3">
+        <v>0.97277854024625399</v>
+      </c>
+      <c r="CG3">
         <v>1</v>
       </c>
-      <c r="CG3">
-        <v>379.99149295325202</v>
+      <c r="CH3">
+        <v>16.377171238468001</v>
       </c>
       <c r="CI3">
-        <v>0.76574257821147196</v>
+        <v>1.2178919907250301</v>
+      </c>
+      <c r="CJ3">
+        <v>0.20500235766852901</v>
       </c>
     </row>
-    <row r="4" spans="1:90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:91" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1200</v>
+        <v>1001</v>
       </c>
       <c r="I4">
         <v>0.1</v>
       </c>
       <c r="J4">
-        <v>0.83046812929889602</v>
+        <v>0.89622859571165403</v>
       </c>
       <c r="K4">
-        <v>12.9196804267342</v>
+        <v>10.3475336075009</v>
       </c>
       <c r="L4">
-        <v>0.93430023322482503</v>
+        <v>0.95875869086416399</v>
       </c>
       <c r="M4" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0.92285396534869102</v>
+      </c>
+      <c r="O4">
+        <v>9.8571957579962302</v>
+      </c>
+      <c r="P4">
+        <v>0.96721088014367096</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>-0.32876631361057901</v>
+        <v>0.89622859571165403</v>
       </c>
       <c r="S4">
-        <v>33.3423292157213</v>
+        <v>10.3475336075009</v>
       </c>
       <c r="T4">
-        <v>0.51638466339185196</v>
+        <v>0.95875869086416399</v>
       </c>
       <c r="U4">
-        <v>1.4835698757575999</v>
+        <v>3.54795897381565E-2</v>
       </c>
       <c r="V4">
-        <v>25.4042002747867</v>
+        <v>1.3462851339108799</v>
       </c>
       <c r="X4">
-        <v>-5.3947368421052602</v>
-      </c>
-      <c r="Y4" t="e">
-        <v>#NUM!</v>
+        <v>-333.03677815492699</v>
+      </c>
+      <c r="Y4">
+        <v>15.271227281443901</v>
       </c>
       <c r="Z4">
-        <v>0.38700647742010602</v>
+        <v>2.6909265905565598</v>
       </c>
       <c r="AA4" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AB4" t="e">
-        <v>#NUM!</v>
+      <c r="AB4">
+        <v>-1.58954753533072</v>
       </c>
       <c r="AC4" t="e">
         <v>#NUM!</v>
       </c>
       <c r="AD4">
-        <v>-2.26270276997167</v>
+        <v>0.858213282451469</v>
       </c>
       <c r="AE4">
-        <v>-3.4656198325313099</v>
+        <v>0.81747640298829205</v>
       </c>
       <c r="AF4">
-        <v>64.317104056111205</v>
+        <v>12.3143716210182</v>
       </c>
       <c r="AG4">
-        <v>67.231165148396002</v>
+        <v>13.4485813736372</v>
       </c>
       <c r="AH4">
-        <v>-5.3947368421052602</v>
+        <v>-196.434177805242</v>
+      </c>
+      <c r="AI4">
+        <v>12.407971813021399</v>
       </c>
       <c r="AJ4">
-        <v>0.226921743803353</v>
+        <v>2.4738860449713198</v>
+      </c>
+      <c r="AL4">
+        <v>-2.00117125918882</v>
       </c>
       <c r="AN4" t="s">
         <v>109</v>
       </c>
       <c r="AP4" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="AR4" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="AT4" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AV4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AW4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AX4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BB4">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="BC4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BD4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BE4" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF4">
-        <v>-5.3947368421052602</v>
+        <v>111</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BG4">
+        <v>-196.434177805242</v>
       </c>
       <c r="BH4">
-        <v>0.226921743803353</v>
-      </c>
-      <c r="BK4">
-        <v>1144.6052617179</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>110</v>
+        <v>12.407971813021399</v>
+      </c>
+      <c r="BI4">
+        <v>2.4738860449713198</v>
+      </c>
+      <c r="BL4">
+        <v>775.39115552809096</v>
       </c>
       <c r="BM4" t="s">
-        <v>96</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>111</v>
+        <v>115</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>112</v>
+      </c>
+      <c r="BO4">
+        <v>-372.76254231886702</v>
+      </c>
+      <c r="BP4">
+        <v>15.3397687479594</v>
+      </c>
+      <c r="BQ4">
+        <v>2.7229618075238502</v>
+      </c>
+      <c r="BS4">
+        <v>-1.4136282763791399</v>
+      </c>
+      <c r="BU4">
+        <v>971.82533333333299</v>
+      </c>
+      <c r="BV4">
+        <v>599.06279101446603</v>
       </c>
       <c r="BW4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BX4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BY4" t="s">
-        <v>111</v>
-      </c>
-      <c r="CC4">
-        <v>1144.6052617179</v>
+        <v>117</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>118</v>
+      </c>
+      <c r="CA4">
+        <v>0.38171324435600901</v>
       </c>
       <c r="CD4">
-        <v>3.8000458482671598E-2</v>
-      </c>
-      <c r="CF4">
+        <v>775.39115552809096</v>
+      </c>
+      <c r="CE4">
+        <v>0.94151946655769703</v>
+      </c>
+      <c r="CG4">
         <v>1</v>
       </c>
+      <c r="CH4">
+        <v>193.185250069956</v>
+      </c>
       <c r="CI4">
-        <v>0.22639400140969701</v>
+        <v>4.0492547159819896</v>
+      </c>
+      <c r="CJ4">
+        <v>0.30694168315150799</v>
+      </c>
+      <c r="CL4">
+        <v>0.58212385287465496</v>
       </c>
     </row>
-    <row r="5" spans="1:90" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:91" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
       <c r="H5">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I5">
         <v>0.1</v>
       </c>
       <c r="J5">
-        <v>0.83046812929889602</v>
+        <v>0.89622859571165403</v>
       </c>
       <c r="K5">
-        <v>12.9196804267342</v>
+        <v>10.3475336075009</v>
       </c>
       <c r="L5">
-        <v>0.93430023322482503</v>
+        <v>0.95875869086416399</v>
       </c>
       <c r="M5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0.92285396534869102</v>
+      </c>
+      <c r="O5">
+        <v>9.8571957579962302</v>
+      </c>
+      <c r="P5">
+        <v>0.96721088014367096</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>-0.32876631361057901</v>
+        <v>0.89622859571165403</v>
       </c>
       <c r="S5">
-        <v>33.3423292157213</v>
+        <v>10.3475336075009</v>
       </c>
       <c r="T5">
-        <v>0.51638466339185196</v>
+        <v>0.95875869086416399</v>
       </c>
       <c r="U5">
-        <v>1.4835698757575999</v>
+        <v>3.54795897381565E-2</v>
       </c>
       <c r="V5">
-        <v>25.4042002747867</v>
+        <v>1.3462851339108799</v>
       </c>
       <c r="X5">
-        <v>-5.3947368421052602</v>
-      </c>
-      <c r="Y5" t="e">
-        <v>#NUM!</v>
+        <v>-333.03677815492699</v>
+      </c>
+      <c r="Y5">
+        <v>15.271227281443901</v>
       </c>
       <c r="Z5">
-        <v>0.38700647742010602</v>
+        <v>2.6909265905565598</v>
       </c>
       <c r="AA5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#NUM!</v>
+      <c r="AB5">
+        <v>-1.58954753533072</v>
       </c>
       <c r="AC5" t="e">
         <v>#NUM!</v>
       </c>
       <c r="AD5">
-        <v>-0.71329874306843799</v>
+        <v>0.88099316969776598</v>
       </c>
       <c r="AE5">
-        <v>-0.125157203050455</v>
+        <v>0.92419637789298603</v>
       </c>
       <c r="AF5">
-        <v>43.212851953305602</v>
+        <v>9.36137129299291</v>
       </c>
       <c r="AG5">
-        <v>35.936452588578</v>
+        <v>7.4872982873871701</v>
+      </c>
+      <c r="AH5">
+        <v>-469.63937850461201</v>
+      </c>
+      <c r="AI5">
+        <v>18.134482749866301</v>
       </c>
       <c r="AJ5">
-        <v>0.54709121103685998</v>
+        <v>2.90796713614181</v>
+      </c>
+      <c r="AL5">
+        <v>-1.17792381147261</v>
       </c>
       <c r="AN5" t="s">
         <v>109</v>
       </c>
       <c r="AP5" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="AR5" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="AT5" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AV5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AW5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AX5" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BB5">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="BC5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BD5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BE5" t="s">
-        <v>106</v>
+        <v>119</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>113</v>
+      </c>
+      <c r="BG5">
+        <v>-469.63937850461201</v>
       </c>
       <c r="BH5">
-        <v>0.54709121103685998</v>
-      </c>
-      <c r="BK5">
-        <v>622.50001052983896</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>110</v>
+        <v>18.134482749866301</v>
+      </c>
+      <c r="BI5">
+        <v>2.90796713614181</v>
+      </c>
+      <c r="BL5">
+        <v>466.55624649538697</v>
       </c>
       <c r="BM5" t="s">
-        <v>96</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>111</v>
+        <v>120</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>112</v>
+      </c>
+      <c r="BO5">
+        <v>-372.41991957109298</v>
+      </c>
+      <c r="BP5">
+        <v>15.3397687479594</v>
+      </c>
+      <c r="BQ5">
+        <v>2.7229618075238502</v>
+      </c>
+      <c r="BS5">
+        <v>-1.4136282763791399</v>
+      </c>
+      <c r="BU5">
+        <v>936.19562499999995</v>
+      </c>
+      <c r="BV5">
+        <v>563.77570542890703</v>
       </c>
       <c r="BW5" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="BX5" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="BY5" t="s">
-        <v>111</v>
-      </c>
-      <c r="CC5">
-        <v>622.50001052983896</v>
+        <v>122</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>123</v>
+      </c>
+      <c r="CA5">
+        <v>0.38171324435600901</v>
       </c>
       <c r="CD5">
-        <v>0.15893772863508801</v>
-      </c>
-      <c r="CF5">
+        <v>466.55624649538697</v>
+      </c>
+      <c r="CE5">
+        <v>0.959093536611616</v>
+      </c>
+      <c r="CG5">
         <v>1</v>
       </c>
+      <c r="CH5">
+        <v>193.185250069956</v>
+      </c>
       <c r="CI5">
-        <v>0.22639400140969701</v>
-      </c>
-    </row>
-    <row r="6" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1200</v>
-      </c>
-      <c r="I6">
-        <v>0.1</v>
-      </c>
-      <c r="J6">
-        <v>8.8030112637406302E-2</v>
-      </c>
-      <c r="K6">
-        <v>25.4024968592257</v>
-      </c>
-      <c r="L6">
-        <v>0.66632748962552601</v>
-      </c>
-      <c r="M6" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>0.83046812929889602</v>
-      </c>
-      <c r="O6">
-        <v>12.9196804267342</v>
-      </c>
-      <c r="P6">
-        <v>0.93430023322482503</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>8.8030112637406302E-2</v>
-      </c>
-      <c r="S6">
-        <v>25.4024968592257</v>
-      </c>
-      <c r="T6">
-        <v>0.66632748962552601</v>
-      </c>
-      <c r="U6">
-        <v>1.31843724885147</v>
-      </c>
-      <c r="V6">
-        <v>23.306390527962101</v>
-      </c>
-      <c r="X6">
-        <v>-414.09257240753101</v>
-      </c>
-      <c r="Y6">
-        <v>-0.53342845613260004</v>
-      </c>
-      <c r="Z6">
-        <v>3.1338786203963802</v>
-      </c>
-      <c r="AA6">
-        <v>-0.31477599844463899</v>
-      </c>
-      <c r="AB6" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AC6" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AD6">
-        <v>0.87795354887985599</v>
-      </c>
-      <c r="AE6">
-        <v>0.85935627531769898</v>
-      </c>
-      <c r="AF6">
-        <v>12.938075052234</v>
-      </c>
-      <c r="AG6">
-        <v>13.0422455412196</v>
-      </c>
-      <c r="AH6">
-        <v>-446.310415879365</v>
-      </c>
-      <c r="AJ6">
-        <v>3.3324585662639401</v>
-      </c>
-      <c r="AK6">
-        <v>-0.26185669279599599</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>112</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>97</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AZ6">
-        <v>19</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>99</v>
-      </c>
-      <c r="BB6">
-        <v>38</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>100</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>101</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>113</v>
-      </c>
-      <c r="BF6">
-        <v>-446.310415879365</v>
-      </c>
-      <c r="BG6">
-        <v>0.27412985470394202</v>
-      </c>
-      <c r="BH6">
-        <v>3.3324585662639401</v>
-      </c>
-      <c r="BI6">
-        <v>-0.26185669279599599</v>
-      </c>
-      <c r="BJ6">
-        <v>-0.26185669279599599</v>
-      </c>
-      <c r="BK6">
-        <v>471.61326833116101</v>
-      </c>
-      <c r="BL6" t="s">
-        <v>115</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>96</v>
-      </c>
-      <c r="BN6">
-        <v>-467.71300486298702</v>
-      </c>
-      <c r="BO6">
-        <v>-1.0053923475541</v>
-      </c>
-      <c r="BP6">
-        <v>3.1465960102752799</v>
-      </c>
-      <c r="BQ6">
-        <v>-0.17542257842859901</v>
-      </c>
-      <c r="BT6">
-        <v>917.92368421052595</v>
-      </c>
-      <c r="BU6">
-        <v>450.21067934753898</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>117</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>118</v>
-      </c>
-      <c r="BZ6">
-        <v>0.41471265136089402</v>
-      </c>
-      <c r="CA6">
-        <v>9.3447395609349004E-2</v>
-      </c>
-      <c r="CC6">
-        <v>471.61326833116101</v>
-      </c>
-      <c r="CD6">
-        <v>0.94665820375000398</v>
-      </c>
-      <c r="CF6">
-        <v>1</v>
-      </c>
-      <c r="CG6">
-        <v>45.562911188282001</v>
-      </c>
-      <c r="CI6">
-        <v>0.28083445266121698</v>
-      </c>
-      <c r="CJ6">
-        <v>7.4839199759677594E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>1200</v>
-      </c>
-      <c r="I7">
-        <v>0.1</v>
-      </c>
-      <c r="J7">
-        <v>8.8030112637406302E-2</v>
-      </c>
-      <c r="K7">
-        <v>25.4024968592257</v>
-      </c>
-      <c r="L7">
-        <v>0.66632748962552601</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>0.83046812929889602</v>
-      </c>
-      <c r="O7">
-        <v>12.9196804267342</v>
-      </c>
-      <c r="P7">
-        <v>0.93430023322482503</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>8.8030112637406302E-2</v>
-      </c>
-      <c r="S7">
-        <v>25.4024968592257</v>
-      </c>
-      <c r="T7">
-        <v>0.66632748962552601</v>
-      </c>
-      <c r="U7">
-        <v>1.31843724885147</v>
-      </c>
-      <c r="V7">
-        <v>23.306390527962101</v>
-      </c>
-      <c r="X7">
-        <v>-414.09257240753101</v>
-      </c>
-      <c r="Y7">
-        <v>-0.53342845613260004</v>
-      </c>
-      <c r="Z7">
-        <v>3.1338786203963802</v>
-      </c>
-      <c r="AA7">
-        <v>-0.31477599844463899</v>
-      </c>
-      <c r="AB7" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AC7" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AD7">
-        <v>0.96529238138689599</v>
-      </c>
-      <c r="AE7">
-        <v>0.98371504468860904</v>
-      </c>
-      <c r="AF7">
-        <v>6.1075892402352903</v>
-      </c>
-      <c r="AG7">
-        <v>3.8593654361033298</v>
-      </c>
-      <c r="AH7">
-        <v>-381.874728935696</v>
-      </c>
-      <c r="AI7">
-        <v>-0.53342845613260004</v>
-      </c>
-      <c r="AJ7">
-        <v>2.9352986745288199</v>
-      </c>
-      <c r="AK7">
-        <v>-0.36769530409328099</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>112</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>119</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>120</v>
-      </c>
-      <c r="AZ7">
-        <v>19</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>99</v>
-      </c>
-      <c r="BB7">
-        <v>38</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>100</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>101</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>119</v>
-      </c>
-      <c r="BF7">
-        <v>-381.874728935696</v>
-      </c>
-      <c r="BG7">
-        <v>-0.53342845613260004</v>
-      </c>
-      <c r="BH7">
-        <v>2.9352986745288199</v>
-      </c>
-      <c r="BI7">
-        <v>-0.36769530409328099</v>
-      </c>
-      <c r="BJ7">
-        <v>-0.36769530409328099</v>
-      </c>
-      <c r="BK7">
-        <v>450.75474474851399</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>121</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>96</v>
-      </c>
-      <c r="BN7">
-        <v>-468.16076000047798</v>
-      </c>
-      <c r="BO7">
-        <v>-0.962715116962511</v>
-      </c>
-      <c r="BP7">
-        <v>3.1465960102752799</v>
-      </c>
-      <c r="BQ7">
-        <v>-0.17542257842859901</v>
-      </c>
-      <c r="BT7">
-        <v>832.62947368420998</v>
-      </c>
-      <c r="BU7">
-        <v>364.46871368373201</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW7" t="s">
-        <v>122</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>123</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>124</v>
-      </c>
-      <c r="BZ7">
-        <v>0.41471265136089402</v>
-      </c>
-      <c r="CA7">
-        <v>9.3447395609349004E-2</v>
-      </c>
-      <c r="CC7">
-        <v>450.75474474851399</v>
-      </c>
-      <c r="CD7">
-        <v>0.98576808043574504</v>
-      </c>
-      <c r="CF7">
-        <v>1</v>
-      </c>
-      <c r="CG7">
-        <v>45.562911188282001</v>
-      </c>
-      <c r="CI7">
-        <v>0.28083445266121698</v>
-      </c>
-      <c r="CJ7">
-        <v>7.4839199759677594E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="B8">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1200</v>
-      </c>
-      <c r="I8">
-        <v>0.1</v>
-      </c>
-      <c r="J8">
-        <v>8.8030112637406302E-2</v>
-      </c>
-      <c r="K8">
-        <v>25.4024968592257</v>
-      </c>
-      <c r="L8">
-        <v>0.66632748962552601</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>-1.7815675368989599E-2</v>
-      </c>
-      <c r="S8">
-        <v>29.0832082521861</v>
-      </c>
-      <c r="T8">
-        <v>0.542480931051604</v>
-      </c>
-      <c r="U8">
-        <v>1.1344976742402499</v>
-      </c>
-      <c r="V8">
-        <v>20.843271848838899</v>
-      </c>
-      <c r="X8" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="Y8" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="Z8">
-        <v>0.44800244214162699</v>
-      </c>
-      <c r="AA8" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AB8" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AC8" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AD8">
-        <v>-0.178300541681365</v>
-      </c>
-      <c r="AE8">
-        <v>-7.2032065209952603E-2</v>
-      </c>
-      <c r="AF8">
-        <v>40.200839928858002</v>
-      </c>
-      <c r="AG8">
-        <v>36.007757935167298</v>
-      </c>
-      <c r="AJ8">
-        <v>0.38367692581450202</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>113</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>97</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AZ8">
-        <v>19</v>
-      </c>
-      <c r="BA8" t="s">
-        <v>99</v>
-      </c>
-      <c r="BB8">
-        <v>38</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>100</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>101</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>113</v>
-      </c>
-      <c r="BH8">
-        <v>0.38367692581450202</v>
-      </c>
-      <c r="BK8">
-        <v>713.99998640545095</v>
-      </c>
-      <c r="BL8" t="s">
-        <v>125</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>96</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>111</v>
-      </c>
-      <c r="BW8" t="s">
-        <v>111</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>111</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>111</v>
-      </c>
-      <c r="CC8">
-        <v>713.99998640545095</v>
-      </c>
-      <c r="CD8">
-        <v>0.14307045164062401</v>
-      </c>
-      <c r="CF8">
-        <v>1</v>
-      </c>
-      <c r="CI8">
-        <v>9.0970017596472594E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="B9">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>1200</v>
-      </c>
-      <c r="I9">
-        <v>0.1</v>
-      </c>
-      <c r="J9">
-        <v>8.8030112637406302E-2</v>
-      </c>
-      <c r="K9">
-        <v>25.4024968592257</v>
-      </c>
-      <c r="L9">
-        <v>0.66632748962552601</v>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>-1.7815675368989599E-2</v>
-      </c>
-      <c r="S9">
-        <v>29.0832082521861</v>
-      </c>
-      <c r="T9">
-        <v>0.542480931051604</v>
-      </c>
-      <c r="U9">
-        <v>1.1344976742402499</v>
-      </c>
-      <c r="V9">
-        <v>20.843271848838899</v>
-      </c>
-      <c r="X9" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="Y9" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="Z9">
-        <v>0.44800244214162699</v>
-      </c>
-      <c r="AA9" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AB9" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AC9" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="AD9">
-        <v>-0.49240553709499002</v>
-      </c>
-      <c r="AE9">
-        <v>3.5669308170445398E-2</v>
-      </c>
-      <c r="AF9">
-        <v>40.049844933276802</v>
-      </c>
-      <c r="AG9">
-        <v>29.698575046886901</v>
-      </c>
-      <c r="AJ9">
-        <v>0.51232795846875201</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>112</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>119</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>97</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>120</v>
-      </c>
-      <c r="AZ9">
-        <v>19</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>99</v>
-      </c>
-      <c r="BB9">
-        <v>38</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>100</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>101</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>119</v>
-      </c>
-      <c r="BH9">
-        <v>0.51232795846875201</v>
-      </c>
-      <c r="BK9">
-        <v>629.50002458808797</v>
-      </c>
-      <c r="BL9" t="s">
-        <v>125</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>111</v>
-      </c>
-      <c r="BW9" t="s">
-        <v>111</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>111</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>111</v>
-      </c>
-      <c r="CC9">
-        <v>629.50002458808797</v>
-      </c>
-      <c r="CD9">
-        <v>0.198812059019052</v>
-      </c>
-      <c r="CF9">
-        <v>1</v>
-      </c>
-      <c r="CI9">
-        <v>9.0970017596472594E-2</v>
+        <v>4.0492547159819896</v>
+      </c>
+      <c r="CJ5">
+        <v>0.30694168315150799</v>
+      </c>
+      <c r="CL5">
+        <v>0.58212385287465496</v>
       </c>
     </row>
   </sheetData>

--- a/Figures.out/gbr_out_sheep_lon.xlsx
+++ b/Figures.out/gbr_out_sheep_lon.xlsx
@@ -1,340 +1,422 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\DMI.prediction\R\Figures.out\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B99231273C29E3BD4895A99233DD1C34C21F59DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="124">
-  <si>
-    <t>matrix.NA..nrow...n.rows..ncol...1.</t>
-  </si>
-  <si>
-    <t>loop.iter</t>
-  </si>
-  <si>
-    <t>species</t>
-  </si>
-  <si>
-    <t>ndf</t>
-  </si>
-  <si>
-    <t>mod.form</t>
-  </si>
-  <si>
-    <t>mod.vers</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>m.stop</t>
-  </si>
-  <si>
-    <t>nu</t>
-  </si>
-  <si>
-    <t>best.w.R2</t>
-  </si>
-  <si>
-    <t>best.w.nRMSE</t>
-  </si>
-  <si>
-    <t>best.w.CCC</t>
-  </si>
-  <si>
-    <t>is.best.model</t>
-  </si>
-  <si>
-    <t>best.global.w.R2</t>
-  </si>
-  <si>
-    <t>best.global.w.nRMSE</t>
-  </si>
-  <si>
-    <t>best.global.w.CCC</t>
-  </si>
-  <si>
-    <t>is.best.global.model</t>
-  </si>
-  <si>
-    <t>w.R2.mean</t>
-  </si>
-  <si>
-    <t>w.nRMSE.mean</t>
-  </si>
-  <si>
-    <t>w.CCC.mean</t>
-  </si>
-  <si>
-    <t>w.R2.sd</t>
-  </si>
-  <si>
-    <t>w.nRMSE.sd</t>
-  </si>
-  <si>
-    <t>w.CCC.sd</t>
-  </si>
-  <si>
-    <t>mean.coef.int</t>
-  </si>
-  <si>
-    <t>mean.coef.BW</t>
-  </si>
-  <si>
-    <t>mean.coef.ADG</t>
-  </si>
-  <si>
-    <t>mean.coef.NDF</t>
-  </si>
-  <si>
-    <t>mean.coef.CP</t>
-  </si>
-  <si>
-    <t>mean.coef.NDF_digest</t>
-  </si>
-  <si>
-    <t>test.r2</t>
-  </si>
-  <si>
-    <t>test.w.r2</t>
-  </si>
-  <si>
-    <t>test.nrmse</t>
-  </si>
-  <si>
-    <t>test.w.nrmse</t>
-  </si>
-  <si>
-    <t>coef.int</t>
-  </si>
-  <si>
-    <t>coef.BW</t>
-  </si>
-  <si>
-    <t>coef.ADG</t>
-  </si>
-  <si>
-    <t>coef.NDF</t>
-  </si>
-  <si>
-    <t>coef.CP</t>
-  </si>
-  <si>
-    <t>coef.NDF_digest</t>
-  </si>
-  <si>
-    <t>observed.Y</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+  <si>
+    <t xml:space="preserve">matrix.NA..nrow...n.rows..ncol...1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loop.iter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">species</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ndf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod.form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mod.vers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m.stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best.w.R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best.w.nRMSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best.w.CCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is.best.model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best.global.w.R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best.global.w.nRMSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best.global.w.CCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is.best.global.model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.R2.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.nRMSE.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.CCC.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.R2.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.nRMSE.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.CCC.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.coef.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.coef.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.coef.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.coef.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.coef.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.coef.NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.r2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.w.r2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.nrmse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.w.nrmse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef.NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">observed.Y</t>
   </si>
   <si>
     <t xml:space="preserve"> mod.Y </t>
   </si>
   <si>
-    <t>gbr.form</t>
-  </si>
-  <si>
-    <t>total.sample</t>
-  </si>
-  <si>
-    <t>k.IDs</t>
-  </si>
-  <si>
-    <t>sample.size</t>
-  </si>
-  <si>
-    <t>treatment.IDs.CCs</t>
-  </si>
-  <si>
-    <t>all.treatment.IDs</t>
-  </si>
-  <si>
-    <t>treatment.IDs</t>
-  </si>
-  <si>
-    <t>experiment.IDs</t>
-  </si>
-  <si>
-    <t>train.IDs</t>
+    <t xml:space="preserve">gbr.form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total.sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k.IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sample.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treatment.IDs.CCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all.treatment.IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treatment.IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">experiment.IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train.IDs</t>
   </si>
   <si>
     <t xml:space="preserve">k.IDs.length </t>
   </si>
   <si>
-    <t>train.IDs.length</t>
-  </si>
-  <si>
-    <t>species.ndf</t>
-  </si>
-  <si>
-    <t>total.sample.size</t>
-  </si>
-  <si>
-    <t>weight.list</t>
-  </si>
-  <si>
-    <t>IDs.remaining</t>
-  </si>
-  <si>
-    <t>k.IDs.length</t>
-  </si>
-  <si>
-    <t>test.IDs</t>
-  </si>
-  <si>
-    <t>gbr.model.train.coef.int</t>
-  </si>
-  <si>
-    <t>gbr.model.train.coef.BW</t>
-  </si>
-  <si>
-    <t>gbr.model.train.coef.ADG</t>
-  </si>
-  <si>
-    <t>gbr.model.train.coef.NDF</t>
-  </si>
-  <si>
-    <t>gbr.model.train.coef.NDF*Digest</t>
-  </si>
-  <si>
-    <t>gbr.model.train.coef.offset.plus.intercept</t>
-  </si>
-  <si>
-    <t>gbr.whole.sample</t>
-  </si>
-  <si>
-    <t>ws.ut.ids</t>
-  </si>
-  <si>
-    <t>ws.coef.intercept</t>
-  </si>
-  <si>
-    <t>ws.coef.bw_kg</t>
-  </si>
-  <si>
-    <t>ws.coef.adg_g_day</t>
-  </si>
-  <si>
-    <t>ws.coef.NDF_nutrition</t>
-  </si>
-  <si>
-    <t>ws.coef.CP_nutrition</t>
-  </si>
-  <si>
-    <t>ws.coef.NDF_digest</t>
-  </si>
-  <si>
-    <t>ws.coef.offset</t>
-  </si>
-  <si>
-    <t>ws.coef.offset.plus.intercept</t>
-  </si>
-  <si>
-    <t>ws.predicted</t>
-  </si>
-  <si>
-    <t>ws.predicted.base</t>
-  </si>
-  <si>
-    <t>ws.residuals</t>
-  </si>
-  <si>
-    <t>ws.rms.residuals</t>
-  </si>
-  <si>
-    <t>var.corr.bw.adg</t>
-  </si>
-  <si>
-    <t>var.corr.bw.ndf</t>
-  </si>
-  <si>
-    <t>coef.NDF_Digest</t>
-  </si>
-  <si>
-    <t>coef.offset.plus.intercept</t>
-  </si>
-  <si>
-    <t>test.ccc</t>
-  </si>
-  <si>
-    <t>w.AIC.mean</t>
-  </si>
-  <si>
-    <t>test.w.coef.bw.sd</t>
-  </si>
-  <si>
-    <t>sd.coef.int</t>
-  </si>
-  <si>
-    <t>sd.coef.BW</t>
-  </si>
-  <si>
-    <t>sd.coef.ADG</t>
-  </si>
-  <si>
-    <t>sd.coef.NDF</t>
-  </si>
-  <si>
-    <t>sd.coef.CP</t>
-  </si>
-  <si>
-    <t>sd.coef.NDF_digest</t>
-  </si>
-  <si>
-    <t>Sheep</t>
-  </si>
-  <si>
-    <t>low</t>
-  </si>
-  <si>
-    <t>1-1-1-1</t>
-  </si>
-  <si>
-    <t>c(699.7, 696.5, 1390, 1540, 1521, 1263, 1426, 1345, 1317, 1170, 1150, 1210, 1190, 1150, 595.5, 596.38, 598.88, 589.88, 592.97, 1050, 1183, 1344, 877, 622.5, 604.2, 613, 615.5, 653.5, 629.5, 620.5, 702, 714, 536, 489, 518, 493, 452, 502)</t>
-  </si>
-  <si>
-    <t>feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t>c(166, 211, 196, 205, 138, 208, 164, 108, 136, 190, 213, 167, 183, 181, 116, 191, 193, 200, 141)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 208, 209, 210, 211, 212, 213)</t>
-  </si>
-  <si>
-    <t>c(27, 27, 29, 29, 33, 33, 33, 34, 34, 40, 40, 40, 40, 40, 44, 44, 44, 44, 44, 47, 47, 47, 47, 48, 48, 48, 48, 48, 48, 48, 49, 50, 51, 51, 51, 51, 51, 51)</t>
-  </si>
-  <si>
-    <t>c(107, 118, 134, 142, 163, 165, 180, 182, 184, 192, 194, 195, 197, 198, 199, 203, 209, 210, 212)</t>
-  </si>
-  <si>
-    <t>Sheep - Low NDF</t>
-  </si>
-  <si>
-    <t>numeric(0)</t>
-  </si>
-  <si>
-    <t>c(2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 214, 215, 216)</t>
-  </si>
-  <si>
-    <t>c(108, 116, 136, 138, 141, 164, 166, 167, 181, 183, 190, 191, 193, 196, 200, 205, 208, 211, 213)</t>
-  </si>
-  <si>
-    <t>list(baselearner = list(list(model.frame = function () 
+    <t xml:space="preserve">train.IDs.length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">species.ndf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total.sample.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight.list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDs.remaining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k.IDs.length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gbr.model.train.coef.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gbr.model.train.coef.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gbr.model.train.coef.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gbr.model.train.coef.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gbr.model.train.coef.NDF*Digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gbr.model.train.coef.offset.plus.intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gbr.whole.sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.ut.ids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.adg_g_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.CP_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.offset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.offset.plus.intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.predicted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.predicted.base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.residuals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.rms.residuals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.corr.bw.adg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.corr.bw.ndf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.NDF_Digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.NDF_Digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef.NDF_Digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef.offset.plus.intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.ccc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w.AIC.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.w.coef.bw.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.coef.NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-1-1-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(699.7, 696.5, 1390, 1540, 1521, 1263, 1426, 1345, 1317, 1170, 1150, 1210, 1190, 1150, 595.5, 596.38, 598.88, 589.88, 592.97, 1050, 1183, 1344, 877, 622.5, 604.2, 613, 615.5, 653.5, 629.5, 620.5, 702, 714, 536, 489, 518, 493, 452, 502)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(193, 209, 199, 138, 212, 192, 142, 197, 196, 116, 191, 181, 180, 108, 165, 208, 210, 194, 183)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 208, 209, 210, 211, 212, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(27, 27, 29, 29, 33, 33, 33, 34, 34, 40, 40, 40, 40, 40, 44, 44, 44, 44, 44, 47, 47, 47, 47, 48, 48, 48, 48, 48, 48, 48, 49, 50, 51, 51, 51, 51, 51, 51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 118, 134, 136, 141, 163, 164, 166, 167, 182, 184, 190, 195, 198, 200, 203, 205, 211, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheep - Low NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numeric(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2, 3, 4, 105, 106, 109, 153, 154, 155, 156, 202, 214, 215, 216)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 116, 138, 142, 165, 180, 181, 183, 191, 192, 193, 194, 196, 197, 199, 208, 209, 210, 212)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
 return(NULL), get_data = function () 
 X, get_index = function () 
 index, get_vary = function () 
@@ -467,7 +549,7 @@
     X %*% (MPinvS/sxtx)
 })), offset = 875.276578947368, ustart = c(`1376` = -175.576578947368, `1377` = -178.776578947368, `1487` = 514.723421052632, `1490` = 664.723421052632, `1585` = 645.723421052632, `1587` = 387.723421052632, `1589` = 550.723421052632, `1639` = 469.723421052632, `1640` = 441.723421052632, `1770` = 294.723421052632, `1771` = 274.723421052632, `1772` = 334.723421052632, `1773` = 314.723421052632, `1774` = 274.723421052632, `1815` = -279.776578947368, `1816` = -278.896578947368, `1817` = -276.396578947368, 
 `1818` = -285.396578947368, `1819` = -282.306578947368, `1921` = 174.723421052632, `1922` = 307.723421052632, `1923` = 468.723421052632, `1924` = 1.72342105263158, `1945` = -252.776578947368, `1946` = -271.076578947368, `1947` = -262.276578947368, `1948` = -259.776578947368, `1949` = -221.776578947368, `1950` = -245.776578947368, `1951` = -254.776578947368, `1968` = -173.276578947368, `1981` = -161.276578947368, `1984` = -339.276578947368, `1985` = -386.276578947368, `1986` = -357.276578947368, `1987` = -382.276578947368, 
-`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 1100, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
+`1988` = -423.276578947368, `1989` = -373.276578947368), control = list(mstop = 1000, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
 return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
 y - f, risk = function (y, f, w = 1) 
 sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
@@ -714,40 +796,40 @@
 }, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
   </si>
   <si>
-    <t>c(710.620997249566, 750.401075611211, 1389.96976803688, 1406.93392311784, 1446.30728649106, 1337.52169848894, 1385.07653796687, 1148.47465226024, 1090.66374128349, 1201.58188402975, 1164.23371059722, 1263.25333281729, 1230.49159918997, 1188.24651938514, 619.10535621307, 614.404331363065, 572.653300144295, 572.478818666772, 609.659097867675, 1084.90379778241, 1326.24958649781, 1362.64567624072, 1000.76266767438, 572.098291864774, 596.654345380954, 604.527318348069, 594.095652561544, 618.345176803266, 
-608.545733529338, 595.109462553002, 712.143532974217, 759.732281657244, 559.29199585301, 493.396280404922, 537.771233017176, 597.29554398003, 491.351110891663, 555.608946116062)</t>
-  </si>
-  <si>
-    <t>c(10.9209972495659, 53.9010756112107, -0.0302319631236969, -133.066076882165, -74.6927135089368, 74.5216984889405, -40.9234620331254, -196.525347739765, -226.336258716511, 31.5818840297479, 14.2337105972219, 53.2533328172908, 40.4915991899652, 38.2465193851417, 23.6053562130701, 18.0243313630654, -26.2266998557051, -17.4011813332282, 16.6890978676745, 34.9037977824119, 143.24958649781, 18.6456762407192, 123.762667674382, -50.4017081352256, -7.54565461904565, -8.47268165193066, -21.4043474384562, 
--35.1548231967342, -20.9542664706619, -25.3905374469983, 10.1435329742167, 45.7322816572441, 23.2919958530096, 4.39628040492244, 19.771233017176, 104.29554398003, 39.3511108916634, 53.6089461160625)</t>
-  </si>
-  <si>
-    <t>c(10.9209972495659, 53.9010756112107, 0.0302319631236969, 133.066076882165, 74.6927135089368, 74.5216984889405, 40.9234620331254, 196.525347739765, 226.336258716511, 31.5818840297479, 14.2337105972219, 53.2533328172908, 40.4915991899652, 38.2465193851417, 23.6053562130701, 18.0243313630654, 26.2266998557051, 17.4011813332282, 16.6890978676745, 34.9037977824119, 143.24958649781, 18.6456762407192, 123.762667674382, 50.4017081352256, 7.54565461904565, 8.47268165193066, 21.4043474384562, 35.1548231967342, 
-20.9542664706619, 25.3905374469983, 10.1435329742167, 45.7322816572441, 23.2919958530096, 4.39628040492244, 19.771233017176, 104.29554398003, 39.3511108916634, 53.6089461160625)</t>
-  </si>
-  <si>
-    <t>c(199, 198, 192, 182, 212, 134, 203, 184, 165, 197, 163, 118, 195, 210, 180, 142, 194, 107, 209)</t>
-  </si>
-  <si>
-    <t>c(699.7, 696.5, 1390, 1540, 1521, 1263, 1426, 1345, 1317, 1170, 1150, 1210, 1190, 1150, 595.5, 596.38, 598.88, 589.88, 592.97, 1050, 1183, 1344, 877, 622.5, 604.2, 613, 615.5, 653.5, 629.5, 620.5, 702)</t>
-  </si>
-  <si>
-    <t>feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition + CP_nutrition</t>
-  </si>
-  <si>
-    <t>c(190, 136, 195, 134, 116, 108, 183, 118, 141, 203, 107, 182, 163, 180, 200, 184)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203)</t>
-  </si>
-  <si>
-    <t>c(138, 142, 164, 165, 166, 167, 181, 191, 192, 193, 194, 196, 197, 198, 199)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 116, 118, 134, 136, 141, 163, 180, 182, 183, 184, 190, 195, 200, 203)</t>
-  </si>
-  <si>
-    <t>list(baselearner = list(list(model.frame = function () 
+    <t xml:space="preserve">c(714.446698412496, 754.107300564118, 1387.1718287791, 1403.13722332753, 1450.18781829323, 1341.99813875728, 1389.29591968118, 1138.34427600944, 1079.94914104626, 1197.76994291072, 1160.71465425341, 1259.55862288655, 1228.36356034894, 1185.08840815532, 621.951033662728, 617.858875860441, 577.153183040574, 577.172910426004, 612.525032690721, 1082.25161681378, 1322.38074705344, 1358.74421628778, 996.296447179907, 575.495278275508, 599.193402875597, 607.018469475824, 597.04376288136, 621.198738871946, 
+611.471547303002, 598.106455618344, 713.834057075308, 760.616656659748, 562.311749605868, 496.380980718595, 540.767617810577, 600.02318573967, 494.347495685064, 558.523539551362)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14.7466984124956, 57.6073005641184, -2.82817122089727, -136.862776672467, -70.8121817067668, 78.9981387572768, -36.7040803188215, -206.655723990558, -237.050858953741, 27.7699429107197, 10.7146542534149, 49.5586228865513, 38.3635603489422, 35.0884081553163, 26.4510336627285, 21.4788758604408, -21.7268169594256, -12.7070895739961, 19.5550326907214, 32.2516168137804, 139.380747053444, 14.7442162877805, 119.296447179907, -47.0047217244919, -5.00659712440302, -5.98153052417592, -18.4562371186403, -32.3012611280544, 
+-18.0284526969976, -22.3935443816556, 11.8340570753078, 46.6166566597483, 26.3117496058682, 7.38098071859474, 22.767617810577, 107.02318573967, 42.3474956850645, 56.5235395513624)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14.7466984124956, 57.6073005641184, 2.82817122089727, 136.862776672467, 70.8121817067668, 78.9981387572768, 36.7040803188215, 206.655723990558, 237.050858953741, 27.7699429107197, 10.7146542534149, 49.5586228865513, 38.3635603489422, 35.0884081553163, 26.4510336627285, 21.4788758604408, 21.7268169594256, 12.7070895739961, 19.5550326907214, 32.2516168137804, 139.380747053444, 14.7442162877805, 119.296447179907, 47.0047217244919, 5.00659712440302, 5.98153052417592, 18.4562371186403, 32.3012611280544, 
+18.0284526969976, 22.3935443816556, 11.8340570753078, 46.6166566597483, 26.3117496058682, 7.38098071859474, 22.767617810577, 107.02318573967, 42.3474956850645, 56.5235395513624)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(205, 136, 190, 198, 118, 107, 134, 200, 213, 167, 184, 211, 195, 166, 141, 164, 182, 203, 163)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(699.7, 696.5, 1390, 1540, 1521, 1263, 1426, 1345, 1317, 1170, 1150, 1210, 1190, 1150, 595.5, 596.38, 598.88, 589.88, 592.97, 1050, 1183, 1344, 877, 622.5, 604.2, 613, 615.5, 653.5, 629.5, 620.5, 702)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition + CP_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(184, 194, 180, 167, 200, 196, 203, 182, 142, 107, 134, 108, 116, 195, 198, 163)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 136, 138, 141, 164, 165, 166, 181, 183, 190, 191, 192, 193, 197, 199)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 134, 142, 163, 167, 180, 182, 184, 194, 195, 196, 198, 200, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
 return(NULL), get_data = function () 
 X, get_index = function () 
 index, get_vary = function () 
@@ -879,7 +961,7 @@
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
 })), offset = 953.435806451613, ustart = c(`1376` = -253.735806451613, `1377` = -256.935806451613, `1487` = 436.564193548387, `1490` = 586.564193548387, `1585` = 567.564193548387, `1587` = 309.564193548387, `1589` = 472.564193548387, `1639` = 391.564193548387, `1640` = 363.564193548387, `1770` = 216.564193548387, `1771` = 196.564193548387, `1772` = 256.564193548387, `1773` = 236.564193548387, `1774` = 196.564193548387, `1815` = -357.935806451613, `1816` = -357.055806451613, `1817` = -354.555806451613, 
-`1818` = -363.555806451613, `1819` = -360.465806451613, `1921` = 96.5641935483872, `1922` = 229.564193548387, `1923` = 390.564193548387, `1924` = -76.4358064516128, `1945` = -330.935806451613, `1946` = -349.235806451613, `1947` = -340.435806451613, `1948` = -337.935806451613, `1949` = -299.935806451613, `1950` = -323.935806451613, `1951` = -332.935806451613, `1968` = -251.435806451613), control = list(mstop = 1100, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", 
+`1818` = -363.555806451613, `1819` = -360.465806451613, `1921` = 96.5641935483872, `1922` = 229.564193548387, `1923` = 390.564193548387, `1924` = -76.4358064516128, `1945` = -330.935806451613, `1946` = -349.235806451613, `1947` = -340.435806451613, `1948` = -337.935806451613, `1949` = -299.935806451613, `1950` = -323.935806451613, `1951` = -332.935806451613, `1968` = -251.435806451613), control = list(mstop = 1000, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", 
     fW = function (f) 
     return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
     y - f, risk = function (y, f, w = 1) 
@@ -1126,22 +1208,52 @@
 }, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
   </si>
   <si>
-    <t>c(690.646246988091, 702.266791435633, 1415.7669277196, 1427.56651479569, 1379.38931691978, 1316.28621977746, 1336.03051748987, 1166.34278944223, 1111.88355329175, 1209.08343094914, 1177.77343438695, 1260.08884957976, 1231.89672417258, 1197.34850785696, 708.189715626926, 706.001514401897, 671.713902258108, 661.530682062377, 706.18068758043, 1100.76986368753, 1316.59630304364, 1345.25560324843, 1034.70000193737, 594.647492121294, 584.089723473352, 605.336995360276, 583.754695165285, 608.731652349524, 
-610.00309851547, 604.614127368904, 587.615863622735)</t>
-  </si>
-  <si>
-    <t>c(-9.05375301190918, 5.76679143563308, 25.7669277196026, -112.43348520431, -141.610683080222, 53.28621977746, -89.9694825101349, -178.65721055777, -205.116446708247, 39.0834309491447, 27.7734343869488, 50.088849579764, 41.8967241725813, 47.3485078569556, 112.689715626926, 109.621514401897, 72.833902258108, 71.6506820623766, 113.21068758043, 50.7698636875346, 133.596303043635, 1.25560324843491, 157.700001937375, -27.8525078787061, -20.1102765266475, -7.66300463972379, -31.7453048347147, -44.7683476504765, 
--19.4969014845298, -15.8858726310957, -114.384136377265)</t>
-  </si>
-  <si>
-    <t>c(9.05375301190918, 5.76679143563308, 25.7669277196026, 112.43348520431, 141.610683080222, 53.28621977746, 89.9694825101349, 178.65721055777, 205.116446708247, 39.0834309491447, 27.7734343869488, 50.088849579764, 41.8967241725813, 47.3485078569556, 112.689715626926, 109.621514401897, 72.833902258108, 71.6506820623766, 113.21068758043, 50.7698636875346, 133.596303043635, 1.25560324843491, 157.700001937375, 27.8525078787061, 20.1102765266475, 7.66300463972379, 31.7453048347147, 44.7683476504765, 19.4969014845298, 
-15.8858726310957, 114.384136377265)</t>
-  </si>
-  <si>
-    <t>c(167, 199, 164, 196, 198, 138, 142, 181, 165, 197, 166, 192, 194, 193, 191)</t>
-  </si>
-  <si>
-    <t>list(baselearner = list(list(model.frame = function () 
+    <t xml:space="preserve">c(689.201017035568, 699.730506812939, 1416.41669274449, 1428.02268039102, 1378.83915087344, 1317.03061014606, 1335.88345892659, 1163.47704434123, 1109.20596566856, 1209.27034594566, 1178.12423337306, 1260.06406828557, 1232.43686602276, 1197.73617855564, 711.875074755913, 709.887603850572, 676.02681061553, 665.483662905559, 710.319957721894, 1100.14116961269, 1315.66669687399, 1344.07938501403, 1034.23924002973, 595.044280697841, 583.635934108517, 605.481047131077, 583.160802130138, 608.226830080314, 
+610.010710294069, 604.939933184697, 581.28314149524)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(-10.498982964432, 3.23050681293853, 26.416692744494, -111.977319608985, -142.160849126563, 54.030610146061, -90.1165410734061, -181.522955658766, -207.794034331443, 39.2703459456648, 28.1242333730561, 50.0640682855656, 42.4368660227594, 47.7361785556402, 116.375074755913, 113.507603850572, 77.1468106155304, 75.603662905559, 117.349957721894, 50.1411696126866, 132.666696873987, 0.0793850140257746, 157.239240029735, -27.4557193021589, -20.5640658914828, -7.51895286892341, -32.3391978698622, -45.2731699196863, 
+-19.4892897059311, -15.5600668153028, -120.71685850476)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(10.498982964432, 3.23050681293853, 26.416692744494, 111.977319608985, 142.160849126563, 54.030610146061, 90.1165410734061, 181.522955658766, 207.794034331443, 39.2703459456648, 28.1242333730561, 50.0640682855656, 42.4368660227594, 47.7361785556402, 116.375074755913, 113.507603850572, 77.1468106155304, 75.603662905559, 117.349957721894, 50.1411696126866, 132.666696873987, 0.0793850140257746, 157.239240029735, 27.4557193021589, 20.5640658914828, 7.51895286892341, 32.3391978698622, 45.2731699196863, 
+19.4892897059311, 15.5600668153028, 120.71685850476)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 136, 164, 193, 181, 190, 192, 197, 166, 191, 141, 183, 165, 199, 138)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 198, 180, 194, 199, 183, 141, 165, 108, 166, 163, 196, 191, 182, 200, 142)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 116, 134, 136, 138, 164, 167, 181, 184, 190, 192, 193, 195, 197, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 118, 141, 142, 163, 165, 166, 180, 182, 183, 191, 194, 196, 198, 199, 200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 203, 107, 193, 136, 138, 192, 190, 197, 181, 195, 116, 164, 184, 167)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(699.7, 696.5, 1050, 1183, 1344, 877, 702)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition + CP_nutrition + NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 203, 193, 190)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 190, 191, 192, 193, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 191, 192)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 190, 193, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
 return(NULL), get_data = function () 
 X, get_index = function () 
 index, get_vary = function () 
@@ -1262,7 +1374,7 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, Xnames = c("(Intercept)", "bw_kg", "adg_g_day", "NDF_nutrition", "CP_nutrition"), MPinv = function () 
+}, Xnames = c("(Intercept)", "bw_kg", "adg_g_day", "NDF_nutrition", "CP_nutrition", "NDF_digest"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
@@ -1272,25 +1384,22 @@
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-})), offset = 953.435806451613, ustart = c(`1376` = -253.735806451613, `1377` = -256.935806451613, `1487` = 436.564193548387, `1490` = 586.564193548387, `1585` = 567.564193548387, `1587` = 309.564193548387, `1589` = 472.564193548387, `1639` = 391.564193548387, `1640` = 363.564193548387, `1770` = 216.564193548387, `1771` = 196.564193548387, `1772` = 256.564193548387, `1773` = 236.564193548387, `1774` = 196.564193548387, `1815` = -357.935806451613, `1816` = -357.055806451613, `1817` = -354.555806451613, 
-`1818` = -363.555806451613, `1819` = -360.465806451613, `1921` = 96.5641935483872, `1922` = 229.564193548387, `1923` = 390.564193548387, `1924` = -76.4358064516128, `1945` = -330.935806451613, `1946` = -349.235806451613, `1947` = -340.435806451613, `1948` = -337.935806451613, `1949` = -299.935806451613, `1950` = -323.935806451613, `1951` = -332.935806451613, `1968` = -251.435806451613), control = list(mstop = 1099, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", 
-    fW = function (f) 
-    return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
-    y - f, risk = function (y, f, w = 1) 
-    sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
-    UseMethod("weighted.mean"), check_y = function (y) 
-    {
-        if (!is.numeric(y) || !is.null(dim(y))) 
-            stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
-        y
-    }, weights = function (w) 
-    {
-        switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
-    }, nuisance = function () 
-    return(NA), response = function (f) 
-    f, rclass = function (f) 
-    NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1487` = 1390, `1490` = 1540, `1585` = 1521, `1587` = 1263, `1589` = 1426, `1639` = 1345, `1640` = 1317, `1770` = 1170, `1771` = 1150, `1772` = 1210, `1773` = 1190, `1774` = 1150, `1815` = 595.5, `1816` = 596.38, `1817` = 598.88, `1818` = 589.88, `1819` = 592.97, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1945` = 622.5, `1946` = 604.2, `1947` = 613, `1948` = 615.5, 
-`1949` = 653.5, `1950` = 629.5, `1951` = 620.5, `1968` = 702), rownames = c("1376", "1377", "1487", "1490", "1585", "1587", "1589", "1639", "1640", "1770", "1771", "1772", "1773", "1774", "1815", "1816", "1817", "1818", "1819", "1921", "1922", "1923", "1924", "1945", "1946", "1947", "1948", "1949", "1950", "1951", "1968"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+})), offset = 936.028571428571, ustart = c(`1376` = -236.328571428571, `1377` = -239.528571428571, `1921` = 113.971428571429, `1922` = 246.971428571429, `1923` = 407.971428571429, `1924` = -59.0285714285714, `1968` = -234.028571428571), control = list(mstop = 1000, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
+return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
+y - f, risk = function (y, f, w = 1) 
+sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
+UseMethod("weighted.mean"), check_y = function (y) 
+{
+    if (!is.numeric(y) || !is.null(dim(y))) 
+        stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
+    y
+}, weights = function (w) 
+{
+    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
+}, nuisance = function () 
+return(NA), response = function (f) 
+f, rclass = function (f) 
+NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`1376` = 699.7, `1377` = 696.5, `1921` = 1050, `1922` = 1183, `1923` = 1344, `1924` = 877, `1968` = 702), rownames = c("1376", "1377", "1921", "1922", "1923", "1924", "1968"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1), nuisance = function () 
 nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
 {
     res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
@@ -1517,26 +1626,27 @@
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
-  </si>
-  <si>
-    <t>c(690.988869735865, 702.609414183407, 1416.10955046738, 1427.90913754346, 1379.73193966755, 1316.62884252523, 1336.37314023764, 1166.68541219, 1112.22617603953, 1209.42605369692, 1178.11605713472, 1260.43147232754, 1232.23934692036, 1197.69113060473, 708.5323383747, 706.344137149671, 672.056525005882, 661.873304810151, 706.523310328204, 1101.11248643531, 1316.93892579141, 1345.59822599621, 1035.04262468515, 594.990114869068, 584.432346221127, 605.679618108051, 584.09731791306, 609.074275097298, 610.345721263245, 
-604.956750116679, 587.958486370509)</t>
-  </si>
-  <si>
-    <t>c(-8.71113026413479, 6.10941418340747, 26.1095504673769, -112.090862456536, -141.268060332448, 53.6288425252344, -89.6268597623605, -178.314587809996, -204.773823960473, 39.4260536969191, 28.1160571347232, 50.4314723275384, 42.2393469203557, 47.69113060473, 113.0323383747, 109.964137149671, 73.1765250058824, 71.993304810151, 113.553310328204, 51.1124864353089, 133.938925791409, 1.59822599620929, 158.042624685149, -27.5098851309317, -19.7676537788731, -7.32038189194941, -31.4026820869403, -44.4257249027021, 
--19.1542787367554, -15.5432498833213, -114.041513629491)</t>
-  </si>
-  <si>
-    <t>c(8.71113026413479, 6.10941418340747, 26.1095504673769, 112.090862456536, 141.268060332448, 53.6288425252344, 89.6268597623605, 178.314587809996, 204.773823960473, 39.4260536969191, 28.1160571347232, 50.4314723275384, 42.2393469203557, 47.69113060473, 113.0323383747, 109.964137149671, 73.1765250058824, 71.993304810151, 113.553310328204, 51.1124864353089, 133.938925791409, 1.59822599620929, 158.042624685149, 27.5098851309317, 19.7676537788731, 7.32038189194941, 31.4026820869403, 44.4257249027021, 
-19.1542787367554, 15.5432498833213, 114.041513629491)</t>
+}, assign = 0:5, center = c(0, 0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(733.932826696724, 748.181462738792, 1018.91749944247, 1239.07030479412, 1265.76921261556, 934.609070541025, 623.756121102992)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(34.2328266967238, 51.681462738792, -31.0825005575255, 56.0703047941249, -78.2307873844431, 57.6090705410249, -78.243878897008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(34.2328266967238, 51.681462738792, 31.0825005575255, 56.0703047941249, 78.2307873844431, 57.6090705410249, 78.243878897008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 192, 191)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1572,15 +1682,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1862,11 +1963,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CM5"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:91" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2140,82 +2241,174 @@
       <c r="CM1" t="s">
         <v>90</v>
       </c>
+      <c r="CN1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>118</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>119</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>120</v>
+      </c>
     </row>
-    <row r="2" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="B2">
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2">
+        <v>122</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2">
+        <v>123</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>1100</v>
-      </c>
-      <c r="I2">
+      <c r="H2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J2">
-        <v>0.92285396534869102</v>
-      </c>
-      <c r="K2">
-        <v>9.8571957579962302</v>
-      </c>
-      <c r="L2">
-        <v>0.96721088014367096</v>
+      <c r="J2" t="n">
+        <v>0.943349997657261</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.57894635227775</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.975120423608415</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
-      <c r="N2">
-        <v>0.92285396534869102</v>
-      </c>
-      <c r="O2">
-        <v>9.8571957579962302</v>
-      </c>
-      <c r="P2">
-        <v>0.96721088014367096</v>
+      <c r="N2" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.923428882466923</v>
       </c>
       <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0.92285396534869102</v>
-      </c>
-      <c r="S2">
-        <v>9.8571957579962302</v>
-      </c>
-      <c r="T2">
-        <v>0.96721088014367096</v>
-      </c>
-      <c r="U2">
-        <v>2.6101743222462202E-2</v>
-      </c>
-      <c r="V2">
-        <v>0.34003042523030902</v>
-      </c>
-      <c r="X2">
-        <v>-632.77451196780601</v>
-      </c>
-      <c r="Y2">
-        <v>16.501360631762299</v>
-      </c>
-      <c r="Z2">
-        <v>3.2221389594992398</v>
-      </c>
-      <c r="AA2">
-        <v>-0.12947072348824501</v>
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.943349997657261</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8.57894635227775</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.975120423608415</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.000524784759243288</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.608713831447753</v>
+      </c>
+      <c r="W2"/>
+      <c r="X2" t="n">
+        <v>-605.576388594081</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>15.8451677373375</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.18615245179865</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.111234506980636</v>
       </c>
       <c r="AB2" t="e">
         <v>#NUM!</v>
@@ -2223,217 +2416,318 @@
       <c r="AC2" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD2">
-        <v>0.904397245715298</v>
-      </c>
-      <c r="AE2">
-        <v>0.94341633750407405</v>
-      </c>
-      <c r="AF2">
-        <v>10.097633577486301</v>
-      </c>
-      <c r="AG2">
-        <v>7.9095086704082798</v>
-      </c>
-      <c r="AH2">
-        <v>-621.19410312843195</v>
-      </c>
-      <c r="AI2">
-        <v>17.3625403171568</v>
-      </c>
-      <c r="AJ2">
-        <v>3.3670975167658801</v>
-      </c>
+      <c r="AD2" t="n">
+        <v>0.943721076519185</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.945352176179733</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9.0093720302965</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>7.93850598104709</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-682.775890380792</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>16.7174342227577</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.20560987576525</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.0627521891193563</v>
+      </c>
+      <c r="AL2"/>
+      <c r="AM2"/>
       <c r="AN2" t="s">
-        <v>94</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="AO2"/>
       <c r="AP2" t="s">
-        <v>95</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="AQ2"/>
       <c r="AR2" t="s">
-        <v>96</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="AS2"/>
       <c r="AT2" t="s">
-        <v>97</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="AU2"/>
       <c r="AV2" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AW2" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="AX2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AZ2">
+        <v>129</v>
+      </c>
+      <c r="AY2"/>
+      <c r="AZ2" t="n">
         <v>19</v>
       </c>
       <c r="BA2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB2">
+        <v>130</v>
+      </c>
+      <c r="BB2" t="n">
         <v>38</v>
       </c>
       <c r="BC2" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="BD2" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="BE2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="BF2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BG2">
-        <v>-621.19410312843195</v>
-      </c>
-      <c r="BH2">
-        <v>17.3625403171568</v>
-      </c>
-      <c r="BI2">
-        <v>3.3670975167658801</v>
-      </c>
-      <c r="BL2">
-        <v>214.345370555778</v>
+        <v>133</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-682.775890380792</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>16.7174342227577</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.20560987576525</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-0.0627521891193563</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-0.0627521891193563</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>241.421478040261</v>
       </c>
       <c r="BM2" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="BN2" t="s">
-        <v>97</v>
-      </c>
-      <c r="BO2">
-        <v>-621.92898641646696</v>
-      </c>
-      <c r="BP2">
-        <v>16.781721765066099</v>
-      </c>
-      <c r="BQ2">
-        <v>3.2013877327939699</v>
-      </c>
-      <c r="BR2">
-        <v>-0.12433687358266</v>
-      </c>
-      <c r="BU2">
-        <v>835.53947368421098</v>
-      </c>
-      <c r="BV2">
-        <v>213.61048726774399</v>
+        <v>127</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-609.398321890158</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>15.98813749018</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>3.20138773279397</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-0.11265239385391</v>
+      </c>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2" t="n">
+        <v>924.197368421053</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>314.799046530894</v>
       </c>
       <c r="BW2" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="BX2" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="BY2" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="BZ2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CA2">
-        <v>0.41471265136089402</v>
-      </c>
-      <c r="CB2">
-        <v>9.3447395609349004E-2</v>
-      </c>
-      <c r="CD2">
-        <v>214.345370555778</v>
-      </c>
-      <c r="CE2">
-        <v>0.96164322004108904</v>
-      </c>
-      <c r="CG2">
+        <v>137</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.414712651360894</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.093447395609349</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>41731.3563425708</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>6125.15155895096</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>66431.0871737463</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>211.959172913262</v>
+      </c>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2" t="n">
+        <v>0.364467413140463</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.053494981698134</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.580186426138873</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.00185117902252994</v>
+      </c>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2" t="n">
+        <v>241.421478040261</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.976418197286092</v>
+      </c>
+      <c r="CR2"/>
+      <c r="CS2" t="n">
         <v>1</v>
       </c>
-      <c r="CH2">
-        <v>16.377171238468001</v>
-      </c>
-      <c r="CI2">
-        <v>1.2178919907250301</v>
-      </c>
-      <c r="CJ2">
-        <v>0.20500235766852901</v>
-      </c>
+      <c r="CT2" t="n">
+        <v>109.176582435212</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.23357109368488</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.0275169528624054</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0.068564351454705</v>
+      </c>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2" t="n">
+        <v>38107.6550702163</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>5426.91876830678</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>69593.4503699292</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>406.761295996726</v>
+      </c>
+      <c r="DD2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DE2"/>
+      <c r="DF2" t="n">
+        <v>0.335400396911774</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.047750801116463</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.613251260210731</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.00359754176103187</v>
+      </c>
+      <c r="DJ2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DK2"/>
+      <c r="DL2" t="n">
+        <v>5124.68748535227</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>987.450282222611</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>4472.25692119133</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>275.491804443709</v>
+      </c>
+      <c r="DP2"/>
+      <c r="DQ2"/>
     </row>
-    <row r="3" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="B3">
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3">
+        <v>122</v>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3">
+        <v>123</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="H3">
-        <v>1099</v>
-      </c>
-      <c r="I3">
+      <c r="H3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.1</v>
       </c>
-      <c r="J3">
-        <v>0.92285396534869102</v>
-      </c>
-      <c r="K3">
-        <v>9.8571957579962302</v>
-      </c>
-      <c r="L3">
-        <v>0.96721088014367096</v>
+      <c r="J3" t="n">
+        <v>0.943349997657261</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.57894635227775</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.975120423608415</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
-      <c r="N3">
-        <v>0.92285396534869102</v>
-      </c>
-      <c r="O3">
-        <v>9.8571957579962302</v>
-      </c>
-      <c r="P3">
-        <v>0.96721088014367096</v>
+      <c r="N3" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="O3" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.923428882466923</v>
       </c>
       <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0.92285396534869102</v>
-      </c>
-      <c r="S3">
-        <v>9.8571957579962302</v>
-      </c>
-      <c r="T3">
-        <v>0.96721088014367096</v>
-      </c>
-      <c r="U3">
-        <v>2.6101743222462202E-2</v>
-      </c>
-      <c r="V3">
-        <v>0.34003042523030902</v>
-      </c>
-      <c r="X3">
-        <v>-632.77451196780601</v>
-      </c>
-      <c r="Y3">
-        <v>16.501360631762299</v>
-      </c>
-      <c r="Z3">
-        <v>3.2221389594992398</v>
-      </c>
-      <c r="AA3">
-        <v>-0.12947072348824501</v>
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.943349997657261</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8.57894635227775</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.975120423608415</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.000524784759243288</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.608713831447753</v>
+      </c>
+      <c r="W3"/>
+      <c r="X3" t="n">
+        <v>-605.576388594081</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15.8451677373375</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.18615245179865</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.111234506980636</v>
       </c>
       <c r="AB3" t="e">
         <v>#NUM!</v>
@@ -2441,595 +2735,2097 @@
       <c r="AC3" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD3">
-        <v>0.94131068498208403</v>
-      </c>
-      <c r="AE3">
-        <v>0.92791452499900495</v>
-      </c>
-      <c r="AF3">
-        <v>9.6167579385061295</v>
-      </c>
-      <c r="AG3">
-        <v>8.9699253528807503</v>
-      </c>
-      <c r="AH3">
-        <v>-644.35492080717995</v>
-      </c>
-      <c r="AI3">
-        <v>15.640180946367799</v>
-      </c>
-      <c r="AJ3">
-        <v>3.0771804022325902</v>
-      </c>
-      <c r="AK3">
-        <v>-0.12947072348824501</v>
-      </c>
+      <c r="AD3" t="n">
+        <v>0.942978918795337</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.937203039577722</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8.148520674259</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>8.05566758168007</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-528.376886807371</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>14.9729012519172</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.16669502783206</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.159716824841916</v>
+      </c>
+      <c r="AL3"/>
+      <c r="AM3"/>
       <c r="AN3" t="s">
-        <v>94</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="AO3"/>
       <c r="AP3" t="s">
-        <v>95</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="AQ3"/>
       <c r="AR3" t="s">
-        <v>108</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AS3"/>
       <c r="AT3" t="s">
-        <v>97</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="AU3"/>
       <c r="AV3" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AW3" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="AX3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AZ3">
+        <v>133</v>
+      </c>
+      <c r="AY3"/>
+      <c r="AZ3" t="n">
         <v>19</v>
       </c>
       <c r="BA3" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB3">
+        <v>130</v>
+      </c>
+      <c r="BB3" t="n">
         <v>38</v>
       </c>
       <c r="BC3" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="BD3" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="BE3" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="BF3" t="s">
-        <v>99</v>
-      </c>
-      <c r="BG3">
-        <v>-644.35492080717995</v>
-      </c>
-      <c r="BH3">
-        <v>15.640180946367799</v>
-      </c>
-      <c r="BI3">
-        <v>3.0771804022325902</v>
-      </c>
-      <c r="BJ3">
-        <v>-0.12947072348824501</v>
-      </c>
-      <c r="BK3">
-        <v>-0.12947072348824501</v>
-      </c>
-      <c r="BL3">
-        <v>270.65876340334597</v>
+        <v>129</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-528.376886807371</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>14.9729012519172</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.16669502783206</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-0.159716824841916</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-0.159716824841916</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>297.978902666313</v>
       </c>
       <c r="BM3" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="BN3" t="s">
-        <v>97</v>
-      </c>
-      <c r="BO3">
-        <v>-621.92898641646696</v>
-      </c>
-      <c r="BP3">
-        <v>16.781721765066099</v>
-      </c>
-      <c r="BQ3">
-        <v>3.2013877327939699</v>
-      </c>
-      <c r="BR3">
-        <v>-0.12433687358266</v>
-      </c>
-      <c r="BU3">
-        <v>915.01368421052598</v>
-      </c>
-      <c r="BV3">
-        <v>293.08469779405903</v>
+        <v>127</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-609.398321890158</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>15.98813749018</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>3.20138773279397</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>-0.11265239385391</v>
+      </c>
+      <c r="BS3"/>
+      <c r="BT3"/>
+      <c r="BU3" t="n">
+        <v>826.355789473684</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>216.957467583526</v>
       </c>
       <c r="BW3" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="BX3" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="BY3" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="BZ3" t="s">
-        <v>107</v>
-      </c>
-      <c r="CA3">
-        <v>0.41471265136089402</v>
-      </c>
-      <c r="CB3">
-        <v>9.3447395609349004E-2</v>
-      </c>
-      <c r="CD3">
-        <v>270.65876340334597</v>
-      </c>
-      <c r="CE3">
-        <v>0.97277854024625399</v>
-      </c>
-      <c r="CG3">
+        <v>137</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.414712651360894</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>0.093447395609349</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>34483.9537978619</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>4728.68597766261</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>72755.813566112</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>601.563419080191</v>
+      </c>
+      <c r="CG3"/>
+      <c r="CH3"/>
+      <c r="CI3" t="n">
+        <v>0.306333380683085</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.042006620534792</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.646316094282589</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0.00534390449953381</v>
+      </c>
+      <c r="CM3"/>
+      <c r="CN3"/>
+      <c r="CO3"/>
+      <c r="CP3" t="n">
+        <v>297.978902666313</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>0.973822649930738</v>
+      </c>
+      <c r="CR3"/>
+      <c r="CS3" t="n">
         <v>1</v>
       </c>
-      <c r="CH3">
-        <v>16.377171238468001</v>
-      </c>
-      <c r="CI3">
-        <v>1.2178919907250301</v>
-      </c>
-      <c r="CJ3">
-        <v>0.20500235766852901</v>
-      </c>
+      <c r="CT3" t="n">
+        <v>109.176582435212</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.23357109368488</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0.0275169528624054</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>0.068564351454705</v>
+      </c>
+      <c r="CX3"/>
+      <c r="CY3"/>
+      <c r="CZ3" t="n">
+        <v>38107.6550702163</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>5426.91876830678</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>69593.4503699292</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>406.761295996726</v>
+      </c>
+      <c r="DD3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DE3"/>
+      <c r="DF3" t="n">
+        <v>0.335400396911774</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>0.047750801116463</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>0.613251260210731</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0.00359754176103187</v>
+      </c>
+      <c r="DJ3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DK3"/>
+      <c r="DL3" t="n">
+        <v>5124.68748535227</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>987.450282222611</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>4472.25692119133</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>275.491804443709</v>
+      </c>
+      <c r="DP3"/>
+      <c r="DQ3"/>
     </row>
-    <row r="4" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="B4">
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4">
+        <v>122</v>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4">
+        <v>123</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>1001</v>
-      </c>
-      <c r="I4">
+      <c r="H4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.1</v>
       </c>
-      <c r="J4">
-        <v>0.89622859571165403</v>
-      </c>
-      <c r="K4">
-        <v>10.3475336075009</v>
-      </c>
-      <c r="L4">
-        <v>0.95875869086416399</v>
+      <c r="J4" t="n">
+        <v>0.895057416657277</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.9589742683892</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.958969576277601</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
-      <c r="N4">
-        <v>0.92285396534869102</v>
-      </c>
-      <c r="O4">
-        <v>9.8571957579962302</v>
-      </c>
-      <c r="P4">
-        <v>0.96721088014367096</v>
+      <c r="N4" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.923428882466923</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
-      <c r="R4">
-        <v>0.89622859571165403</v>
-      </c>
-      <c r="S4">
-        <v>10.3475336075009</v>
-      </c>
-      <c r="T4">
-        <v>0.95875869086416399</v>
-      </c>
-      <c r="U4">
-        <v>3.54795897381565E-2</v>
-      </c>
-      <c r="V4">
-        <v>1.3462851339108799</v>
-      </c>
-      <c r="X4">
-        <v>-333.03677815492699</v>
-      </c>
-      <c r="Y4">
-        <v>15.271227281443901</v>
-      </c>
-      <c r="Z4">
-        <v>2.6909265905565598</v>
+      <c r="R4" t="n">
+        <v>0.895057416657277</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9.9589742683892</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.958969576277601</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0626146804723808</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.71868785431874</v>
+      </c>
+      <c r="W4"/>
+      <c r="X4" t="n">
+        <v>-330.34684001913</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>15.263362457464</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.76641294064886</v>
       </c>
       <c r="AA4" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AB4">
-        <v>-1.58954753533072</v>
+      <c r="AB4" t="n">
+        <v>-1.68700536645133</v>
       </c>
       <c r="AC4" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD4">
-        <v>0.858213282451469</v>
-      </c>
-      <c r="AE4">
-        <v>0.81747640298829205</v>
-      </c>
-      <c r="AF4">
-        <v>12.3143716210182</v>
-      </c>
-      <c r="AG4">
-        <v>13.4485813736372</v>
-      </c>
-      <c r="AH4">
-        <v>-196.434177805242</v>
-      </c>
-      <c r="AI4">
-        <v>12.407971813021399</v>
-      </c>
-      <c r="AJ4">
-        <v>2.4738860449713198</v>
-      </c>
-      <c r="AL4">
-        <v>-2.00117125918882</v>
-      </c>
+      <c r="AD4" t="n">
+        <v>0.811887724865461</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.763568144275636</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14.0022098577846</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13.4697362311685</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-280.433964904796</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>13.1086469517401</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.63661539787246</v>
+      </c>
+      <c r="AK4"/>
+      <c r="AL4" t="n">
+        <v>-2.32480604910902</v>
+      </c>
+      <c r="AM4"/>
       <c r="AN4" t="s">
-        <v>109</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AO4"/>
       <c r="AP4" t="s">
-        <v>110</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AQ4"/>
       <c r="AR4" t="s">
-        <v>111</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AS4"/>
       <c r="AT4" t="s">
-        <v>112</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="AU4"/>
       <c r="AV4" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AW4" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="AX4" t="s">
-        <v>113</v>
-      </c>
-      <c r="AZ4">
+        <v>143</v>
+      </c>
+      <c r="AY4"/>
+      <c r="AZ4" t="n">
         <v>16</v>
       </c>
       <c r="BA4" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB4">
+        <v>130</v>
+      </c>
+      <c r="BB4" t="n">
         <v>31</v>
       </c>
       <c r="BC4" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="BD4" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="BE4" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="BF4" t="s">
-        <v>114</v>
-      </c>
-      <c r="BG4">
-        <v>-196.434177805242</v>
-      </c>
-      <c r="BH4">
-        <v>12.407971813021399</v>
-      </c>
-      <c r="BI4">
-        <v>2.4738860449713198</v>
-      </c>
-      <c r="BL4">
-        <v>775.39115552809096</v>
+        <v>144</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-280.433964904796</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>13.1086469517401</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.63661539787246</v>
+      </c>
+      <c r="BJ4"/>
+      <c r="BK4"/>
+      <c r="BL4" t="n">
+        <v>786.850035095204</v>
       </c>
       <c r="BM4" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="BN4" t="s">
-        <v>112</v>
-      </c>
-      <c r="BO4">
-        <v>-372.76254231886702</v>
-      </c>
-      <c r="BP4">
-        <v>15.3397687479594</v>
-      </c>
-      <c r="BQ4">
-        <v>2.7229618075238502</v>
-      </c>
-      <c r="BS4">
-        <v>-1.4136282763791399</v>
-      </c>
-      <c r="BU4">
-        <v>971.82533333333299</v>
-      </c>
-      <c r="BV4">
-        <v>599.06279101446603</v>
+        <v>142</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-355.296606399859</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>15.0773429934962</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>2.71355393363388</v>
+      </c>
+      <c r="BR4"/>
+      <c r="BS4" t="n">
+        <v>-1.47206971464165</v>
+      </c>
+      <c r="BT4"/>
+      <c r="BU4" t="n">
+        <v>1067.284</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>711.987393600141</v>
       </c>
       <c r="BW4" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="BX4" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="BY4" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="BZ4" t="s">
-        <v>118</v>
-      </c>
-      <c r="CA4">
-        <v>0.38171324435600901</v>
-      </c>
-      <c r="CD4">
-        <v>775.39115552809096</v>
-      </c>
-      <c r="CE4">
-        <v>0.94151946655769703</v>
-      </c>
-      <c r="CG4">
+        <v>148</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.381713244356009</v>
+      </c>
+      <c r="CB4"/>
+      <c r="CC4" t="n">
+        <v>4507.17556378279</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>5184.6088405629</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>46096.6758319594</v>
+      </c>
+      <c r="CF4"/>
+      <c r="CG4" t="n">
+        <v>33168.9636835132</v>
+      </c>
+      <c r="CH4"/>
+      <c r="CI4" t="n">
+        <v>0.0506666601299665</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.0582819129883532</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.518188070211077</v>
+      </c>
+      <c r="CL4"/>
+      <c r="CM4" t="n">
+        <v>0.372863356670603</v>
+      </c>
+      <c r="CN4"/>
+      <c r="CO4"/>
+      <c r="CP4" t="n">
+        <v>786.850035095204</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.930537202398444</v>
+      </c>
+      <c r="CR4"/>
+      <c r="CS4" t="n">
         <v>1</v>
       </c>
-      <c r="CH4">
-        <v>193.185250069956</v>
-      </c>
-      <c r="CI4">
-        <v>4.0492547159819896</v>
-      </c>
-      <c r="CJ4">
-        <v>0.30694168315150799</v>
-      </c>
-      <c r="CL4">
-        <v>0.58212385287465496</v>
-      </c>
+      <c r="CT4" t="n">
+        <v>70.5874649237248</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>3.04722789125028</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.18356144535709</v>
+      </c>
+      <c r="CW4"/>
+      <c r="CX4" t="n">
+        <v>0.901986375505321</v>
+      </c>
+      <c r="CY4"/>
+      <c r="CZ4" t="n">
+        <v>6083.38171545364</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>5688.11293113439</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>52232.0069583862</v>
+      </c>
+      <c r="DC4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>30319.7402642574</v>
+      </c>
+      <c r="DE4"/>
+      <c r="DF4" t="n">
+        <v>0.0637507245165854</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.0601956029767982</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.551840993452801</v>
+      </c>
+      <c r="DI4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.324212679053816</v>
+      </c>
+      <c r="DK4"/>
+      <c r="DL4" t="n">
+        <v>2229.09211678883</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>712.062313596536</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>8676.66848864263</v>
+      </c>
+      <c r="DO4"/>
+      <c r="DP4" t="n">
+        <v>4029.41040174271</v>
+      </c>
+      <c r="DQ4"/>
     </row>
-    <row r="5" spans="1:91" x14ac:dyDescent="0.25">
-      <c r="B5">
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5" t="n">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5">
+        <v>122</v>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5">
+        <v>123</v>
+      </c>
+      <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="H5">
-        <v>1100</v>
-      </c>
-      <c r="I5">
+      <c r="H5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.1</v>
       </c>
-      <c r="J5">
-        <v>0.89622859571165403</v>
-      </c>
-      <c r="K5">
-        <v>10.3475336075009</v>
-      </c>
-      <c r="L5">
-        <v>0.95875869086416399</v>
+      <c r="J5" t="n">
+        <v>0.895057416657277</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.9589742683892</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.958969576277601</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
-      <c r="N5">
-        <v>0.92285396534869102</v>
-      </c>
-      <c r="O5">
-        <v>9.8571957579962302</v>
-      </c>
-      <c r="P5">
-        <v>0.96721088014367096</v>
+      <c r="N5" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="O5" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.923428882466923</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
-      <c r="R5">
-        <v>0.89622859571165403</v>
-      </c>
-      <c r="S5">
-        <v>10.3475336075009</v>
-      </c>
-      <c r="T5">
-        <v>0.95875869086416399</v>
-      </c>
-      <c r="U5">
-        <v>3.54795897381565E-2</v>
-      </c>
-      <c r="V5">
-        <v>1.3462851339108799</v>
-      </c>
-      <c r="X5">
-        <v>-333.03677815492699</v>
-      </c>
-      <c r="Y5">
-        <v>15.271227281443901</v>
-      </c>
-      <c r="Z5">
-        <v>2.6909265905565598</v>
+      <c r="R5" t="n">
+        <v>0.895057416657277</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9.9589742683892</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.958969576277601</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0626146804723808</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.71868785431874</v>
+      </c>
+      <c r="W5"/>
+      <c r="X5" t="n">
+        <v>-330.34684001913</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15.263362457464</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.76641294064886</v>
       </c>
       <c r="AA5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AB5">
-        <v>-1.58954753533072</v>
+      <c r="AB5" t="n">
+        <v>-1.68700536645133</v>
       </c>
       <c r="AC5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AD5">
-        <v>0.88099316969776598</v>
-      </c>
-      <c r="AE5">
-        <v>0.92419637789298603</v>
-      </c>
-      <c r="AF5">
-        <v>9.36137129299291</v>
-      </c>
-      <c r="AG5">
-        <v>7.4872982873871701</v>
-      </c>
-      <c r="AH5">
-        <v>-469.63937850461201</v>
-      </c>
-      <c r="AI5">
-        <v>18.134482749866301</v>
-      </c>
-      <c r="AJ5">
-        <v>2.90796713614181</v>
-      </c>
-      <c r="AL5">
-        <v>-1.17792381147261</v>
-      </c>
+      <c r="AD5" t="n">
+        <v>0.881641946449126</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.941776291645185</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8.67579451121668</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>6.95193965674187</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-380.259715133463</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>17.4180779631878</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.89621048342526</v>
+      </c>
+      <c r="AK5"/>
+      <c r="AL5" t="n">
+        <v>-1.04920468379364</v>
+      </c>
+      <c r="AM5"/>
       <c r="AN5" t="s">
-        <v>109</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AO5"/>
       <c r="AP5" t="s">
-        <v>110</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AQ5"/>
       <c r="AR5" t="s">
-        <v>119</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="AS5"/>
       <c r="AT5" t="s">
-        <v>112</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="AU5"/>
       <c r="AV5" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AW5" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="AX5" t="s">
-        <v>114</v>
-      </c>
-      <c r="AZ5">
+        <v>144</v>
+      </c>
+      <c r="AY5"/>
+      <c r="AZ5" t="n">
         <v>15</v>
       </c>
       <c r="BA5" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB5">
+        <v>130</v>
+      </c>
+      <c r="BB5" t="n">
         <v>31</v>
       </c>
       <c r="BC5" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="BD5" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="BE5" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="BF5" t="s">
-        <v>113</v>
-      </c>
-      <c r="BG5">
-        <v>-469.63937850461201</v>
-      </c>
-      <c r="BH5">
-        <v>18.134482749866301</v>
-      </c>
-      <c r="BI5">
-        <v>2.90796713614181</v>
-      </c>
-      <c r="BL5">
-        <v>466.55624649538697</v>
+        <v>143</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-380.259715133463</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>17.4180779631878</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.89621048342526</v>
+      </c>
+      <c r="BJ5"/>
+      <c r="BK5"/>
+      <c r="BL5" t="n">
+        <v>466.443409866537</v>
       </c>
       <c r="BM5" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="BN5" t="s">
-        <v>112</v>
-      </c>
-      <c r="BO5">
-        <v>-372.41991957109298</v>
-      </c>
-      <c r="BP5">
-        <v>15.3397687479594</v>
-      </c>
-      <c r="BQ5">
-        <v>2.7229618075238502</v>
-      </c>
-      <c r="BS5">
-        <v>-1.4136282763791399</v>
-      </c>
-      <c r="BU5">
-        <v>936.19562499999995</v>
-      </c>
-      <c r="BV5">
-        <v>563.77570542890703</v>
+        <v>142</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-355.296606399859</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>15.0773429934962</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>2.71355393363388</v>
+      </c>
+      <c r="BR5"/>
+      <c r="BS5" t="n">
+        <v>-1.47206971464165</v>
+      </c>
+      <c r="BT5"/>
+      <c r="BU5" t="n">
+        <v>846.703125</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>491.406518600141</v>
       </c>
       <c r="BW5" t="s">
+        <v>146</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>146</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>147</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>148</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.381713244356009</v>
+      </c>
+      <c r="CB5"/>
+      <c r="CC5" t="n">
+        <v>7659.5878671245</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>6191.61702170588</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>58367.3380848131</v>
+      </c>
+      <c r="CF5"/>
+      <c r="CG5" t="n">
+        <v>27470.5168450015</v>
+      </c>
+      <c r="CH5"/>
+      <c r="CI5" t="n">
+        <v>0.0768347889032044</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.0621092929652433</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.585493916694524</v>
+      </c>
+      <c r="CL5"/>
+      <c r="CM5" t="n">
+        <v>0.275562001437029</v>
+      </c>
+      <c r="CN5"/>
+      <c r="CO5"/>
+      <c r="CP5" t="n">
+        <v>466.443409866537</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.955100255495129</v>
+      </c>
+      <c r="CR5"/>
+      <c r="CS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>70.5874649237248</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>3.04722789125028</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0.18356144535709</v>
+      </c>
+      <c r="CW5"/>
+      <c r="CX5" t="n">
+        <v>0.901986375505321</v>
+      </c>
+      <c r="CY5"/>
+      <c r="CZ5" t="n">
+        <v>6083.38171545364</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>5688.11293113439</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>52232.0069583862</v>
+      </c>
+      <c r="DC5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>30319.7402642574</v>
+      </c>
+      <c r="DE5"/>
+      <c r="DF5" t="n">
+        <v>0.0637507245165854</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0.0601956029767982</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0.551840993452801</v>
+      </c>
+      <c r="DI5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0.324212679053816</v>
+      </c>
+      <c r="DK5"/>
+      <c r="DL5" t="n">
+        <v>2229.09211678883</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>712.062313596536</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>8676.66848864263</v>
+      </c>
+      <c r="DO5"/>
+      <c r="DP5" t="n">
+        <v>4029.41040174271</v>
+      </c>
+      <c r="DQ5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>121</v>
       </c>
-      <c r="BX5" t="s">
+      <c r="D6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.843790856019427</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11.6945603720711</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.936078593670723</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.923428882466923</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.843790856019427</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11.6945603720711</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.936078593670723</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.100821177573966</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.7544323658953</v>
+      </c>
+      <c r="W6"/>
+      <c r="X6" t="n">
+        <v>-307.681133989504</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>12.3763556399368</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.63955941204439</v>
+      </c>
+      <c r="AA6" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1.48180088254798</v>
+      </c>
+      <c r="AC6" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.67992409091989</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.643458278243626</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>17.6312864242358</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>17.9402611353216</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-294.959515188274</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.98788728400377</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3.08322314950392</v>
+      </c>
+      <c r="AK6"/>
+      <c r="AL6" t="n">
+        <v>-1.02358320368712</v>
+      </c>
+      <c r="AM6"/>
+      <c r="AN6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO6"/>
+      <c r="AP6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ6"/>
+      <c r="AR6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AS6"/>
+      <c r="AT6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU6"/>
+      <c r="AV6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AY6"/>
+      <c r="AZ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>31</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>132</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>152</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-294.959515188274</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1.98788728400377</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.08322314950392</v>
+      </c>
+      <c r="BJ6"/>
+      <c r="BK6"/>
+      <c r="BL6" t="n">
+        <v>703.82381814506</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>145</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>142</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-355.296606399859</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>15.0773429934962</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>2.71355393363388</v>
+      </c>
+      <c r="BR6"/>
+      <c r="BS6" t="n">
+        <v>-1.47206971464165</v>
+      </c>
+      <c r="BT6"/>
+      <c r="BU6" t="n">
+        <v>998.783333333333</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>643.486726933474</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>146</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>146</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>147</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>148</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.381713244356009</v>
+      </c>
+      <c r="CB6"/>
+      <c r="CC6" t="n">
+        <v>7150.91366100072</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>275.254609000125</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>64375.0357935475</v>
+      </c>
+      <c r="CF6"/>
+      <c r="CG6" t="n">
+        <v>35125.7580307174</v>
+      </c>
+      <c r="CH6"/>
+      <c r="CI6" t="n">
+        <v>0.0668766185903285</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.00257423014372618</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.602046804030541</v>
+      </c>
+      <c r="CL6"/>
+      <c r="CM6" t="n">
+        <v>0.328502347235404</v>
+      </c>
+      <c r="CN6"/>
+      <c r="CO6"/>
+      <c r="CP6" t="n">
+        <v>703.82381814506</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.859999445383316</v>
+      </c>
+      <c r="CR6"/>
+      <c r="CS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>17.9910858440403</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>14.6915128412443</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.627435274648404</v>
+      </c>
+      <c r="CW6"/>
+      <c r="CX6" t="n">
+        <v>0.648017655964142</v>
+      </c>
+      <c r="CY6"/>
+      <c r="CZ6" t="n">
+        <v>7061.24408019181</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>6922.73785791078</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>58159.0372522406</v>
+      </c>
+      <c r="DC6" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>35072.3932906588</v>
+      </c>
+      <c r="DE6"/>
+      <c r="DF6" t="n">
+        <v>0.0658630720590847</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.0644021545914979</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.542610249805285</v>
+      </c>
+      <c r="DI6" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.327124523544133</v>
+      </c>
+      <c r="DK6"/>
+      <c r="DL6" t="n">
+        <v>126.811937312263</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>9400.96096625741</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>8790.74944080751</v>
+      </c>
+      <c r="DO6"/>
+      <c r="DP6" t="n">
+        <v>75.4691391432655</v>
+      </c>
+      <c r="DQ6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
         <v>121</v>
       </c>
-      <c r="BY5" t="s">
+      <c r="D7" t="s">
         <v>122</v>
       </c>
-      <c r="BZ5" t="s">
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
         <v>123</v>
       </c>
-      <c r="CA5">
-        <v>0.38171324435600901</v>
-      </c>
-      <c r="CD5">
-        <v>466.55624649538697</v>
-      </c>
-      <c r="CE5">
-        <v>0.959093536611616</v>
-      </c>
-      <c r="CG5">
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.843790856019427</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11.6945603720711</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.936078593670723</v>
+      </c>
+      <c r="M7" t="b">
         <v>1</v>
       </c>
-      <c r="CH5">
-        <v>193.185250069956</v>
-      </c>
-      <c r="CI5">
-        <v>4.0492547159819896</v>
-      </c>
-      <c r="CJ5">
-        <v>0.30694168315150799</v>
-      </c>
-      <c r="CL5">
-        <v>0.58212385287465496</v>
-      </c>
+      <c r="N7" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.923428882466923</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.843790856019427</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11.6945603720711</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.936078593670723</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.100821177573966</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.7544323658953</v>
+      </c>
+      <c r="W7"/>
+      <c r="X7" t="n">
+        <v>-307.681133989504</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>12.3763556399368</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.63955941204439</v>
+      </c>
+      <c r="AA7" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1.48180088254798</v>
+      </c>
+      <c r="AC7" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.802591378567561</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.890765260538358</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12.7001787346342</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>9.69430407364479</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-320.402752790734</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>22.7648239958699</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.19589567458486</v>
+      </c>
+      <c r="AK7"/>
+      <c r="AL7" t="n">
+        <v>-1.94001856140884</v>
+      </c>
+      <c r="AM7"/>
+      <c r="AN7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO7"/>
+      <c r="AP7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ7"/>
+      <c r="AR7" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS7"/>
+      <c r="AT7" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU7"/>
+      <c r="AV7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>152</v>
+      </c>
+      <c r="AY7"/>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>31</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>132</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>153</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>151</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-320.402752790734</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>22.7648239958699</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.19589567458486</v>
+      </c>
+      <c r="BJ7"/>
+      <c r="BK7"/>
+      <c r="BL7" t="n">
+        <v>590.519747209266</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>142</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-355.296606399859</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>15.0773429934962</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>2.71355393363388</v>
+      </c>
+      <c r="BR7"/>
+      <c r="BS7" t="n">
+        <v>-1.47206971464165</v>
+      </c>
+      <c r="BT7"/>
+      <c r="BU7" t="n">
+        <v>910.9225</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>555.625893600141</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>146</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>146</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>147</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>148</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.381713244356009</v>
+      </c>
+      <c r="CB7"/>
+      <c r="CC7" t="n">
+        <v>6971.57449938291</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>13570.2211068214</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>51943.0387109338</v>
+      </c>
+      <c r="CF7"/>
+      <c r="CG7" t="n">
+        <v>35019.0285506003</v>
+      </c>
+      <c r="CH7"/>
+      <c r="CI7" t="n">
+        <v>0.0648495255278409</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.12623007903927</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.483173695580029</v>
+      </c>
+      <c r="CL7"/>
+      <c r="CM7" t="n">
+        <v>0.325746699852861</v>
+      </c>
+      <c r="CN7"/>
+      <c r="CO7"/>
+      <c r="CP7" t="n">
+        <v>590.519747209266</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.920593811530622</v>
+      </c>
+      <c r="CR7"/>
+      <c r="CS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>17.9910858440403</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>14.6915128412443</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.627435274648404</v>
+      </c>
+      <c r="CW7"/>
+      <c r="CX7" t="n">
+        <v>0.648017655964142</v>
+      </c>
+      <c r="CY7"/>
+      <c r="CZ7" t="n">
+        <v>7061.24408019181</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>6922.73785791078</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>58159.0372522406</v>
+      </c>
+      <c r="DC7" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>35072.3932906588</v>
+      </c>
+      <c r="DE7"/>
+      <c r="DF7" t="n">
+        <v>0.0658630720590847</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.0644021545914979</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.542610249805285</v>
+      </c>
+      <c r="DI7" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.327124523544133</v>
+      </c>
+      <c r="DK7"/>
+      <c r="DL7" t="n">
+        <v>126.811937312263</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>9400.96096625741</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>8790.74944080751</v>
+      </c>
+      <c r="DO7"/>
+      <c r="DP7" t="n">
+        <v>75.4691391432655</v>
+      </c>
+      <c r="DQ7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.923428882466923</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="O8" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.923428882466923</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.923428882466923</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.225139647445005</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.70568645971381</v>
+      </c>
+      <c r="W8"/>
+      <c r="X8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.66036677869078</v>
+      </c>
+      <c r="AA8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1.60371333567494</v>
+      </c>
+      <c r="AC8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.40844302878679</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.1516996152784</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13.7088816656405</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>20.7622203919317</v>
+      </c>
+      <c r="AH8"/>
+      <c r="AI8"/>
+      <c r="AJ8" t="n">
+        <v>2.68766778470884</v>
+      </c>
+      <c r="AK8"/>
+      <c r="AL8" t="n">
+        <v>-2.3543752289443</v>
+      </c>
+      <c r="AM8"/>
+      <c r="AN8" t="s">
+        <v>154</v>
+      </c>
+      <c r="AO8"/>
+      <c r="AP8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AQ8"/>
+      <c r="AR8" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS8"/>
+      <c r="AT8" t="s">
+        <v>157</v>
+      </c>
+      <c r="AU8"/>
+      <c r="AV8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>158</v>
+      </c>
+      <c r="AY8"/>
+      <c r="AZ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>132</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>156</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>159</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-15.9528793943367</v>
+      </c>
+      <c r="BH8"/>
+      <c r="BI8" t="n">
+        <v>2.68766778470884</v>
+      </c>
+      <c r="BJ8"/>
+      <c r="BK8"/>
+      <c r="BL8" t="n">
+        <v>1059.61378727233</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>160</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>157</v>
+      </c>
+      <c r="BO8"/>
+      <c r="BP8"/>
+      <c r="BQ8" t="n">
+        <v>2.79045140386664</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>-0.360591298064282</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-1.06893696028779</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-0.154006854914166</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1075.56666666667</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1075.56666666667</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>161</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>161</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>163</v>
+      </c>
+      <c r="CA8"/>
+      <c r="CB8" t="n">
+        <v>-0.824175767887696</v>
+      </c>
+      <c r="CC8"/>
+      <c r="CD8"/>
+      <c r="CE8" t="n">
+        <v>38671.2775424346</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>33184.8776725946</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.158831831976039</v>
+      </c>
+      <c r="CI8"/>
+      <c r="CJ8"/>
+      <c r="CK8" t="n">
+        <v>0.538098655107051</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0.461757127778379</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.00000221009494917025</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0.158831831976039</v>
+      </c>
+      <c r="CP8"/>
+      <c r="CQ8" t="n">
+        <v>0.816068524263708</v>
+      </c>
+      <c r="CR8"/>
+      <c r="CS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT8"/>
+      <c r="CU8"/>
+      <c r="CV8" t="n">
+        <v>0.0386094529771716</v>
+      </c>
+      <c r="CW8"/>
+      <c r="CX8" t="n">
+        <v>1.0615962302182</v>
+      </c>
+      <c r="CY8"/>
+      <c r="CZ8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DA8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>24121.5598652763</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>20940.7449248358</v>
+      </c>
+      <c r="DE8"/>
+      <c r="DF8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DG8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.527618359035469</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.465804562835587</v>
+      </c>
+      <c r="DK8"/>
+      <c r="DL8"/>
+      <c r="DM8"/>
+      <c r="DN8" t="n">
+        <v>20576.4080677369</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>17315.818591377</v>
+      </c>
+      <c r="DQ8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.923428882466923</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="O9" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.923428882466923</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.947871655299846</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11.3531470030297</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.923428882466923</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.225139647445005</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.70568645971381</v>
+      </c>
+      <c r="W9"/>
+      <c r="X9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.66036677869078</v>
+      </c>
+      <c r="AA9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-1.60371333567494</v>
+      </c>
+      <c r="AC9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.11178507749541</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.02161952077338</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>6.94893212617071</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.19540489019685</v>
+      </c>
+      <c r="AH9"/>
+      <c r="AI9"/>
+      <c r="AJ9" t="n">
+        <v>2.63306577267272</v>
+      </c>
+      <c r="AK9"/>
+      <c r="AL9" t="n">
+        <v>-0.853051442405572</v>
+      </c>
+      <c r="AM9"/>
+      <c r="AN9" t="s">
+        <v>154</v>
+      </c>
+      <c r="AO9"/>
+      <c r="AP9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AQ9"/>
+      <c r="AR9" t="s">
+        <v>164</v>
+      </c>
+      <c r="AS9"/>
+      <c r="AT9" t="s">
+        <v>157</v>
+      </c>
+      <c r="AU9"/>
+      <c r="AV9" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>159</v>
+      </c>
+      <c r="AY9"/>
+      <c r="AZ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>132</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>164</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>158</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-8.12145819658074</v>
+      </c>
+      <c r="BH9"/>
+      <c r="BI9" t="n">
+        <v>2.63306577267272</v>
+      </c>
+      <c r="BJ9"/>
+      <c r="BK9"/>
+      <c r="BL9" t="n">
+        <v>823.253541803419</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>160</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>157</v>
+      </c>
+      <c r="BO9"/>
+      <c r="BP9"/>
+      <c r="BQ9" t="n">
+        <v>2.79045140386664</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-0.360591298064282</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-1.06893696028779</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0.154006854914166</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>831.375</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>831.375</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>161</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>161</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>163</v>
+      </c>
+      <c r="CA9"/>
+      <c r="CB9" t="n">
+        <v>-0.824175767887696</v>
+      </c>
+      <c r="CC9"/>
+      <c r="CD9"/>
+      <c r="CE9" t="n">
+        <v>9571.84218811793</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>8696.612177077</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-1.00217486182996</v>
+      </c>
+      <c r="CI9"/>
+      <c r="CJ9"/>
+      <c r="CK9" t="n">
+        <v>0.517138062963887</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.469851997892796</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.0000541445164485889</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-1.00217486182996</v>
+      </c>
+      <c r="CP9"/>
+      <c r="CQ9" t="n">
+        <v>0.954890973447339</v>
+      </c>
+      <c r="CR9"/>
+      <c r="CS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT9"/>
+      <c r="CU9"/>
+      <c r="CV9" t="n">
+        <v>0.0386094529771716</v>
+      </c>
+      <c r="CW9"/>
+      <c r="CX9" t="n">
+        <v>1.0615962302182</v>
+      </c>
+      <c r="CY9"/>
+      <c r="CZ9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DA9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>24121.5598652763</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>20940.7449248358</v>
+      </c>
+      <c r="DE9"/>
+      <c r="DF9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DG9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.527618359035469</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.465804562835587</v>
+      </c>
+      <c r="DK9"/>
+      <c r="DL9"/>
+      <c r="DM9"/>
+      <c r="DN9" t="n">
+        <v>20576.4080677369</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>17315.818591377</v>
+      </c>
+      <c r="DQ9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>